--- a/inp_Excel/ana_date_viaggi.xlsx
+++ b/inp_Excel/ana_date_viaggi.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="22">
   <si>
     <t>VIAGGIO_ID_FK</t>
   </si>
@@ -178,8 +178,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:P148" totalsRowShown="0" headerRowCount="1">
-  <autoFilter ref="A1:P148"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:P143" totalsRowShown="0" headerRowCount="1">
+  <autoFilter ref="A1:P143"/>
   <tableColumns count="16">
     <tableColumn id="1" name="VIAGGIO_ID_FK"/>
     <tableColumn id="2" name="DATA_VIAGGIO_ID"/>
@@ -1185,25 +1185,25 @@
     </row>
     <row r="26" customHeight="1" ht="20">
       <c r="A26" s="5" t="n">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>1543</v>
+        <v>1585</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>45798</v>
+        <v>45804</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>45807</v>
+        <v>45810</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>5700</v>
+        <v>960</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>4500</v>
+        <v>960</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -1211,39 +1211,39 @@
       <c r="K26" s="5"/>
       <c r="L26" s="7"/>
       <c r="M26" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>45661</v>
+        <v>45700</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P26" s="8" t="n">
-        <v>45788.4144907407</v>
+        <v>46030.6455092593</v>
       </c>
     </row>
     <row r="27" customHeight="1" ht="20">
       <c r="A27" s="5" t="n">
-        <v>601</v>
+        <v>624</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1564</v>
+        <v>1587</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>45757</v>
+        <v>45825</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>45767</v>
+        <v>45829</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>6700</v>
+        <v>390</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>6500</v>
+        <v>390</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
@@ -1251,39 +1251,39 @@
       <c r="K27" s="5"/>
       <c r="L27" s="7"/>
       <c r="M27" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>45669</v>
+        <v>45700</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P27" s="8" t="n">
-        <v>45748.5811226852</v>
+        <v>45908.4481365741</v>
       </c>
     </row>
     <row r="28" customHeight="1" ht="20">
       <c r="A28" s="5" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>45804</v>
+        <v>46252</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>45810</v>
+        <v>46262</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
@@ -1300,30 +1300,30 @@
         <v>19</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>45811.528275463</v>
+        <v>45983.3247569444</v>
       </c>
     </row>
     <row r="29" customHeight="1" ht="20">
       <c r="A29" s="5" t="n">
-        <v>624</v>
+        <v>822</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>1587</v>
+        <v>1784</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>45825</v>
+        <v>46045</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>45829</v>
+        <v>46047</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>390</v>
+        <v>490</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>390</v>
+        <v>490</v>
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
@@ -1334,36 +1334,32 @@
         <v>19</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>45700</v>
-      </c>
-      <c r="O29" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P29" s="8" t="n">
-        <v>45908.4481365741</v>
-      </c>
+        <v>45983.3522106481</v>
+      </c>
+      <c r="O29" s="7"/>
+      <c r="P29" s="8"/>
     </row>
     <row r="30" customHeight="1" ht="20">
       <c r="A30" s="5" t="n">
-        <v>626</v>
+        <v>61</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1588</v>
+        <v>121</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>46252</v>
+        <v>44470</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>46262</v>
+        <v>44472</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>940</v>
+        <v>350</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>940</v>
+        <v>150</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
@@ -1371,39 +1367,35 @@
       <c r="K30" s="5"/>
       <c r="L30" s="7"/>
       <c r="M30" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N30" s="8" t="n">
-        <v>45700</v>
-      </c>
-      <c r="O30" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P30" s="8" t="n">
-        <v>45983.3247569444</v>
-      </c>
+        <v>44468.7524884259</v>
+      </c>
+      <c r="O30" s="7"/>
+      <c r="P30" s="8"/>
     </row>
     <row r="31" customHeight="1" ht="20">
       <c r="A31" s="5" t="n">
-        <v>822</v>
+        <v>1</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>1784</v>
+        <v>141</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>46045</v>
+        <v>44513</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>46047</v>
+        <v>44514</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>490</v>
+        <v>230</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>490</v>
+        <v>130</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -1411,35 +1403,35 @@
       <c r="K31" s="5"/>
       <c r="L31" s="7"/>
       <c r="M31" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N31" s="8" t="n">
-        <v>45983.3522106481</v>
+        <v>44515.6906597222</v>
       </c>
       <c r="O31" s="7"/>
       <c r="P31" s="8"/>
     </row>
     <row r="32" customHeight="1" ht="20">
       <c r="A32" s="5" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>44470</v>
+        <v>44625</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>44472</v>
+        <v>44626</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>350</v>
+        <v>245</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -1450,32 +1442,36 @@
         <v>17</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>44468.7524884259</v>
-      </c>
-      <c r="O32" s="7"/>
-      <c r="P32" s="8"/>
+        <v>44594</v>
+      </c>
+      <c r="O32" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P32" s="8" t="n">
+        <v>44627.6058680556</v>
+      </c>
     </row>
     <row r="33" customHeight="1" ht="20">
       <c r="A33" s="5" t="n">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>44513</v>
+        <v>44863</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>44514</v>
+        <v>44866</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>230</v>
+        <v>540</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>130</v>
+        <v>340</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
@@ -1486,32 +1482,36 @@
         <v>17</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>44515.6906597222</v>
-      </c>
-      <c r="O33" s="7"/>
-      <c r="P33" s="8"/>
+        <v>44645</v>
+      </c>
+      <c r="O33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>44875.334537037</v>
+      </c>
     </row>
     <row r="34" customHeight="1" ht="20">
       <c r="A34" s="5" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>162</v>
+        <v>282</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>44625</v>
+        <v>44660</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>44626</v>
+        <v>44660</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>245</v>
+        <v>130</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
@@ -1522,36 +1522,36 @@
         <v>17</v>
       </c>
       <c r="N34" s="8" t="n">
-        <v>44594</v>
+        <v>44648</v>
       </c>
       <c r="O34" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>44627.6058680556</v>
+        <v>44659.3133333333</v>
       </c>
     </row>
     <row r="35" customHeight="1" ht="20">
       <c r="A35" s="5" t="n">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>44863</v>
+        <v>44661</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>44866</v>
+        <v>44661</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>540</v>
+        <v>130</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>340</v>
+        <v>30</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
@@ -1562,36 +1562,36 @@
         <v>17</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>44645</v>
+        <v>44648</v>
       </c>
       <c r="O35" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>44875.334537037</v>
+        <v>44785.5688194444</v>
       </c>
     </row>
     <row r="36" customHeight="1" ht="20">
       <c r="A36" s="5" t="n">
-        <v>52</v>
+        <v>221</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>282</v>
+        <v>542</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>44660</v>
+        <v>44868</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>44660</v>
+        <v>44871</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
@@ -1602,36 +1602,32 @@
         <v>17</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>44648</v>
-      </c>
-      <c r="O36" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P36" s="8" t="n">
-        <v>44659.3133333333</v>
-      </c>
+        <v>44878.7394907407</v>
+      </c>
+      <c r="O36" s="7"/>
+      <c r="P36" s="8"/>
     </row>
     <row r="37" customHeight="1" ht="20">
       <c r="A37" s="5" t="n">
-        <v>49</v>
+        <v>241</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>283</v>
+        <v>662</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>44661</v>
+        <v>45059</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>44661</v>
+        <v>45060</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
@@ -1642,36 +1638,36 @@
         <v>17</v>
       </c>
       <c r="N37" s="8" t="n">
-        <v>44648</v>
+        <v>44965</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P37" s="8" t="n">
-        <v>44785.5688194444</v>
+        <v>45062.5050347222</v>
       </c>
     </row>
     <row r="38" customHeight="1" ht="20">
       <c r="A38" s="5" t="n">
-        <v>221</v>
+        <v>261</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>542</v>
+        <v>762</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>44868</v>
+        <v>45002</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>44871</v>
+        <v>45004</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
@@ -1682,32 +1678,36 @@
         <v>17</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>44878.7394907407</v>
-      </c>
-      <c r="O38" s="7"/>
-      <c r="P38" s="8"/>
+        <v>45000</v>
+      </c>
+      <c r="O38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P38" s="8" t="n">
+        <v>45004.5737615741</v>
+      </c>
     </row>
     <row r="39" customHeight="1" ht="20">
       <c r="A39" s="5" t="n">
-        <v>241</v>
+        <v>301</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>662</v>
+        <v>842</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>45059</v>
+        <v>45079</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>45060</v>
+        <v>45081</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
@@ -1718,36 +1718,32 @@
         <v>17</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>44965</v>
-      </c>
-      <c r="O39" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P39" s="8" t="n">
-        <v>45062.5050347222</v>
-      </c>
+        <v>45035.7764699074</v>
+      </c>
+      <c r="O39" s="7"/>
+      <c r="P39" s="8"/>
     </row>
     <row r="40" customHeight="1" ht="20">
       <c r="A40" s="5" t="n">
-        <v>261</v>
+        <v>341</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>762</v>
+        <v>882</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>45002</v>
+        <v>45044</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>45004</v>
+        <v>45046</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
@@ -1758,36 +1754,32 @@
         <v>17</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O40" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P40" s="8" t="n">
-        <v>45004.5737615741</v>
-      </c>
+        <v>45049.8069675926</v>
+      </c>
+      <c r="O40" s="7"/>
+      <c r="P40" s="8"/>
     </row>
     <row r="41" customHeight="1" ht="20">
       <c r="A41" s="5" t="n">
-        <v>301</v>
+        <v>46</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>842</v>
+        <v>922</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>45079</v>
+        <v>45087</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>45081</v>
+        <v>45088</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
@@ -1798,32 +1790,32 @@
         <v>17</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>45035.7764699074</v>
+        <v>45079.3949074074</v>
       </c>
       <c r="O41" s="7"/>
       <c r="P41" s="8"/>
     </row>
     <row r="42" customHeight="1" ht="20">
       <c r="A42" s="5" t="n">
-        <v>341</v>
+        <v>48</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>882</v>
+        <v>1002</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>45044</v>
+        <v>45178</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>45046</v>
+        <v>45179</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
@@ -1834,26 +1826,26 @@
         <v>17</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>45049.8069675926</v>
+        <v>45129.5794328704</v>
       </c>
       <c r="O42" s="7"/>
       <c r="P42" s="8"/>
     </row>
     <row r="43" customHeight="1" ht="20">
       <c r="A43" s="5" t="n">
-        <v>46</v>
+        <v>461</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>922</v>
+        <v>1222</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>45087</v>
+        <v>45332</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>45088</v>
+        <v>45333</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F43" s="5" t="n">
         <v>250</v>
@@ -1870,32 +1862,36 @@
         <v>17</v>
       </c>
       <c r="N43" s="8" t="n">
-        <v>45079.3949074074</v>
-      </c>
-      <c r="O43" s="7"/>
-      <c r="P43" s="8"/>
+        <v>45285</v>
+      </c>
+      <c r="O43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P43" s="8" t="n">
+        <v>45335.3894675926</v>
+      </c>
     </row>
     <row r="44" customHeight="1" ht="20">
       <c r="A44" s="5" t="n">
-        <v>48</v>
+        <v>501</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1002</v>
+        <v>1322</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>45178</v>
+        <v>45381</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>45179</v>
+        <v>45383</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>250</v>
+        <v>395</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -1906,32 +1902,36 @@
         <v>17</v>
       </c>
       <c r="N44" s="8" t="n">
-        <v>45129.5794328704</v>
-      </c>
-      <c r="O44" s="7"/>
-      <c r="P44" s="8"/>
+        <v>45310</v>
+      </c>
+      <c r="O44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P44" s="8" t="n">
+        <v>45386.3521296296</v>
+      </c>
     </row>
     <row r="45" customHeight="1" ht="20">
       <c r="A45" s="5" t="n">
-        <v>461</v>
+        <v>521</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1222</v>
+        <v>1423</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>45332</v>
+        <v>45512</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>45333</v>
+        <v>45529</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>250</v>
+        <v>1650</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>150</v>
+        <v>1100</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
@@ -1942,76 +1942,78 @@
         <v>17</v>
       </c>
       <c r="N45" s="8" t="n">
-        <v>45285</v>
+        <v>45348</v>
       </c>
       <c r="O45" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>45335.3894675926</v>
+        <v>45517.6562268519</v>
       </c>
     </row>
     <row r="46" customHeight="1" ht="20">
       <c r="A46" s="5" t="n">
-        <v>501</v>
+        <v>261</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1322</v>
+        <v>1463</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>45381</v>
+        <v>45421</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>45383</v>
+        <v>45423</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>395</v>
+        <v>150</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
-      <c r="L46" s="7"/>
+      <c r="L46" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="M46" s="7" t="s">
         <v>17</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>45310</v>
+        <v>45419</v>
       </c>
       <c r="O46" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>45386.3521296296</v>
+        <v>45419.5241203704</v>
       </c>
     </row>
     <row r="47" customHeight="1" ht="20">
       <c r="A47" s="5" t="n">
-        <v>521</v>
+        <v>461</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1423</v>
+        <v>1483</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>45512</v>
+        <v>45458</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>45529</v>
+        <v>45459</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>1650</v>
+        <v>250</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1100</v>
+        <v>150</v>
       </c>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
@@ -2022,78 +2024,72 @@
         <v>17</v>
       </c>
       <c r="N47" s="8" t="n">
-        <v>45348</v>
-      </c>
-      <c r="O47" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P47" s="8" t="n">
-        <v>45517.6562268519</v>
-      </c>
+        <v>45446.6197337963</v>
+      </c>
+      <c r="O47" s="7"/>
+      <c r="P47" s="8"/>
     </row>
     <row r="48" customHeight="1" ht="20">
       <c r="A48" s="5" t="n">
-        <v>261</v>
+        <v>621</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1463</v>
+        <v>1584</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>45421</v>
+        <v>45774</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>45423</v>
+        <v>45780</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>150</v>
+        <v>1060</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>80</v>
+        <v>1060</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
-      <c r="L48" s="7" t="s">
-        <v>20</v>
-      </c>
+      <c r="L48" s="7"/>
       <c r="M48" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N48" s="8" t="n">
-        <v>45419</v>
+        <v>45700</v>
       </c>
       <c r="O48" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P48" s="8" t="n">
-        <v>45419.5241203704</v>
+        <v>45793.6937847222</v>
       </c>
     </row>
     <row r="49" customHeight="1" ht="20">
       <c r="A49" s="5" t="n">
-        <v>461</v>
+        <v>54</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>1483</v>
+        <v>41</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>45458</v>
+        <v>44002</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>45459</v>
+        <v>44003</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
@@ -2104,32 +2100,36 @@
         <v>17</v>
       </c>
       <c r="N49" s="8" t="n">
-        <v>45446.6197337963</v>
-      </c>
-      <c r="O49" s="7"/>
-      <c r="P49" s="8"/>
+        <v>44445</v>
+      </c>
+      <c r="O49" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P49" s="8" t="n">
+        <v>44764.5170138889</v>
+      </c>
     </row>
     <row r="50" customHeight="1" ht="20">
       <c r="A50" s="5" t="n">
-        <v>701</v>
+        <v>49</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>1663</v>
+        <v>54</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>45915</v>
+        <v>44150</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>45919</v>
+        <v>44150</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>680</v>
+        <v>130</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>680</v>
+        <v>30</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
@@ -2137,35 +2137,35 @@
       <c r="K50" s="5"/>
       <c r="L50" s="7"/>
       <c r="M50" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N50" s="8" t="n">
-        <v>45811.5362615741</v>
+        <v>44446.5280439815</v>
       </c>
       <c r="O50" s="7"/>
       <c r="P50" s="8"/>
     </row>
     <row r="51" customHeight="1" ht="20">
       <c r="A51" s="5" t="n">
-        <v>621</v>
+        <v>46</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>1584</v>
+        <v>62</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>45774</v>
+        <v>43883</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>45780</v>
+        <v>43884</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>1060</v>
+        <v>230</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>1060</v>
+        <v>130</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
@@ -2173,33 +2173,33 @@
       <c r="K51" s="5"/>
       <c r="L51" s="7"/>
       <c r="M51" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N51" s="8" t="n">
-        <v>45700</v>
+        <v>44446</v>
       </c>
       <c r="O51" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P51" s="8" t="n">
-        <v>45793.6937847222</v>
+        <v>44792.650150463</v>
       </c>
     </row>
     <row r="52" customHeight="1" ht="20">
       <c r="A52" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C52" s="6" t="n">
-        <v>44002</v>
+        <v>44471</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>44003</v>
+        <v>44472</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>230</v>
@@ -2216,36 +2216,32 @@
         <v>17</v>
       </c>
       <c r="N52" s="8" t="n">
-        <v>44445</v>
-      </c>
-      <c r="O52" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P52" s="8" t="n">
-        <v>44764.5170138889</v>
-      </c>
+        <v>44446.5346527778</v>
+      </c>
+      <c r="O52" s="7"/>
+      <c r="P52" s="8"/>
     </row>
     <row r="53" customHeight="1" ht="20">
       <c r="A53" s="5" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>54</v>
+        <v>622</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>44150</v>
+        <v>45024</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>44150</v>
+        <v>45030</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>130</v>
+        <v>1190</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>30</v>
+        <v>840</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
@@ -2256,32 +2252,32 @@
         <v>17</v>
       </c>
       <c r="N53" s="8" t="n">
-        <v>44446.5280439815</v>
+        <v>44930.4891435185</v>
       </c>
       <c r="O53" s="7"/>
       <c r="P53" s="8"/>
     </row>
     <row r="54" customHeight="1" ht="20">
       <c r="A54" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>62</v>
+        <v>202</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>43883</v>
+        <v>44618</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>43884</v>
+        <v>44619</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
@@ -2292,36 +2288,36 @@
         <v>17</v>
       </c>
       <c r="N54" s="8" t="n">
-        <v>44446</v>
+        <v>44607</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P54" s="8" t="n">
-        <v>44792.650150463</v>
+        <v>44792.5757407407</v>
       </c>
     </row>
     <row r="55" customHeight="1" ht="20">
       <c r="A55" s="5" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>68</v>
+        <v>242</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>44471</v>
+        <v>44809</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>44472</v>
+        <v>44815</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>230</v>
+        <v>980</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>130</v>
+        <v>690</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
@@ -2332,32 +2328,32 @@
         <v>17</v>
       </c>
       <c r="N55" s="8" t="n">
-        <v>44446.5346527778</v>
+        <v>44620.8319791667</v>
       </c>
       <c r="O55" s="7"/>
       <c r="P55" s="8"/>
     </row>
     <row r="56" customHeight="1" ht="20">
       <c r="A56" s="5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>622</v>
+        <v>382</v>
       </c>
       <c r="C56" s="6" t="n">
-        <v>45024</v>
+        <v>44702</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>45030</v>
+        <v>44703</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>1190</v>
+        <v>245</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>840</v>
+        <v>140</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
@@ -2368,23 +2364,27 @@
         <v>17</v>
       </c>
       <c r="N56" s="8" t="n">
-        <v>44930.4891435185</v>
-      </c>
-      <c r="O56" s="7"/>
-      <c r="P56" s="8"/>
+        <v>44686</v>
+      </c>
+      <c r="O56" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P56" s="8" t="n">
+        <v>44701.8047222222</v>
+      </c>
     </row>
     <row r="57" customHeight="1" ht="20">
       <c r="A57" s="5" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>202</v>
+        <v>402</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>44618</v>
+        <v>44835</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>44619</v>
+        <v>44836</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>18</v>
@@ -2404,36 +2404,36 @@
         <v>17</v>
       </c>
       <c r="N57" s="8" t="n">
-        <v>44607</v>
+        <v>44732</v>
       </c>
       <c r="O57" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P57" s="8" t="n">
-        <v>44792.5757407407</v>
+        <v>44834.645</v>
       </c>
     </row>
     <row r="58" customHeight="1" ht="20">
       <c r="A58" s="5" t="n">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>242</v>
+        <v>642</v>
       </c>
       <c r="C58" s="6" t="n">
-        <v>44809</v>
+        <v>45038</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>44815</v>
+        <v>45041</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>980</v>
+        <v>495</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>690</v>
+        <v>345</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
@@ -2444,32 +2444,36 @@
         <v>17</v>
       </c>
       <c r="N58" s="8" t="n">
-        <v>44620.8319791667</v>
-      </c>
-      <c r="O58" s="7"/>
-      <c r="P58" s="8"/>
+        <v>44952</v>
+      </c>
+      <c r="O58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P58" s="8" t="n">
+        <v>45035.7756018519</v>
+      </c>
     </row>
     <row r="59" customHeight="1" ht="20">
       <c r="A59" s="5" t="n">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>382</v>
+        <v>1022</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>44702</v>
+        <v>45164</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>44703</v>
+        <v>45165</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
@@ -2480,36 +2484,36 @@
         <v>17</v>
       </c>
       <c r="N59" s="8" t="n">
-        <v>44686</v>
+        <v>45157</v>
       </c>
       <c r="O59" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P59" s="8" t="n">
-        <v>44701.8047222222</v>
+        <v>45163.4064814815</v>
       </c>
     </row>
     <row r="60" customHeight="1" ht="20">
       <c r="A60" s="5" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>402</v>
+        <v>1042</v>
       </c>
       <c r="C60" s="6" t="n">
-        <v>44835</v>
+        <v>45199</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>44836</v>
+        <v>45200</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
@@ -2520,27 +2524,27 @@
         <v>17</v>
       </c>
       <c r="N60" s="8" t="n">
-        <v>44732</v>
+        <v>45169</v>
       </c>
       <c r="O60" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P60" s="8" t="n">
-        <v>44834.645</v>
+        <v>45198.5217708333</v>
       </c>
     </row>
     <row r="61" customHeight="1" ht="20">
       <c r="A61" s="5" t="n">
-        <v>121</v>
+        <v>421</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>642</v>
+        <v>1102</v>
       </c>
       <c r="C61" s="6" t="n">
-        <v>45038</v>
+        <v>45232</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>45041</v>
+        <v>45235</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>18</v>
@@ -2560,36 +2564,36 @@
         <v>17</v>
       </c>
       <c r="N61" s="8" t="n">
-        <v>44952</v>
+        <v>45191</v>
       </c>
       <c r="O61" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P61" s="8" t="n">
-        <v>45035.7756018519</v>
+        <v>45223.3995949074</v>
       </c>
     </row>
     <row r="62" customHeight="1" ht="20">
       <c r="A62" s="5" t="n">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>1022</v>
+        <v>1383</v>
       </c>
       <c r="C62" s="6" t="n">
-        <v>45164</v>
+        <v>45431</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>45165</v>
+        <v>45437</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>250</v>
+        <v>1190</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>150</v>
+        <v>870</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
@@ -2600,36 +2604,32 @@
         <v>17</v>
       </c>
       <c r="N62" s="8" t="n">
-        <v>45157</v>
-      </c>
-      <c r="O62" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P62" s="8" t="n">
-        <v>45163.4064814815</v>
-      </c>
+        <v>45335.3893055556</v>
+      </c>
+      <c r="O62" s="7"/>
+      <c r="P62" s="8"/>
     </row>
     <row r="63" customHeight="1" ht="20">
       <c r="A63" s="5" t="n">
-        <v>50</v>
+        <v>561</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>1042</v>
+        <v>1523</v>
       </c>
       <c r="C63" s="6" t="n">
-        <v>45199</v>
+        <v>45655</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>45200</v>
+        <v>45660</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
@@ -2640,36 +2640,36 @@
         <v>17</v>
       </c>
       <c r="N63" s="8" t="n">
-        <v>45169</v>
+        <v>45646</v>
       </c>
       <c r="O63" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P63" s="8" t="n">
-        <v>45198.5217708333</v>
+        <v>45793.6944444444</v>
       </c>
     </row>
     <row r="64" customHeight="1" ht="20">
       <c r="A64" s="5" t="n">
-        <v>421</v>
+        <v>722</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>1102</v>
+        <v>1684</v>
       </c>
       <c r="C64" s="6" t="n">
-        <v>45232</v>
+        <v>46020</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>45235</v>
+        <v>46027</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>495</v>
+        <v>1390</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>345</v>
+        <v>1390</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
@@ -2677,39 +2677,39 @@
       <c r="K64" s="5"/>
       <c r="L64" s="7"/>
       <c r="M64" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N64" s="8" t="n">
-        <v>45191</v>
+        <v>45908</v>
       </c>
       <c r="O64" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P64" s="8" t="n">
-        <v>45223.3995949074</v>
+        <v>46030.6407060185</v>
       </c>
     </row>
     <row r="65" customHeight="1" ht="20">
       <c r="A65" s="5" t="n">
-        <v>25</v>
+        <v>741</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>1383</v>
+        <v>1703</v>
       </c>
       <c r="C65" s="6" t="n">
-        <v>45431</v>
+        <v>45995</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>45437</v>
+        <v>45999</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>1190</v>
+        <v>690</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>870</v>
+        <v>690</v>
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
@@ -2717,73 +2717,75 @@
       <c r="K65" s="5"/>
       <c r="L65" s="7"/>
       <c r="M65" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N65" s="8" t="n">
-        <v>45335.3893055556</v>
-      </c>
-      <c r="O65" s="7"/>
-      <c r="P65" s="8"/>
+        <v>45951</v>
+      </c>
+      <c r="O65" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P65" s="8" t="n">
+        <v>46030.640462963</v>
+      </c>
     </row>
     <row r="66" customHeight="1" ht="20">
       <c r="A66" s="5" t="n">
-        <v>641</v>
+        <v>761</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>1603</v>
+        <v>1723</v>
       </c>
       <c r="C66" s="6" t="n">
-        <v>45795</v>
+        <v>46144</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>45797</v>
+        <v>46149</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>100</v>
+        <v>790</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H66" s="5" t="n">
-        <v>100</v>
-      </c>
+        <v>790</v>
+      </c>
+      <c r="H66" s="5"/>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
       <c r="L66" s="7"/>
       <c r="M66" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N66" s="8" t="n">
-        <v>45761.7557060185</v>
+        <v>45963.3395717593</v>
       </c>
       <c r="O66" s="7"/>
       <c r="P66" s="8"/>
     </row>
     <row r="67" customHeight="1" ht="20">
       <c r="A67" s="5" t="n">
-        <v>561</v>
+        <v>1</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>1523</v>
+        <v>24</v>
       </c>
       <c r="C67" s="6" t="n">
-        <v>45655</v>
+        <v>44324</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>45660</v>
+        <v>44325</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>1</v>
+        <v>230</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
@@ -2794,36 +2796,32 @@
         <v>17</v>
       </c>
       <c r="N67" s="8" t="n">
-        <v>45646</v>
-      </c>
-      <c r="O67" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P67" s="8" t="n">
-        <v>45793.6944444444</v>
-      </c>
+        <v>44420.5177546296</v>
+      </c>
+      <c r="O67" s="7"/>
+      <c r="P67" s="8"/>
     </row>
     <row r="68" customHeight="1" ht="20">
       <c r="A68" s="5" t="n">
-        <v>722</v>
+        <v>22</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>1684</v>
+        <v>25</v>
       </c>
       <c r="C68" s="6" t="n">
-        <v>46020</v>
+        <v>43995</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>46027</v>
+        <v>43996</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>1390</v>
+        <v>230</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>1390</v>
+        <v>130</v>
       </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
@@ -2831,35 +2829,35 @@
       <c r="K68" s="5"/>
       <c r="L68" s="7"/>
       <c r="M68" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N68" s="8" t="n">
-        <v>45908.4608680556</v>
+        <v>44420.5183796296</v>
       </c>
       <c r="O68" s="7"/>
       <c r="P68" s="8"/>
     </row>
     <row r="69" customHeight="1" ht="20">
       <c r="A69" s="5" t="n">
-        <v>741</v>
+        <v>22</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>1703</v>
+        <v>26</v>
       </c>
       <c r="C69" s="6" t="n">
-        <v>45995</v>
+        <v>44121</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>45999</v>
+        <v>44122</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>690</v>
+        <v>230</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>690</v>
+        <v>130</v>
       </c>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
@@ -2867,35 +2865,35 @@
       <c r="K69" s="5"/>
       <c r="L69" s="7"/>
       <c r="M69" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N69" s="8" t="n">
-        <v>45951.6464699074</v>
+        <v>44420.5187268519</v>
       </c>
       <c r="O69" s="7"/>
       <c r="P69" s="8"/>
     </row>
     <row r="70" customHeight="1" ht="20">
       <c r="A70" s="5" t="n">
-        <v>761</v>
+        <v>52</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>1723</v>
+        <v>48</v>
       </c>
       <c r="C70" s="6" t="n">
-        <v>46144</v>
+        <v>44149</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>46149</v>
+        <v>44149</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>790</v>
+        <v>130</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>790</v>
+        <v>30</v>
       </c>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
@@ -2903,35 +2901,35 @@
       <c r="K70" s="5"/>
       <c r="L70" s="7"/>
       <c r="M70" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N70" s="8" t="n">
-        <v>45963.3395717593</v>
+        <v>44446.5248032407</v>
       </c>
       <c r="O70" s="7"/>
       <c r="P70" s="8"/>
     </row>
     <row r="71" customHeight="1" ht="20">
       <c r="A71" s="5" t="n">
-        <v>841</v>
+        <v>49</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>1803</v>
+        <v>55</v>
       </c>
       <c r="C71" s="6" t="n">
-        <v>46252</v>
+        <v>44492</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>46293</v>
+        <v>44492</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>945</v>
+        <v>130</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>945</v>
+        <v>30</v>
       </c>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
@@ -2939,35 +2937,39 @@
       <c r="K71" s="5"/>
       <c r="L71" s="7"/>
       <c r="M71" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N71" s="8" t="n">
-        <v>45987.5723032407</v>
-      </c>
-      <c r="O71" s="7"/>
-      <c r="P71" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O71" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P71" s="8" t="n">
+        <v>44785.5593287037</v>
+      </c>
     </row>
     <row r="72" customHeight="1" ht="20">
       <c r="A72" s="5" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>44324</v>
+        <v>44133</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>44325</v>
+        <v>44136</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>230</v>
+        <v>520</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>130</v>
+        <v>280</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
@@ -2978,32 +2980,36 @@
         <v>17</v>
       </c>
       <c r="N72" s="8" t="n">
-        <v>44420.5177546296</v>
-      </c>
-      <c r="O72" s="7"/>
-      <c r="P72" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P72" s="8" t="n">
+        <v>44847.4125231481</v>
+      </c>
     </row>
     <row r="73" customHeight="1" ht="20">
       <c r="A73" s="5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="C73" s="6" t="n">
-        <v>43995</v>
+        <v>43690</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>43996</v>
+        <v>43697</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>230</v>
+        <v>780</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>130</v>
+        <v>560</v>
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
@@ -3014,32 +3020,32 @@
         <v>17</v>
       </c>
       <c r="N73" s="8" t="n">
-        <v>44420.5183796296</v>
+        <v>44446.5365856481</v>
       </c>
       <c r="O73" s="7"/>
       <c r="P73" s="8"/>
     </row>
     <row r="74" customHeight="1" ht="20">
       <c r="A74" s="5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="C74" s="6" t="n">
-        <v>44121</v>
+        <v>44380</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>44122</v>
+        <v>44386</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>230</v>
+        <v>820</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>130</v>
+        <v>590</v>
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
@@ -3050,32 +3056,32 @@
         <v>17</v>
       </c>
       <c r="N74" s="8" t="n">
-        <v>44420.5187268519</v>
+        <v>44446.5373958333</v>
       </c>
       <c r="O74" s="7"/>
       <c r="P74" s="8"/>
     </row>
     <row r="75" customHeight="1" ht="20">
       <c r="A75" s="5" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C75" s="6" t="n">
-        <v>44149</v>
+        <v>43932</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>44149</v>
+        <v>43938</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>130</v>
+        <v>890</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>30</v>
+        <v>580</v>
       </c>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
@@ -3086,32 +3092,32 @@
         <v>17</v>
       </c>
       <c r="N75" s="8" t="n">
-        <v>44446.5248032407</v>
+        <v>44446.5383217593</v>
       </c>
       <c r="O75" s="7"/>
       <c r="P75" s="8"/>
     </row>
     <row r="76" customHeight="1" ht="20">
       <c r="A76" s="5" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C76" s="6" t="n">
-        <v>44492</v>
+        <v>44380</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>44492</v>
+        <v>44386</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>130</v>
+        <v>890</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>30</v>
+        <v>590</v>
       </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
@@ -3122,36 +3128,32 @@
         <v>17</v>
       </c>
       <c r="N76" s="8" t="n">
-        <v>44446</v>
-      </c>
-      <c r="O76" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P76" s="8" t="n">
-        <v>44785.5593287037</v>
-      </c>
+        <v>44446.5391898148</v>
+      </c>
+      <c r="O76" s="7"/>
+      <c r="P76" s="8"/>
     </row>
     <row r="77" customHeight="1" ht="20">
       <c r="A77" s="5" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>67</v>
+        <v>182</v>
       </c>
       <c r="C77" s="6" t="n">
-        <v>44133</v>
+        <v>44611</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>44136</v>
+        <v>44612</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>520</v>
+        <v>245</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
@@ -3162,36 +3164,36 @@
         <v>17</v>
       </c>
       <c r="N77" s="8" t="n">
-        <v>44446</v>
+        <v>44603</v>
       </c>
       <c r="O77" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P77" s="8" t="n">
-        <v>44847.4125231481</v>
+        <v>44620.6170717593</v>
       </c>
     </row>
     <row r="78" customHeight="1" ht="20">
       <c r="A78" s="5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>72</v>
+        <v>302</v>
       </c>
       <c r="C78" s="6" t="n">
-        <v>43690</v>
+        <v>44786</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>43697</v>
+        <v>44797</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>780</v>
+        <v>1440</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>560</v>
+        <v>990</v>
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
@@ -3202,7 +3204,7 @@
         <v>17</v>
       </c>
       <c r="N78" s="8" t="n">
-        <v>44446.5365856481</v>
+        <v>44655.6645833333</v>
       </c>
       <c r="O78" s="7"/>
       <c r="P78" s="8"/>
@@ -3212,19 +3214,19 @@
         <v>27</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>74</v>
+        <v>363</v>
       </c>
       <c r="C79" s="6" t="n">
-        <v>44380</v>
+        <v>44737</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>44386</v>
+        <v>44743</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>820</v>
+        <v>890</v>
       </c>
       <c r="G79" s="5" t="n">
         <v>590</v>
@@ -3238,34 +3240,40 @@
         <v>17</v>
       </c>
       <c r="N79" s="8" t="n">
-        <v>44446.5373958333</v>
-      </c>
-      <c r="O79" s="7"/>
-      <c r="P79" s="8"/>
+        <v>44679</v>
+      </c>
+      <c r="O79" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P79" s="8" t="n">
+        <v>44745.8054282407</v>
+      </c>
     </row>
     <row r="80" customHeight="1" ht="20">
       <c r="A80" s="5" t="n">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>76</v>
+        <v>462</v>
       </c>
       <c r="C80" s="6" t="n">
-        <v>43932</v>
+        <v>44898</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>43938</v>
+        <v>44907</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>890</v>
+        <v>1600</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>580</v>
-      </c>
-      <c r="H80" s="5"/>
+        <v>1350</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>1550</v>
+      </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
@@ -3274,32 +3282,36 @@
         <v>17</v>
       </c>
       <c r="N80" s="8" t="n">
-        <v>44446.5383217593</v>
-      </c>
-      <c r="O80" s="7"/>
-      <c r="P80" s="8"/>
+        <v>44791</v>
+      </c>
+      <c r="O80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P80" s="8" t="n">
+        <v>44915.6469675926</v>
+      </c>
     </row>
     <row r="81" customHeight="1" ht="20">
       <c r="A81" s="5" t="n">
-        <v>25</v>
+        <v>201</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="C81" s="6" t="n">
-        <v>44380</v>
+        <v>44856</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>44386</v>
+        <v>44857</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>890</v>
+        <v>245</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>590</v>
+        <v>140</v>
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
@@ -3310,32 +3322,36 @@
         <v>17</v>
       </c>
       <c r="N81" s="8" t="n">
-        <v>44446.5391898148</v>
-      </c>
-      <c r="O81" s="7"/>
-      <c r="P81" s="8"/>
+        <v>44834</v>
+      </c>
+      <c r="O81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P81" s="8" t="n">
+        <v>44837.3615972222</v>
+      </c>
     </row>
     <row r="82" customHeight="1" ht="20">
       <c r="A82" s="5" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>182</v>
+        <v>742</v>
       </c>
       <c r="C82" s="6" t="n">
-        <v>44611</v>
+        <v>45010</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>44612</v>
+        <v>45011</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
@@ -3346,13 +3362,13 @@
         <v>17</v>
       </c>
       <c r="N82" s="8" t="n">
-        <v>44603</v>
+        <v>44994</v>
       </c>
       <c r="O82" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P82" s="8" t="n">
-        <v>44620.6170717593</v>
+        <v>45012.3928240741</v>
       </c>
     </row>
     <row r="83" customHeight="1" ht="20">
@@ -3360,22 +3376,22 @@
         <v>23</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>302</v>
+        <v>782</v>
       </c>
       <c r="C83" s="6" t="n">
-        <v>44786</v>
+        <v>45115</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>44797</v>
+        <v>45127</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>1440</v>
+        <v>1490</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
@@ -3386,32 +3402,32 @@
         <v>17</v>
       </c>
       <c r="N83" s="8" t="n">
-        <v>44655.6645833333</v>
+        <v>45013.6681597222</v>
       </c>
       <c r="O83" s="7"/>
       <c r="P83" s="8"/>
     </row>
     <row r="84" customHeight="1" ht="20">
       <c r="A84" s="5" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>363</v>
+        <v>783</v>
       </c>
       <c r="C84" s="6" t="n">
-        <v>44737</v>
+        <v>45101</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>44743</v>
+        <v>45108</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>890</v>
+        <v>1100</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>590</v>
+        <v>710</v>
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
@@ -3422,40 +3438,34 @@
         <v>17</v>
       </c>
       <c r="N84" s="8" t="n">
-        <v>44679</v>
-      </c>
-      <c r="O84" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P84" s="8" t="n">
-        <v>44745.8054282407</v>
-      </c>
+        <v>45013.6687037037</v>
+      </c>
+      <c r="O84" s="7"/>
+      <c r="P84" s="8"/>
     </row>
     <row r="85" customHeight="1" ht="20">
       <c r="A85" s="5" t="n">
-        <v>141</v>
+        <v>26</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>462</v>
+        <v>942</v>
       </c>
       <c r="C85" s="6" t="n">
-        <v>44898</v>
+        <v>45107</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>44907</v>
+        <v>45109</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>1600</v>
+        <v>180</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1350</v>
-      </c>
-      <c r="H85" s="5" t="n">
-        <v>1550</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H85" s="5"/>
       <c r="I85" s="5"/>
       <c r="J85" s="5"/>
       <c r="K85" s="5"/>
@@ -3464,36 +3474,36 @@
         <v>17</v>
       </c>
       <c r="N85" s="8" t="n">
-        <v>44791</v>
+        <v>45080</v>
       </c>
       <c r="O85" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P85" s="8" t="n">
-        <v>44915.6469675926</v>
+        <v>45111.2536921296</v>
       </c>
     </row>
     <row r="86" customHeight="1" ht="20">
       <c r="A86" s="5" t="n">
-        <v>201</v>
+        <v>381</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>522</v>
+        <v>962</v>
       </c>
       <c r="C86" s="6" t="n">
-        <v>44856</v>
+        <v>45110</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>44857</v>
+        <v>45111</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
@@ -3504,36 +3514,36 @@
         <v>17</v>
       </c>
       <c r="N86" s="8" t="n">
-        <v>44834</v>
+        <v>45082</v>
       </c>
       <c r="O86" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P86" s="8" t="n">
-        <v>44837.3615972222</v>
+        <v>45111.2538310185</v>
       </c>
     </row>
     <row r="87" customHeight="1" ht="20">
       <c r="A87" s="5" t="n">
-        <v>101</v>
+        <v>381</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>742</v>
+        <v>1082</v>
       </c>
       <c r="C87" s="6" t="n">
-        <v>45010</v>
+        <v>45177</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>45011</v>
+        <v>45179</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
@@ -3544,36 +3554,36 @@
         <v>17</v>
       </c>
       <c r="N87" s="8" t="n">
-        <v>44994</v>
+        <v>45173</v>
       </c>
       <c r="O87" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P87" s="8" t="n">
-        <v>45012.3928240741</v>
+        <v>45173.6145601852</v>
       </c>
     </row>
     <row r="88" customHeight="1" ht="20">
       <c r="A88" s="5" t="n">
-        <v>23</v>
+        <v>301</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>782</v>
+        <v>1122</v>
       </c>
       <c r="C88" s="6" t="n">
-        <v>45115</v>
+        <v>45268</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>45127</v>
+        <v>45270</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>1490</v>
+        <v>370</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>995</v>
+        <v>145</v>
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
@@ -3584,32 +3594,36 @@
         <v>17</v>
       </c>
       <c r="N88" s="8" t="n">
-        <v>45013.6681597222</v>
-      </c>
-      <c r="O88" s="7"/>
-      <c r="P88" s="8"/>
+        <v>45205</v>
+      </c>
+      <c r="O88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P88" s="8" t="n">
+        <v>45267.4084143519</v>
+      </c>
     </row>
     <row r="89" customHeight="1" ht="20">
       <c r="A89" s="5" t="n">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>783</v>
+        <v>1162</v>
       </c>
       <c r="C89" s="6" t="n">
-        <v>45101</v>
+        <v>45318</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>45108</v>
+        <v>45319</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>1100</v>
+        <v>250</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>710</v>
+        <v>150</v>
       </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
@@ -3620,32 +3634,36 @@
         <v>17</v>
       </c>
       <c r="N89" s="8" t="n">
-        <v>45013.6687037037</v>
-      </c>
-      <c r="O89" s="7"/>
-      <c r="P89" s="8"/>
+        <v>45274</v>
+      </c>
+      <c r="O89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P89" s="8" t="n">
+        <v>45320.4609837963</v>
+      </c>
     </row>
     <row r="90" customHeight="1" ht="20">
       <c r="A90" s="5" t="n">
-        <v>26</v>
+        <v>441</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>942</v>
+        <v>1182</v>
       </c>
       <c r="C90" s="6" t="n">
-        <v>45107</v>
+        <v>45290</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>45109</v>
+        <v>45295</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>180</v>
+        <v>860</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>100</v>
+        <v>660</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
@@ -3656,36 +3674,36 @@
         <v>17</v>
       </c>
       <c r="N90" s="8" t="n">
-        <v>45080</v>
+        <v>45277</v>
       </c>
       <c r="O90" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P90" s="8" t="n">
-        <v>45111.2536921296</v>
+        <v>45285.4578009259</v>
       </c>
     </row>
     <row r="91" customHeight="1" ht="20">
       <c r="A91" s="5" t="n">
-        <v>381</v>
+        <v>261</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>962</v>
+        <v>1202</v>
       </c>
       <c r="C91" s="6" t="n">
-        <v>45110</v>
+        <v>45366</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>45111</v>
+        <v>45368</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>250</v>
+        <v>385</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
@@ -3696,36 +3714,36 @@
         <v>17</v>
       </c>
       <c r="N91" s="8" t="n">
-        <v>45082</v>
+        <v>45280</v>
       </c>
       <c r="O91" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P91" s="8" t="n">
-        <v>45111.2538310185</v>
+        <v>45419.522962963</v>
       </c>
     </row>
     <row r="92" customHeight="1" ht="20">
       <c r="A92" s="5" t="n">
-        <v>381</v>
+        <v>181</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>1082</v>
+        <v>1262</v>
       </c>
       <c r="C92" s="6" t="n">
-        <v>45177</v>
+        <v>45339</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>45179</v>
+        <v>45340</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
@@ -3736,36 +3754,36 @@
         <v>17</v>
       </c>
       <c r="N92" s="8" t="n">
-        <v>45173</v>
+        <v>45303</v>
       </c>
       <c r="O92" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P92" s="8" t="n">
-        <v>45173.6145601852</v>
+        <v>45343.4145486111</v>
       </c>
     </row>
     <row r="93" customHeight="1" ht="20">
       <c r="A93" s="5" t="n">
-        <v>301</v>
+        <v>27</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>1122</v>
+        <v>1342</v>
       </c>
       <c r="C93" s="6" t="n">
-        <v>45268</v>
+        <v>45444</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>45270</v>
+        <v>45451</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>370</v>
+        <v>940</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>145</v>
+        <v>590</v>
       </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
@@ -3776,36 +3794,32 @@
         <v>17</v>
       </c>
       <c r="N93" s="8" t="n">
-        <v>45205</v>
-      </c>
-      <c r="O93" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P93" s="8" t="n">
-        <v>45267.4084143519</v>
-      </c>
+        <v>45313.4136458333</v>
+      </c>
+      <c r="O93" s="7"/>
+      <c r="P93" s="8"/>
     </row>
     <row r="94" customHeight="1" ht="20">
       <c r="A94" s="5" t="n">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>1162</v>
+        <v>1403</v>
       </c>
       <c r="C94" s="6" t="n">
-        <v>45318</v>
+        <v>45451</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>45319</v>
+        <v>45459</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>250</v>
+        <v>990</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>150</v>
+        <v>690</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
@@ -3816,36 +3830,32 @@
         <v>17</v>
       </c>
       <c r="N94" s="8" t="n">
-        <v>45274</v>
-      </c>
-      <c r="O94" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P94" s="8" t="n">
-        <v>45320.4609837963</v>
-      </c>
+        <v>45348.3647453704</v>
+      </c>
+      <c r="O94" s="7"/>
+      <c r="P94" s="8"/>
     </row>
     <row r="95" customHeight="1" ht="20">
       <c r="A95" s="5" t="n">
-        <v>441</v>
+        <v>321</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>1182</v>
+        <v>1444</v>
       </c>
       <c r="C95" s="6" t="n">
-        <v>45290</v>
+        <v>45464</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>45295</v>
+        <v>45478</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>860</v>
+        <v>1650</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>660</v>
+        <v>1100</v>
       </c>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
@@ -3856,36 +3866,32 @@
         <v>17</v>
       </c>
       <c r="N95" s="8" t="n">
-        <v>45277</v>
-      </c>
-      <c r="O95" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P95" s="8" t="n">
-        <v>45285.4578009259</v>
-      </c>
+        <v>45405.5582175926</v>
+      </c>
+      <c r="O95" s="7"/>
+      <c r="P95" s="8"/>
     </row>
     <row r="96" customHeight="1" ht="20">
       <c r="A96" s="5" t="n">
-        <v>261</v>
+        <v>622</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>1202</v>
+        <v>1583</v>
       </c>
       <c r="C96" s="6" t="n">
-        <v>45366</v>
+        <v>45767</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>45368</v>
+        <v>45772</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>385</v>
+        <v>790</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>240</v>
+        <v>790</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
@@ -3893,39 +3899,39 @@
       <c r="K96" s="5"/>
       <c r="L96" s="7"/>
       <c r="M96" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N96" s="8" t="n">
-        <v>45280</v>
+        <v>45700</v>
       </c>
       <c r="O96" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P96" s="8" t="n">
-        <v>45419.522962963</v>
+        <v>45793.6939930556</v>
       </c>
     </row>
     <row r="97" customHeight="1" ht="20">
       <c r="A97" s="5" t="n">
-        <v>181</v>
+        <v>861</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>1262</v>
+        <v>1823</v>
       </c>
       <c r="C97" s="6" t="n">
-        <v>45339</v>
+        <v>46122</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>45340</v>
+        <v>46132</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>250</v>
+        <v>2290</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>150</v>
+        <v>2290</v>
       </c>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
@@ -3933,39 +3939,35 @@
       <c r="K97" s="5"/>
       <c r="L97" s="7"/>
       <c r="M97" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N97" s="8" t="n">
-        <v>45303</v>
-      </c>
-      <c r="O97" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P97" s="8" t="n">
-        <v>45343.4145486111</v>
-      </c>
+        <v>46031.3055439815</v>
+      </c>
+      <c r="O97" s="7"/>
+      <c r="P97" s="8"/>
     </row>
     <row r="98" customHeight="1" ht="20">
       <c r="A98" s="5" t="n">
-        <v>27</v>
+        <v>681</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>1342</v>
+        <v>1647</v>
       </c>
       <c r="C98" s="6" t="n">
-        <v>45444</v>
+        <v>46138</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>45451</v>
+        <v>46144</v>
       </c>
       <c r="E98" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>940</v>
+        <v>1160</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>590</v>
+        <v>1160</v>
       </c>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
@@ -3973,35 +3975,39 @@
       <c r="K98" s="5"/>
       <c r="L98" s="7"/>
       <c r="M98" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N98" s="8" t="n">
-        <v>45313.4136458333</v>
-      </c>
-      <c r="O98" s="7"/>
-      <c r="P98" s="8"/>
+        <v>45793</v>
+      </c>
+      <c r="O98" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="P98" s="8" t="n">
+        <v>45958.4886226852</v>
+      </c>
     </row>
     <row r="99" customHeight="1" ht="20">
       <c r="A99" s="5" t="n">
-        <v>41</v>
+        <v>762</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>1403</v>
+        <v>1724</v>
       </c>
       <c r="C99" s="6" t="n">
-        <v>45451</v>
+        <v>46021</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>45459</v>
+        <v>46026</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F99" s="5" t="n">
         <v>990</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>690</v>
+        <v>990</v>
       </c>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
@@ -4009,35 +4015,39 @@
       <c r="K99" s="5"/>
       <c r="L99" s="7"/>
       <c r="M99" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N99" s="8" t="n">
-        <v>45348.3647453704</v>
-      </c>
-      <c r="O99" s="7"/>
-      <c r="P99" s="8"/>
+        <v>45963</v>
+      </c>
+      <c r="O99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P99" s="8" t="n">
+        <v>46030.6411574074</v>
+      </c>
     </row>
     <row r="100" customHeight="1" ht="20">
       <c r="A100" s="5" t="n">
-        <v>321</v>
+        <v>621</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>1444</v>
+        <v>1683</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>45464</v>
+        <v>45950</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>45478</v>
+        <v>45955</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>1650</v>
+        <v>990</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>1100</v>
+        <v>990</v>
       </c>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
@@ -4045,35 +4055,39 @@
       <c r="K100" s="5"/>
       <c r="L100" s="7"/>
       <c r="M100" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N100" s="8" t="n">
-        <v>45405.5582175926</v>
-      </c>
-      <c r="O100" s="7"/>
-      <c r="P100" s="8"/>
+        <v>45908</v>
+      </c>
+      <c r="O100" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="P100" s="8" t="n">
+        <v>45951.6467939815</v>
+      </c>
     </row>
     <row r="101" customHeight="1" ht="20">
       <c r="A101" s="5" t="n">
-        <v>622</v>
+        <v>781</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>1583</v>
+        <v>1743</v>
       </c>
       <c r="C101" s="6" t="n">
-        <v>45767</v>
+        <v>46020</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>45772</v>
+        <v>46025</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>790</v>
+        <v>1</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>790</v>
+        <v>1</v>
       </c>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
@@ -4084,36 +4098,36 @@
         <v>19</v>
       </c>
       <c r="N101" s="8" t="n">
-        <v>45700</v>
+        <v>45964</v>
       </c>
       <c r="O101" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P101" s="8" t="n">
-        <v>45793.6939930556</v>
+        <v>46030.6409490741</v>
       </c>
     </row>
     <row r="102" customHeight="1" ht="20">
       <c r="A102" s="5" t="n">
-        <v>625</v>
+        <v>801</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>1586</v>
+        <v>1763</v>
       </c>
       <c r="C102" s="6" t="n">
-        <v>45782</v>
+        <v>46137</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>45786</v>
+        <v>46143</v>
       </c>
       <c r="E102" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>490</v>
+        <v>1000</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>490</v>
+        <v>1000</v>
       </c>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
@@ -4124,32 +4138,32 @@
         <v>19</v>
       </c>
       <c r="N102" s="8" t="n">
-        <v>45700.9462268519</v>
+        <v>45981.7479166667</v>
       </c>
       <c r="O102" s="7"/>
       <c r="P102" s="8"/>
     </row>
     <row r="103" customHeight="1" ht="20">
       <c r="A103" s="5" t="n">
-        <v>681</v>
+        <v>1</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>1647</v>
+        <v>1</v>
       </c>
       <c r="C103" s="6" t="n">
-        <v>46138</v>
+        <v>43505</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>46144</v>
+        <v>43506</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>1160</v>
+        <v>230</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1160</v>
+        <v>130</v>
       </c>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
@@ -4157,39 +4171,39 @@
       <c r="K103" s="5"/>
       <c r="L103" s="7"/>
       <c r="M103" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N103" s="8" t="n">
-        <v>45793</v>
+        <v>44420</v>
       </c>
       <c r="O103" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P103" s="8" t="n">
-        <v>45958.4886226852</v>
+        <v>44853.7957060185</v>
       </c>
     </row>
     <row r="104" customHeight="1" ht="20">
       <c r="A104" s="5" t="n">
-        <v>762</v>
+        <v>54</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>1724</v>
+        <v>42</v>
       </c>
       <c r="C104" s="6" t="n">
-        <v>46021</v>
+        <v>44345</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>46026</v>
+        <v>44346</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>990</v>
+        <v>230</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>990</v>
+        <v>130</v>
       </c>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
@@ -4197,35 +4211,35 @@
       <c r="K104" s="5"/>
       <c r="L104" s="7"/>
       <c r="M104" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N104" s="8" t="n">
-        <v>45963.3434259259</v>
+        <v>44445.5079513889</v>
       </c>
       <c r="O104" s="7"/>
       <c r="P104" s="8"/>
     </row>
     <row r="105" customHeight="1" ht="20">
       <c r="A105" s="5" t="n">
-        <v>621</v>
+        <v>54</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>1683</v>
+        <v>43</v>
       </c>
       <c r="C105" s="6" t="n">
-        <v>45950</v>
+        <v>44464</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>45955</v>
+        <v>44465</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>990</v>
+        <v>230</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>990</v>
+        <v>130</v>
       </c>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
@@ -4233,39 +4247,39 @@
       <c r="K105" s="5"/>
       <c r="L105" s="7"/>
       <c r="M105" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N105" s="8" t="n">
-        <v>45908</v>
+        <v>44445</v>
       </c>
       <c r="O105" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P105" s="8" t="n">
-        <v>45951.6467939815</v>
+        <v>44764.5626388889</v>
       </c>
     </row>
     <row r="106" customHeight="1" ht="20">
       <c r="A106" s="5" t="n">
-        <v>781</v>
+        <v>55</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>1743</v>
+        <v>44</v>
       </c>
       <c r="C106" s="6" t="n">
-        <v>46020</v>
+        <v>44474</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>46025</v>
+        <v>44475</v>
       </c>
       <c r="E106" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>1</v>
+        <v>230</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
@@ -4273,39 +4287,39 @@
       <c r="K106" s="5"/>
       <c r="L106" s="7"/>
       <c r="M106" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N106" s="8" t="n">
-        <v>45964</v>
+        <v>44446.2805902778</v>
       </c>
       <c r="O106" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P106" s="8" t="n">
-        <v>45965.3531481481</v>
+        <v>44586.645775463</v>
       </c>
     </row>
     <row r="107" customHeight="1" ht="20">
       <c r="A107" s="5" t="n">
-        <v>801</v>
+        <v>53</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>1763</v>
+        <v>45</v>
       </c>
       <c r="C107" s="6" t="n">
-        <v>46137</v>
+        <v>43603</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>46143</v>
+        <v>43604</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
@@ -4313,23 +4327,27 @@
       <c r="K107" s="5"/>
       <c r="L107" s="7"/>
       <c r="M107" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N107" s="8" t="n">
-        <v>45981.7479166667</v>
-      </c>
-      <c r="O107" s="7"/>
-      <c r="P107" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O107" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P107" s="8" t="n">
+        <v>44764.6144791667</v>
+      </c>
     </row>
     <row r="108" customHeight="1" ht="20">
       <c r="A108" s="5" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C108" s="6" t="n">
-        <v>43505</v>
+        <v>43506</v>
       </c>
       <c r="D108" s="6" t="n">
         <v>43506</v>
@@ -4338,10 +4356,10 @@
         <v>18</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
@@ -4352,36 +4370,36 @@
         <v>17</v>
       </c>
       <c r="N108" s="8" t="n">
-        <v>44420</v>
+        <v>44446</v>
       </c>
       <c r="O108" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P108" s="8" t="n">
-        <v>44853.7957060185</v>
+        <v>44767.5292824074</v>
       </c>
     </row>
     <row r="109" customHeight="1" ht="20">
       <c r="A109" s="5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C109" s="6" t="n">
-        <v>44345</v>
+        <v>43877</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>44346</v>
+        <v>43877</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
@@ -4392,32 +4410,36 @@
         <v>17</v>
       </c>
       <c r="N109" s="8" t="n">
-        <v>44445.5079513889</v>
-      </c>
-      <c r="O109" s="7"/>
-      <c r="P109" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O109" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P109" s="8" t="n">
+        <v>44767.5397337963</v>
+      </c>
     </row>
     <row r="110" customHeight="1" ht="20">
       <c r="A110" s="5" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C110" s="6" t="n">
-        <v>44464</v>
+        <v>44170</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>44465</v>
+        <v>44173</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>230</v>
+        <v>495</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>130</v>
+        <v>310</v>
       </c>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
@@ -4428,30 +4450,26 @@
         <v>17</v>
       </c>
       <c r="N110" s="8" t="n">
-        <v>44445</v>
-      </c>
-      <c r="O110" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P110" s="8" t="n">
-        <v>44764.5626388889</v>
-      </c>
+        <v>44446.5258333333</v>
+      </c>
+      <c r="O110" s="7"/>
+      <c r="P110" s="8"/>
     </row>
     <row r="111" customHeight="1" ht="20">
       <c r="A111" s="5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C111" s="6" t="n">
-        <v>44474</v>
+        <v>44331</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>44475</v>
+        <v>44332</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F111" s="5" t="n">
         <v>230</v>
@@ -4468,36 +4486,36 @@
         <v>17</v>
       </c>
       <c r="N111" s="8" t="n">
-        <v>44446.2805902778</v>
+        <v>44446</v>
       </c>
       <c r="O111" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P111" s="8" t="n">
-        <v>44586.645775463</v>
+        <v>44785.5036921296</v>
       </c>
     </row>
     <row r="112" customHeight="1" ht="20">
       <c r="A112" s="5" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C112" s="6" t="n">
-        <v>43603</v>
+        <v>43554</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>43604</v>
+        <v>43554</v>
       </c>
       <c r="E112" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
@@ -4514,30 +4532,30 @@
         <v>17</v>
       </c>
       <c r="P112" s="8" t="n">
-        <v>44764.6144791667</v>
+        <v>44785.5278240741</v>
       </c>
     </row>
     <row r="113" customHeight="1" ht="20">
       <c r="A113" s="5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C113" s="6" t="n">
-        <v>43506</v>
+        <v>43764</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>43506</v>
+        <v>43765</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F113" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="G113" s="5" t="n">
         <v>130</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
@@ -4554,30 +4572,30 @@
         <v>17</v>
       </c>
       <c r="P113" s="8" t="n">
-        <v>44767.5292824074</v>
+        <v>44785.5824074074</v>
       </c>
     </row>
     <row r="114" customHeight="1" ht="20">
       <c r="A114" s="5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C114" s="6" t="n">
-        <v>43877</v>
+        <v>43862</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>43877</v>
+        <v>43863</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F114" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="G114" s="5" t="n">
         <v>130</v>
-      </c>
-      <c r="G114" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
@@ -4594,30 +4612,30 @@
         <v>17</v>
       </c>
       <c r="P114" s="8" t="n">
-        <v>44767.5397337963</v>
+        <v>44785.5965856481</v>
       </c>
     </row>
     <row r="115" customHeight="1" ht="20">
       <c r="A115" s="5" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C115" s="6" t="n">
-        <v>44170</v>
+        <v>44009</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>44173</v>
+        <v>44010</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>495</v>
+        <v>230</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>310</v>
+        <v>130</v>
       </c>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
@@ -4628,23 +4646,27 @@
         <v>17</v>
       </c>
       <c r="N115" s="8" t="n">
-        <v>44446.5258333333</v>
-      </c>
-      <c r="O115" s="7"/>
-      <c r="P115" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O115" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P115" s="8" t="n">
+        <v>44785.6159259259</v>
+      </c>
     </row>
     <row r="116" customHeight="1" ht="20">
       <c r="A116" s="5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C116" s="6" t="n">
-        <v>44331</v>
+        <v>44100</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>44332</v>
+        <v>44101</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>18</v>
@@ -4670,30 +4692,30 @@
         <v>17</v>
       </c>
       <c r="P116" s="8" t="n">
-        <v>44785.5036921296</v>
+        <v>44792.5683217593</v>
       </c>
     </row>
     <row r="117" customHeight="1" ht="20">
       <c r="A117" s="5" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C117" s="6" t="n">
-        <v>43554</v>
+        <v>44338</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>43554</v>
+        <v>44339</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F117" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="G117" s="5" t="n">
         <v>130</v>
-      </c>
-      <c r="G117" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
@@ -4710,21 +4732,21 @@
         <v>17</v>
       </c>
       <c r="P117" s="8" t="n">
-        <v>44785.5278240741</v>
+        <v>44792.5857291667</v>
       </c>
     </row>
     <row r="118" customHeight="1" ht="20">
       <c r="A118" s="5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C118" s="6" t="n">
-        <v>43764</v>
+        <v>44107</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>43765</v>
+        <v>44108</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>18</v>
@@ -4750,21 +4772,21 @@
         <v>17</v>
       </c>
       <c r="P118" s="8" t="n">
-        <v>44785.5824074074</v>
+        <v>44819.4365393519</v>
       </c>
     </row>
     <row r="119" customHeight="1" ht="20">
       <c r="A119" s="5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C119" s="6" t="n">
-        <v>43862</v>
+        <v>44401</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>43863</v>
+        <v>44402</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>18</v>
@@ -4790,30 +4812,30 @@
         <v>17</v>
       </c>
       <c r="P119" s="8" t="n">
-        <v>44785.5965856481</v>
+        <v>44819.4539351852</v>
       </c>
     </row>
     <row r="120" customHeight="1" ht="20">
       <c r="A120" s="5" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C120" s="6" t="n">
-        <v>44009</v>
+        <v>43769</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>44010</v>
+        <v>43772</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>230</v>
+        <v>495</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>130</v>
+        <v>245</v>
       </c>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
@@ -4830,30 +4852,30 @@
         <v>17</v>
       </c>
       <c r="P120" s="8" t="n">
-        <v>44785.6159259259</v>
+        <v>44819.5838773148</v>
       </c>
     </row>
     <row r="121" customHeight="1" ht="20">
       <c r="A121" s="5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C121" s="6" t="n">
-        <v>44100</v>
+        <v>44498</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>44101</v>
+        <v>44501</v>
       </c>
       <c r="E121" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>230</v>
+        <v>495</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>130</v>
+        <v>310</v>
       </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
@@ -4870,30 +4892,30 @@
         <v>17</v>
       </c>
       <c r="P121" s="8" t="n">
-        <v>44792.5683217593</v>
+        <v>44837.6617939815</v>
       </c>
     </row>
     <row r="122" customHeight="1" ht="20">
       <c r="A122" s="5" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>44338</v>
+        <v>43981</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>44339</v>
+        <v>43989</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>230</v>
+        <v>1050</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
@@ -4904,36 +4926,32 @@
         <v>17</v>
       </c>
       <c r="N122" s="8" t="n">
-        <v>44446</v>
-      </c>
-      <c r="O122" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P122" s="8" t="n">
-        <v>44792.5857291667</v>
-      </c>
+        <v>44446.5351157407</v>
+      </c>
+      <c r="O122" s="7"/>
+      <c r="P122" s="8"/>
     </row>
     <row r="123" customHeight="1" ht="20">
       <c r="A123" s="5" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C123" s="6" t="n">
-        <v>44107</v>
+        <v>44450</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>44108</v>
+        <v>44457</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>230</v>
+        <v>970</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>130</v>
+        <v>690</v>
       </c>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
@@ -4944,36 +4962,32 @@
         <v>17</v>
       </c>
       <c r="N123" s="8" t="n">
-        <v>44446</v>
-      </c>
-      <c r="O123" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P123" s="8" t="n">
-        <v>44819.4365393519</v>
-      </c>
+        <v>44446.5361226852</v>
+      </c>
+      <c r="O123" s="7"/>
+      <c r="P123" s="8"/>
     </row>
     <row r="124" customHeight="1" ht="20">
       <c r="A124" s="5" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C124" s="6" t="n">
-        <v>44401</v>
+        <v>44023</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>44402</v>
+        <v>44029</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>230</v>
+        <v>790</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>130</v>
+        <v>570</v>
       </c>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
@@ -4984,36 +4998,32 @@
         <v>17</v>
       </c>
       <c r="N124" s="8" t="n">
-        <v>44446</v>
-      </c>
-      <c r="O124" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P124" s="8" t="n">
-        <v>44819.4539351852</v>
-      </c>
+        <v>44446.5370138889</v>
+      </c>
+      <c r="O124" s="7"/>
+      <c r="P124" s="8"/>
     </row>
     <row r="125" customHeight="1" ht="20">
       <c r="A125" s="5" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C125" s="6" t="n">
-        <v>43769</v>
+        <v>43575</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>43772</v>
+        <v>43581</v>
       </c>
       <c r="E125" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>495</v>
+        <v>860</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>245</v>
+        <v>550</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
@@ -5024,36 +5034,32 @@
         <v>17</v>
       </c>
       <c r="N125" s="8" t="n">
-        <v>44446</v>
-      </c>
-      <c r="O125" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P125" s="8" t="n">
-        <v>44819.5838773148</v>
-      </c>
+        <v>44446.5379398148</v>
+      </c>
+      <c r="O125" s="7"/>
+      <c r="P125" s="8"/>
     </row>
     <row r="126" customHeight="1" ht="20">
       <c r="A126" s="5" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C126" s="6" t="n">
-        <v>44498</v>
+        <v>44284</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>44501</v>
+        <v>44290</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>495</v>
+        <v>890</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>310</v>
+        <v>590</v>
       </c>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
@@ -5064,36 +5070,32 @@
         <v>17</v>
       </c>
       <c r="N126" s="8" t="n">
-        <v>44446</v>
-      </c>
-      <c r="O126" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P126" s="8" t="n">
-        <v>44837.6617939815</v>
-      </c>
+        <v>44446.5387268519</v>
+      </c>
+      <c r="O126" s="7"/>
+      <c r="P126" s="8"/>
     </row>
     <row r="127" customHeight="1" ht="20">
       <c r="A127" s="5" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C127" s="6" t="n">
-        <v>43981</v>
+        <v>44665</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>43989</v>
+        <v>44671</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>1050</v>
+        <v>1150</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>580</v>
+        <v>770</v>
       </c>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
@@ -5104,32 +5106,36 @@
         <v>17</v>
       </c>
       <c r="N127" s="8" t="n">
-        <v>44446.5351157407</v>
-      </c>
-      <c r="O127" s="7"/>
-      <c r="P127" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O127" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P127" s="8" t="n">
+        <v>44676.391724537</v>
+      </c>
     </row>
     <row r="128" customHeight="1" ht="20">
       <c r="A128" s="5" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>71</v>
+        <v>263</v>
       </c>
       <c r="C128" s="6" t="n">
-        <v>44450</v>
+        <v>44653</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>44457</v>
+        <v>44653</v>
       </c>
       <c r="E128" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>970</v>
+        <v>130</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>690</v>
+        <v>30</v>
       </c>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
@@ -5140,32 +5146,32 @@
         <v>17</v>
       </c>
       <c r="N128" s="8" t="n">
-        <v>44446.5361226852</v>
+        <v>44646.3677199074</v>
       </c>
       <c r="O128" s="7"/>
       <c r="P128" s="8"/>
     </row>
     <row r="129" customHeight="1" ht="20">
       <c r="A129" s="5" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C129" s="6" t="n">
-        <v>44023</v>
+        <v>44359</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>44029</v>
+        <v>44360</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>790</v>
+        <v>230</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>570</v>
+        <v>130</v>
       </c>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
@@ -5176,68 +5182,74 @@
         <v>17</v>
       </c>
       <c r="N129" s="8" t="n">
-        <v>44446.5370138889</v>
+        <v>44446.542337963</v>
       </c>
       <c r="O129" s="7"/>
       <c r="P129" s="8"/>
     </row>
     <row r="130" customHeight="1" ht="20">
       <c r="A130" s="5" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C130" s="6" t="n">
-        <v>43575</v>
+        <v>44450</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>43581</v>
+        <v>44453</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>860</v>
+        <v>830</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
       <c r="K130" s="5"/>
-      <c r="L130" s="7"/>
+      <c r="L130" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="M130" s="7" t="s">
         <v>17</v>
       </c>
       <c r="N130" s="8" t="n">
-        <v>44446.5379398148</v>
-      </c>
-      <c r="O130" s="7"/>
-      <c r="P130" s="8"/>
+        <v>44447</v>
+      </c>
+      <c r="O130" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P130" s="8" t="n">
+        <v>44837.6220949074</v>
+      </c>
     </row>
     <row r="131" customHeight="1" ht="20">
       <c r="A131" s="5" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>77</v>
+        <v>342</v>
       </c>
       <c r="C131" s="6" t="n">
-        <v>44284</v>
+        <v>44723</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>44290</v>
+        <v>44724</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>890</v>
+        <v>245</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>590</v>
+        <v>140</v>
       </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
@@ -5248,32 +5260,36 @@
         <v>17</v>
       </c>
       <c r="N131" s="8" t="n">
-        <v>44446.5387268519</v>
-      </c>
-      <c r="O131" s="7"/>
-      <c r="P131" s="8"/>
+        <v>44665</v>
+      </c>
+      <c r="O131" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P131" s="8" t="n">
+        <v>44731.4374652778</v>
+      </c>
     </row>
     <row r="132" customHeight="1" ht="20">
       <c r="A132" s="5" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>79</v>
+        <v>422</v>
       </c>
       <c r="C132" s="6" t="n">
-        <v>44665</v>
+        <v>44828</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>44671</v>
+        <v>44829</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>1150</v>
+        <v>245</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>770</v>
+        <v>140</v>
       </c>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
@@ -5284,36 +5300,36 @@
         <v>17</v>
       </c>
       <c r="N132" s="8" t="n">
-        <v>44446</v>
+        <v>44748</v>
       </c>
       <c r="O132" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P132" s="8" t="n">
-        <v>44676.391724537</v>
+        <v>44830.3892361111</v>
       </c>
     </row>
     <row r="133" customHeight="1" ht="20">
       <c r="A133" s="5" t="n">
-        <v>52</v>
+        <v>181</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>263</v>
+        <v>502</v>
       </c>
       <c r="C133" s="6" t="n">
-        <v>44653</v>
+        <v>44849</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>44653</v>
+        <v>44850</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>130</v>
+        <v>245</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
@@ -5324,32 +5340,36 @@
         <v>17</v>
       </c>
       <c r="N133" s="8" t="n">
-        <v>44646.3677199074</v>
-      </c>
-      <c r="O133" s="7"/>
-      <c r="P133" s="8"/>
+        <v>44810</v>
+      </c>
+      <c r="O133" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P133" s="8" t="n">
+        <v>44847.397962963</v>
+      </c>
     </row>
     <row r="134" customHeight="1" ht="20">
       <c r="A134" s="5" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>84</v>
+        <v>682</v>
       </c>
       <c r="C134" s="6" t="n">
-        <v>44359</v>
+        <v>44989</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>44360</v>
+        <v>44990</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
@@ -5360,74 +5380,76 @@
         <v>17</v>
       </c>
       <c r="N134" s="8" t="n">
-        <v>44446.542337963</v>
-      </c>
-      <c r="O134" s="7"/>
-      <c r="P134" s="8"/>
+        <v>44970</v>
+      </c>
+      <c r="O134" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P134" s="8" t="n">
+        <v>44988.7055555556</v>
+      </c>
     </row>
     <row r="135" customHeight="1" ht="20">
       <c r="A135" s="5" t="n">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>85</v>
+        <v>702</v>
       </c>
       <c r="C135" s="6" t="n">
-        <v>44450</v>
+        <v>44996</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>44453</v>
+        <v>44997</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>830</v>
+        <v>250</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
       <c r="K135" s="5"/>
-      <c r="L135" s="7" t="s">
-        <v>21</v>
-      </c>
+      <c r="L135" s="7"/>
       <c r="M135" s="7" t="s">
         <v>17</v>
       </c>
       <c r="N135" s="8" t="n">
-        <v>44447</v>
+        <v>44986</v>
       </c>
       <c r="O135" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P135" s="8" t="n">
-        <v>44837.6220949074</v>
+        <v>44998.346400463</v>
       </c>
     </row>
     <row r="136" customHeight="1" ht="20">
       <c r="A136" s="5" t="n">
-        <v>54</v>
+        <v>281</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>342</v>
+        <v>822</v>
       </c>
       <c r="C136" s="6" t="n">
-        <v>44723</v>
+        <v>45227</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>44724</v>
+        <v>45230</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>245</v>
+        <v>540</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>140</v>
+        <v>345</v>
       </c>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
@@ -5438,36 +5460,36 @@
         <v>17</v>
       </c>
       <c r="N136" s="8" t="n">
-        <v>44665</v>
+        <v>45032</v>
       </c>
       <c r="O136" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P136" s="8" t="n">
-        <v>44731.4374652778</v>
+        <v>45231.536724537</v>
       </c>
     </row>
     <row r="137" customHeight="1" ht="20">
       <c r="A137" s="5" t="n">
-        <v>48</v>
+        <v>361</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>422</v>
+        <v>902</v>
       </c>
       <c r="C137" s="6" t="n">
-        <v>44828</v>
+        <v>45074</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>44829</v>
+        <v>45078</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>245</v>
+        <v>695</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>140</v>
+        <v>495</v>
       </c>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
@@ -5478,36 +5500,36 @@
         <v>17</v>
       </c>
       <c r="N137" s="8" t="n">
-        <v>44748</v>
+        <v>45069</v>
       </c>
       <c r="O137" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P137" s="8" t="n">
-        <v>44830.3892361111</v>
+        <v>45071.3412962963</v>
       </c>
     </row>
     <row r="138" customHeight="1" ht="20">
       <c r="A138" s="5" t="n">
-        <v>181</v>
+        <v>401</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>502</v>
+        <v>982</v>
       </c>
       <c r="C138" s="6" t="n">
-        <v>44849</v>
+        <v>45129</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>44850</v>
+        <v>45132</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>245</v>
+        <v>670</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>140</v>
+        <v>380</v>
       </c>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
@@ -5518,36 +5540,32 @@
         <v>17</v>
       </c>
       <c r="N138" s="8" t="n">
-        <v>44810</v>
-      </c>
-      <c r="O138" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P138" s="8" t="n">
-        <v>44847.397962963</v>
-      </c>
+        <v>45111.2535763889</v>
+      </c>
+      <c r="O138" s="7"/>
+      <c r="P138" s="8"/>
     </row>
     <row r="139" customHeight="1" ht="20">
       <c r="A139" s="5" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>682</v>
+        <v>1062</v>
       </c>
       <c r="C139" s="6" t="n">
-        <v>44989</v>
+        <v>45206</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>44990</v>
+        <v>45214</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>250</v>
+        <v>1100</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>150</v>
+        <v>710</v>
       </c>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
@@ -5558,27 +5576,23 @@
         <v>17</v>
       </c>
       <c r="N139" s="8" t="n">
-        <v>44970</v>
-      </c>
-      <c r="O139" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P139" s="8" t="n">
-        <v>44988.7055555556</v>
-      </c>
+        <v>45171.606875</v>
+      </c>
+      <c r="O139" s="7"/>
+      <c r="P139" s="8"/>
     </row>
     <row r="140" customHeight="1" ht="20">
       <c r="A140" s="5" t="n">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>702</v>
+        <v>1302</v>
       </c>
       <c r="C140" s="6" t="n">
-        <v>44996</v>
+        <v>45346</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>44997</v>
+        <v>45347</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>18</v>
@@ -5598,36 +5612,36 @@
         <v>17</v>
       </c>
       <c r="N140" s="8" t="n">
-        <v>44986</v>
+        <v>45308</v>
       </c>
       <c r="O140" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P140" s="8" t="n">
-        <v>44998.346400463</v>
+        <v>45345.4013194444</v>
       </c>
     </row>
     <row r="141" customHeight="1" ht="20">
       <c r="A141" s="5" t="n">
-        <v>281</v>
+        <v>541</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>822</v>
+        <v>1503</v>
       </c>
       <c r="C141" s="6" t="n">
-        <v>45227</v>
+        <v>45594</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>45230</v>
+        <v>45598</v>
       </c>
       <c r="E141" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>540</v>
+        <v>690</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>345</v>
+        <v>690</v>
       </c>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
@@ -5635,39 +5649,39 @@
       <c r="K141" s="5"/>
       <c r="L141" s="7"/>
       <c r="M141" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N141" s="8" t="n">
-        <v>45032</v>
+        <v>45582</v>
       </c>
       <c r="O141" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P141" s="8" t="n">
-        <v>45231.536724537</v>
+        <v>45793.6943287037</v>
       </c>
     </row>
     <row r="142" customHeight="1" ht="20">
       <c r="A142" s="5" t="n">
-        <v>361</v>
+        <v>821</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>902</v>
+        <v>1783</v>
       </c>
       <c r="C142" s="6" t="n">
-        <v>45074</v>
+        <v>45996</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>45078</v>
+        <v>45998</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>695</v>
+        <v>490</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
@@ -5675,39 +5689,35 @@
       <c r="K142" s="5"/>
       <c r="L142" s="7"/>
       <c r="M142" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N142" s="8" t="n">
-        <v>45069</v>
-      </c>
-      <c r="O142" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P142" s="8" t="n">
-        <v>45071.3412962963</v>
-      </c>
+        <v>45983.3458449074</v>
+      </c>
+      <c r="O142" s="7"/>
+      <c r="P142" s="8"/>
     </row>
     <row r="143" customHeight="1" ht="20">
       <c r="A143" s="5" t="n">
-        <v>401</v>
+        <v>541</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>982</v>
+        <v>1664</v>
       </c>
       <c r="C143" s="6" t="n">
-        <v>45129</v>
+        <v>45915</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>45132</v>
+        <v>45919</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>380</v>
+        <v>690</v>
       </c>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
@@ -5715,203 +5725,15 @@
       <c r="K143" s="5"/>
       <c r="L143" s="7"/>
       <c r="M143" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N143" s="8" t="n">
-        <v>45111.2535763889</v>
-      </c>
-      <c r="O143" s="7"/>
-      <c r="P143" s="8"/>
-    </row>
-    <row r="144" customHeight="1" ht="20">
-      <c r="A144" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B144" s="5" t="n">
-        <v>1062</v>
-      </c>
-      <c r="C144" s="6" t="n">
-        <v>45206</v>
-      </c>
-      <c r="D144" s="6" t="n">
-        <v>45214</v>
-      </c>
-      <c r="E144" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F144" s="5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="G144" s="5" t="n">
-        <v>710</v>
-      </c>
-      <c r="H144" s="5"/>
-      <c r="I144" s="5"/>
-      <c r="J144" s="5"/>
-      <c r="K144" s="5"/>
-      <c r="L144" s="7"/>
-      <c r="M144" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N144" s="8" t="n">
-        <v>45171.606875</v>
-      </c>
-      <c r="O144" s="7"/>
-      <c r="P144" s="8"/>
-    </row>
-    <row r="145" customHeight="1" ht="20">
-      <c r="A145" s="5" t="n">
-        <v>461</v>
-      </c>
-      <c r="B145" s="5" t="n">
-        <v>1302</v>
-      </c>
-      <c r="C145" s="6" t="n">
-        <v>45346</v>
-      </c>
-      <c r="D145" s="6" t="n">
-        <v>45347</v>
-      </c>
-      <c r="E145" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F145" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="G145" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="H145" s="5"/>
-      <c r="I145" s="5"/>
-      <c r="J145" s="5"/>
-      <c r="K145" s="5"/>
-      <c r="L145" s="7"/>
-      <c r="M145" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N145" s="8" t="n">
-        <v>45308</v>
-      </c>
-      <c r="O145" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P145" s="8" t="n">
-        <v>45345.4013194444</v>
-      </c>
-    </row>
-    <row r="146" customHeight="1" ht="20">
-      <c r="A146" s="5" t="n">
-        <v>541</v>
-      </c>
-      <c r="B146" s="5" t="n">
-        <v>1503</v>
-      </c>
-      <c r="C146" s="6" t="n">
-        <v>45594</v>
-      </c>
-      <c r="D146" s="6" t="n">
-        <v>45598</v>
-      </c>
-      <c r="E146" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F146" s="5" t="n">
-        <v>690</v>
-      </c>
-      <c r="G146" s="5" t="n">
-        <v>690</v>
-      </c>
-      <c r="H146" s="5"/>
-      <c r="I146" s="5"/>
-      <c r="J146" s="5"/>
-      <c r="K146" s="5"/>
-      <c r="L146" s="7"/>
-      <c r="M146" s="7" t="s">
+        <v>45811</v>
+      </c>
+      <c r="O143" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="N146" s="8" t="n">
-        <v>45582</v>
-      </c>
-      <c r="O146" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P146" s="8" t="n">
-        <v>45793.6943287037</v>
-      </c>
-    </row>
-    <row r="147" customHeight="1" ht="20">
-      <c r="A147" s="5" t="n">
-        <v>821</v>
-      </c>
-      <c r="B147" s="5" t="n">
-        <v>1783</v>
-      </c>
-      <c r="C147" s="6" t="n">
-        <v>45996</v>
-      </c>
-      <c r="D147" s="6" t="n">
-        <v>45998</v>
-      </c>
-      <c r="E147" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F147" s="5" t="n">
-        <v>490</v>
-      </c>
-      <c r="G147" s="5" t="n">
-        <v>490</v>
-      </c>
-      <c r="H147" s="5"/>
-      <c r="I147" s="5"/>
-      <c r="J147" s="5"/>
-      <c r="K147" s="5"/>
-      <c r="L147" s="7"/>
-      <c r="M147" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="N147" s="8" t="n">
-        <v>45983.3458449074</v>
-      </c>
-      <c r="O147" s="7"/>
-      <c r="P147" s="8"/>
-    </row>
-    <row r="148" customHeight="1" ht="20">
-      <c r="A148" s="5" t="n">
-        <v>541</v>
-      </c>
-      <c r="B148" s="5" t="n">
-        <v>1664</v>
-      </c>
-      <c r="C148" s="6" t="n">
-        <v>45915</v>
-      </c>
-      <c r="D148" s="6" t="n">
-        <v>45919</v>
-      </c>
-      <c r="E148" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F148" s="5" t="n">
-        <v>690</v>
-      </c>
-      <c r="G148" s="5" t="n">
-        <v>690</v>
-      </c>
-      <c r="H148" s="5"/>
-      <c r="I148" s="5"/>
-      <c r="J148" s="5"/>
-      <c r="K148" s="5"/>
-      <c r="L148" s="7"/>
-      <c r="M148" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="N148" s="8" t="n">
-        <v>45811</v>
-      </c>
-      <c r="O148" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P148" s="8" t="n">
+      <c r="P143" s="8" t="n">
         <v>45951.6466550926</v>
       </c>
     </row>

--- a/inp_Excel/ana_date_viaggi.xlsx
+++ b/inp_Excel/ana_date_viaggi.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="22">
   <si>
     <t>VIAGGIO_ID_FK</t>
   </si>
@@ -178,8 +178,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:P143" totalsRowShown="0" headerRowCount="1">
-  <autoFilter ref="A1:P143"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:P142" totalsRowShown="0" headerRowCount="1">
+  <autoFilter ref="A1:P142"/>
   <tableColumns count="16">
     <tableColumn id="1" name="VIAGGIO_ID_FK"/>
     <tableColumn id="2" name="DATA_VIAGGIO_ID"/>
@@ -1185,25 +1185,25 @@
     </row>
     <row r="26" customHeight="1" ht="20">
       <c r="A26" s="5" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>45804</v>
+        <v>45825</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>45810</v>
+        <v>45829</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>960</v>
+        <v>390</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>960</v>
+        <v>390</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -1220,30 +1220,30 @@
         <v>19</v>
       </c>
       <c r="P26" s="8" t="n">
-        <v>46030.6455092593</v>
+        <v>45908.4481365741</v>
       </c>
     </row>
     <row r="27" customHeight="1" ht="20">
       <c r="A27" s="5" t="n">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>45825</v>
+        <v>46252</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>45829</v>
+        <v>46262</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>390</v>
+        <v>940</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>390</v>
+        <v>940</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
@@ -1260,30 +1260,30 @@
         <v>19</v>
       </c>
       <c r="P27" s="8" t="n">
-        <v>45908.4481365741</v>
+        <v>45983.3247569444</v>
       </c>
     </row>
     <row r="28" customHeight="1" ht="20">
       <c r="A28" s="5" t="n">
-        <v>626</v>
+        <v>822</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1588</v>
+        <v>1784</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>46252</v>
+        <v>46045</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>46262</v>
+        <v>46047</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>940</v>
+        <v>490</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>940</v>
+        <v>490</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
@@ -1294,36 +1294,32 @@
         <v>19</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>45700</v>
-      </c>
-      <c r="O28" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P28" s="8" t="n">
-        <v>45983.3247569444</v>
-      </c>
+        <v>45983.3522106481</v>
+      </c>
+      <c r="O28" s="7"/>
+      <c r="P28" s="8"/>
     </row>
     <row r="29" customHeight="1" ht="20">
       <c r="A29" s="5" t="n">
-        <v>822</v>
+        <v>61</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>1784</v>
+        <v>121</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>46045</v>
+        <v>44470</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>46047</v>
+        <v>44472</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>490</v>
+        <v>350</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>490</v>
+        <v>150</v>
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
@@ -1331,35 +1327,35 @@
       <c r="K29" s="5"/>
       <c r="L29" s="7"/>
       <c r="M29" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>45983.3522106481</v>
+        <v>44468.7524884259</v>
       </c>
       <c r="O29" s="7"/>
       <c r="P29" s="8"/>
     </row>
     <row r="30" customHeight="1" ht="20">
       <c r="A30" s="5" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>44470</v>
+        <v>44513</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>44472</v>
+        <v>44514</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>350</v>
+        <v>230</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
@@ -1370,32 +1366,32 @@
         <v>17</v>
       </c>
       <c r="N30" s="8" t="n">
-        <v>44468.7524884259</v>
+        <v>44515.6906597222</v>
       </c>
       <c r="O30" s="7"/>
       <c r="P30" s="8"/>
     </row>
     <row r="31" customHeight="1" ht="20">
       <c r="A31" s="5" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>44513</v>
+        <v>44625</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>44514</v>
+        <v>44626</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -1406,32 +1402,36 @@
         <v>17</v>
       </c>
       <c r="N31" s="8" t="n">
-        <v>44515.6906597222</v>
-      </c>
-      <c r="O31" s="7"/>
-      <c r="P31" s="8"/>
+        <v>44594</v>
+      </c>
+      <c r="O31" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>44627.6058680556</v>
+      </c>
     </row>
     <row r="32" customHeight="1" ht="20">
       <c r="A32" s="5" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>162</v>
+        <v>262</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>44625</v>
+        <v>44863</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>44626</v>
+        <v>44866</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>245</v>
+        <v>540</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>140</v>
+        <v>340</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -1442,36 +1442,36 @@
         <v>17</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>44594</v>
+        <v>44645</v>
       </c>
       <c r="O32" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P32" s="8" t="n">
-        <v>44627.6058680556</v>
+        <v>44875.334537037</v>
       </c>
     </row>
     <row r="33" customHeight="1" ht="20">
       <c r="A33" s="5" t="n">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>44863</v>
+        <v>44660</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>44866</v>
+        <v>44660</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>540</v>
+        <v>130</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>340</v>
+        <v>30</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
@@ -1482,27 +1482,27 @@
         <v>17</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>44645</v>
+        <v>44648</v>
       </c>
       <c r="O33" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P33" s="8" t="n">
-        <v>44875.334537037</v>
+        <v>44659.3133333333</v>
       </c>
     </row>
     <row r="34" customHeight="1" ht="20">
       <c r="A34" s="5" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>44660</v>
+        <v>44661</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>44660</v>
+        <v>44661</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>18</v>
@@ -1528,30 +1528,30 @@
         <v>17</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>44659.3133333333</v>
+        <v>44785.5688194444</v>
       </c>
     </row>
     <row r="35" customHeight="1" ht="20">
       <c r="A35" s="5" t="n">
-        <v>49</v>
+        <v>221</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>283</v>
+        <v>542</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>44661</v>
+        <v>44868</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>44661</v>
+        <v>44871</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
@@ -1562,36 +1562,32 @@
         <v>17</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>44648</v>
-      </c>
-      <c r="O35" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P35" s="8" t="n">
-        <v>44785.5688194444</v>
-      </c>
+        <v>44878.7394907407</v>
+      </c>
+      <c r="O35" s="7"/>
+      <c r="P35" s="8"/>
     </row>
     <row r="36" customHeight="1" ht="20">
       <c r="A36" s="5" t="n">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>542</v>
+        <v>662</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>44868</v>
+        <v>45059</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>44871</v>
+        <v>45060</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
@@ -1602,32 +1598,36 @@
         <v>17</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>44878.7394907407</v>
-      </c>
-      <c r="O36" s="7"/>
-      <c r="P36" s="8"/>
+        <v>44965</v>
+      </c>
+      <c r="O36" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P36" s="8" t="n">
+        <v>45062.5050347222</v>
+      </c>
     </row>
     <row r="37" customHeight="1" ht="20">
       <c r="A37" s="5" t="n">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>662</v>
+        <v>762</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>45059</v>
+        <v>45002</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>45060</v>
+        <v>45004</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
@@ -1638,36 +1638,36 @@
         <v>17</v>
       </c>
       <c r="N37" s="8" t="n">
-        <v>44965</v>
+        <v>45000</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P37" s="8" t="n">
-        <v>45062.5050347222</v>
+        <v>45004.5737615741</v>
       </c>
     </row>
     <row r="38" customHeight="1" ht="20">
       <c r="A38" s="5" t="n">
-        <v>261</v>
+        <v>301</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>762</v>
+        <v>842</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>45002</v>
+        <v>45079</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>45004</v>
+        <v>45081</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
@@ -1678,36 +1678,32 @@
         <v>17</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>45000</v>
-      </c>
-      <c r="O38" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P38" s="8" t="n">
-        <v>45004.5737615741</v>
-      </c>
+        <v>45035.7764699074</v>
+      </c>
+      <c r="O38" s="7"/>
+      <c r="P38" s="8"/>
     </row>
     <row r="39" customHeight="1" ht="20">
       <c r="A39" s="5" t="n">
-        <v>301</v>
+        <v>341</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>842</v>
+        <v>882</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>45079</v>
+        <v>45044</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>45081</v>
+        <v>45046</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>225</v>
+        <v>1</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
@@ -1718,32 +1714,32 @@
         <v>17</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>45035.7764699074</v>
+        <v>45049.8069675926</v>
       </c>
       <c r="O39" s="7"/>
       <c r="P39" s="8"/>
     </row>
     <row r="40" customHeight="1" ht="20">
       <c r="A40" s="5" t="n">
-        <v>341</v>
+        <v>46</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>882</v>
+        <v>922</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>45044</v>
+        <v>45087</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>45046</v>
+        <v>45088</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
@@ -1754,23 +1750,23 @@
         <v>17</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>45049.8069675926</v>
+        <v>45079.3949074074</v>
       </c>
       <c r="O40" s="7"/>
       <c r="P40" s="8"/>
     </row>
     <row r="41" customHeight="1" ht="20">
       <c r="A41" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>922</v>
+        <v>1002</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>45087</v>
+        <v>45178</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>45088</v>
+        <v>45179</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>16</v>
@@ -1790,26 +1786,26 @@
         <v>17</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>45079.3949074074</v>
+        <v>45129.5794328704</v>
       </c>
       <c r="O41" s="7"/>
       <c r="P41" s="8"/>
     </row>
     <row r="42" customHeight="1" ht="20">
       <c r="A42" s="5" t="n">
-        <v>48</v>
+        <v>461</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1002</v>
+        <v>1222</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>45178</v>
+        <v>45332</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>45179</v>
+        <v>45333</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>250</v>
@@ -1826,32 +1822,36 @@
         <v>17</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>45129.5794328704</v>
-      </c>
-      <c r="O42" s="7"/>
-      <c r="P42" s="8"/>
+        <v>45285</v>
+      </c>
+      <c r="O42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P42" s="8" t="n">
+        <v>45335.3894675926</v>
+      </c>
     </row>
     <row r="43" customHeight="1" ht="20">
       <c r="A43" s="5" t="n">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1222</v>
+        <v>1322</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>45332</v>
+        <v>45381</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>45333</v>
+        <v>45383</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>250</v>
+        <v>395</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
@@ -1862,36 +1862,36 @@
         <v>17</v>
       </c>
       <c r="N43" s="8" t="n">
-        <v>45285</v>
+        <v>45310</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P43" s="8" t="n">
-        <v>45335.3894675926</v>
+        <v>45386.3521296296</v>
       </c>
     </row>
     <row r="44" customHeight="1" ht="20">
       <c r="A44" s="5" t="n">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1322</v>
+        <v>1423</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>45381</v>
+        <v>45512</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>45383</v>
+        <v>45529</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>395</v>
+        <v>1650</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>260</v>
+        <v>1100</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -1902,118 +1902,114 @@
         <v>17</v>
       </c>
       <c r="N44" s="8" t="n">
-        <v>45310</v>
+        <v>45348</v>
       </c>
       <c r="O44" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>45386.3521296296</v>
+        <v>45517.6562268519</v>
       </c>
     </row>
     <row r="45" customHeight="1" ht="20">
       <c r="A45" s="5" t="n">
-        <v>521</v>
+        <v>261</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1423</v>
+        <v>1463</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>45512</v>
+        <v>45421</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>45529</v>
+        <v>45423</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>1650</v>
+        <v>150</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1100</v>
+        <v>80</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
-      <c r="L45" s="7"/>
+      <c r="L45" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="M45" s="7" t="s">
         <v>17</v>
       </c>
       <c r="N45" s="8" t="n">
-        <v>45348</v>
+        <v>45419</v>
       </c>
       <c r="O45" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>45517.6562268519</v>
+        <v>45419.5241203704</v>
       </c>
     </row>
     <row r="46" customHeight="1" ht="20">
       <c r="A46" s="5" t="n">
-        <v>261</v>
+        <v>461</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1463</v>
+        <v>1483</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>45421</v>
+        <v>45458</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>45423</v>
+        <v>45459</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F46" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="G46" s="5" t="n">
         <v>150</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>80</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
-      <c r="L46" s="7" t="s">
-        <v>20</v>
-      </c>
+      <c r="L46" s="7"/>
       <c r="M46" s="7" t="s">
         <v>17</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>45419</v>
-      </c>
-      <c r="O46" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P46" s="8" t="n">
-        <v>45419.5241203704</v>
-      </c>
+        <v>45446.6197337963</v>
+      </c>
+      <c r="O46" s="7"/>
+      <c r="P46" s="8"/>
     </row>
     <row r="47" customHeight="1" ht="20">
       <c r="A47" s="5" t="n">
-        <v>461</v>
+        <v>621</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1483</v>
+        <v>1584</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>45458</v>
+        <v>45774</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>45459</v>
+        <v>45780</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>250</v>
+        <v>1060</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>150</v>
+        <v>1060</v>
       </c>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
@@ -2021,35 +2017,39 @@
       <c r="K47" s="5"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N47" s="8" t="n">
-        <v>45446.6197337963</v>
-      </c>
-      <c r="O47" s="7"/>
-      <c r="P47" s="8"/>
+        <v>45700</v>
+      </c>
+      <c r="O47" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="P47" s="8" t="n">
+        <v>45793.6937847222</v>
+      </c>
     </row>
     <row r="48" customHeight="1" ht="20">
       <c r="A48" s="5" t="n">
-        <v>621</v>
+        <v>54</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>1584</v>
+        <v>41</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>45774</v>
+        <v>44002</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>45780</v>
+        <v>44003</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>1060</v>
+        <v>230</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>1060</v>
+        <v>130</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
@@ -2057,39 +2057,39 @@
       <c r="K48" s="5"/>
       <c r="L48" s="7"/>
       <c r="M48" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N48" s="8" t="n">
-        <v>45700</v>
+        <v>44445</v>
       </c>
       <c r="O48" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P48" s="8" t="n">
-        <v>45793.6937847222</v>
+        <v>44764.5170138889</v>
       </c>
     </row>
     <row r="49" customHeight="1" ht="20">
       <c r="A49" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B49" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B49" s="5" t="n">
-        <v>41</v>
-      </c>
       <c r="C49" s="6" t="n">
-        <v>44002</v>
+        <v>44150</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>44003</v>
+        <v>44150</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
@@ -2100,36 +2100,32 @@
         <v>17</v>
       </c>
       <c r="N49" s="8" t="n">
-        <v>44445</v>
-      </c>
-      <c r="O49" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P49" s="8" t="n">
-        <v>44764.5170138889</v>
-      </c>
+        <v>44446.5280439815</v>
+      </c>
+      <c r="O49" s="7"/>
+      <c r="P49" s="8"/>
     </row>
     <row r="50" customHeight="1" ht="20">
       <c r="A50" s="5" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>44150</v>
+        <v>43883</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>44150</v>
+        <v>43884</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F50" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="G50" s="5" t="n">
         <v>130</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
@@ -2140,26 +2136,30 @@
         <v>17</v>
       </c>
       <c r="N50" s="8" t="n">
-        <v>44446.5280439815</v>
-      </c>
-      <c r="O50" s="7"/>
-      <c r="P50" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P50" s="8" t="n">
+        <v>44792.650150463</v>
+      </c>
     </row>
     <row r="51" customHeight="1" ht="20">
       <c r="A51" s="5" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>43883</v>
+        <v>44471</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>43884</v>
+        <v>44472</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F51" s="5" t="n">
         <v>230</v>
@@ -2176,36 +2176,32 @@
         <v>17</v>
       </c>
       <c r="N51" s="8" t="n">
-        <v>44446</v>
-      </c>
-      <c r="O51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P51" s="8" t="n">
-        <v>44792.650150463</v>
-      </c>
+        <v>44446.5346527778</v>
+      </c>
+      <c r="O51" s="7"/>
+      <c r="P51" s="8"/>
     </row>
     <row r="52" customHeight="1" ht="20">
       <c r="A52" s="5" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>68</v>
+        <v>622</v>
       </c>
       <c r="C52" s="6" t="n">
-        <v>44471</v>
+        <v>45024</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>44472</v>
+        <v>45030</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>230</v>
+        <v>1190</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>130</v>
+        <v>840</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
@@ -2216,32 +2212,32 @@
         <v>17</v>
       </c>
       <c r="N52" s="8" t="n">
-        <v>44446.5346527778</v>
+        <v>44930.4891435185</v>
       </c>
       <c r="O52" s="7"/>
       <c r="P52" s="8"/>
     </row>
     <row r="53" customHeight="1" ht="20">
       <c r="A53" s="5" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>622</v>
+        <v>202</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>45024</v>
+        <v>44618</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>45030</v>
+        <v>44619</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>1190</v>
+        <v>245</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>840</v>
+        <v>140</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
@@ -2252,32 +2248,36 @@
         <v>17</v>
       </c>
       <c r="N53" s="8" t="n">
-        <v>44930.4891435185</v>
-      </c>
-      <c r="O53" s="7"/>
-      <c r="P53" s="8"/>
+        <v>44607</v>
+      </c>
+      <c r="O53" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P53" s="8" t="n">
+        <v>44792.5757407407</v>
+      </c>
     </row>
     <row r="54" customHeight="1" ht="20">
       <c r="A54" s="5" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>202</v>
+        <v>242</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>44618</v>
+        <v>44809</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>44619</v>
+        <v>44815</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>245</v>
+        <v>980</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>140</v>
+        <v>690</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
@@ -2288,36 +2288,32 @@
         <v>17</v>
       </c>
       <c r="N54" s="8" t="n">
-        <v>44607</v>
-      </c>
-      <c r="O54" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P54" s="8" t="n">
-        <v>44792.5757407407</v>
-      </c>
+        <v>44620.8319791667</v>
+      </c>
+      <c r="O54" s="7"/>
+      <c r="P54" s="8"/>
     </row>
     <row r="55" customHeight="1" ht="20">
       <c r="A55" s="5" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>242</v>
+        <v>382</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>44809</v>
+        <v>44702</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>44815</v>
+        <v>44703</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>980</v>
+        <v>245</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
@@ -2328,23 +2324,27 @@
         <v>17</v>
       </c>
       <c r="N55" s="8" t="n">
-        <v>44620.8319791667</v>
-      </c>
-      <c r="O55" s="7"/>
-      <c r="P55" s="8"/>
+        <v>44686</v>
+      </c>
+      <c r="O55" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P55" s="8" t="n">
+        <v>44701.8047222222</v>
+      </c>
     </row>
     <row r="56" customHeight="1" ht="20">
       <c r="A56" s="5" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C56" s="6" t="n">
-        <v>44702</v>
+        <v>44835</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>44703</v>
+        <v>44836</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>18</v>
@@ -2364,36 +2364,36 @@
         <v>17</v>
       </c>
       <c r="N56" s="8" t="n">
-        <v>44686</v>
+        <v>44732</v>
       </c>
       <c r="O56" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P56" s="8" t="n">
-        <v>44701.8047222222</v>
+        <v>44834.645</v>
       </c>
     </row>
     <row r="57" customHeight="1" ht="20">
       <c r="A57" s="5" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>402</v>
+        <v>642</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>44835</v>
+        <v>45038</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>44836</v>
+        <v>45041</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>245</v>
+        <v>495</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>140</v>
+        <v>345</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
@@ -2404,36 +2404,36 @@
         <v>17</v>
       </c>
       <c r="N57" s="8" t="n">
-        <v>44732</v>
+        <v>44952</v>
       </c>
       <c r="O57" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P57" s="8" t="n">
-        <v>44834.645</v>
+        <v>45035.7756018519</v>
       </c>
     </row>
     <row r="58" customHeight="1" ht="20">
       <c r="A58" s="5" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>642</v>
+        <v>1022</v>
       </c>
       <c r="C58" s="6" t="n">
-        <v>45038</v>
+        <v>45164</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>45041</v>
+        <v>45165</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>495</v>
+        <v>250</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>345</v>
+        <v>150</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
@@ -2444,27 +2444,27 @@
         <v>17</v>
       </c>
       <c r="N58" s="8" t="n">
-        <v>44952</v>
+        <v>45157</v>
       </c>
       <c r="O58" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P58" s="8" t="n">
-        <v>45035.7756018519</v>
+        <v>45163.4064814815</v>
       </c>
     </row>
     <row r="59" customHeight="1" ht="20">
       <c r="A59" s="5" t="n">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>1022</v>
+        <v>1042</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>45164</v>
+        <v>45199</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>45165</v>
+        <v>45200</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>18</v>
@@ -2484,36 +2484,36 @@
         <v>17</v>
       </c>
       <c r="N59" s="8" t="n">
-        <v>45157</v>
+        <v>45169</v>
       </c>
       <c r="O59" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P59" s="8" t="n">
-        <v>45163.4064814815</v>
+        <v>45198.5217708333</v>
       </c>
     </row>
     <row r="60" customHeight="1" ht="20">
       <c r="A60" s="5" t="n">
-        <v>50</v>
+        <v>421</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>1042</v>
+        <v>1102</v>
       </c>
       <c r="C60" s="6" t="n">
-        <v>45199</v>
+        <v>45232</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>45200</v>
+        <v>45235</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>250</v>
+        <v>495</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>150</v>
+        <v>345</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
@@ -2524,36 +2524,36 @@
         <v>17</v>
       </c>
       <c r="N60" s="8" t="n">
-        <v>45169</v>
+        <v>45191</v>
       </c>
       <c r="O60" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P60" s="8" t="n">
-        <v>45198.5217708333</v>
+        <v>45223.3995949074</v>
       </c>
     </row>
     <row r="61" customHeight="1" ht="20">
       <c r="A61" s="5" t="n">
-        <v>421</v>
+        <v>25</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>1102</v>
+        <v>1383</v>
       </c>
       <c r="C61" s="6" t="n">
-        <v>45232</v>
+        <v>45431</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>45235</v>
+        <v>45437</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>495</v>
+        <v>1190</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>345</v>
+        <v>870</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
@@ -2564,36 +2564,32 @@
         <v>17</v>
       </c>
       <c r="N61" s="8" t="n">
-        <v>45191</v>
-      </c>
-      <c r="O61" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P61" s="8" t="n">
-        <v>45223.3995949074</v>
-      </c>
+        <v>45335.3893055556</v>
+      </c>
+      <c r="O61" s="7"/>
+      <c r="P61" s="8"/>
     </row>
     <row r="62" customHeight="1" ht="20">
       <c r="A62" s="5" t="n">
-        <v>25</v>
+        <v>561</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>1383</v>
+        <v>1523</v>
       </c>
       <c r="C62" s="6" t="n">
-        <v>45431</v>
+        <v>45655</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>45437</v>
+        <v>45660</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>1190</v>
+        <v>1</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>870</v>
+        <v>1</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
@@ -2604,32 +2600,36 @@
         <v>17</v>
       </c>
       <c r="N62" s="8" t="n">
-        <v>45335.3893055556</v>
-      </c>
-      <c r="O62" s="7"/>
-      <c r="P62" s="8"/>
+        <v>45646</v>
+      </c>
+      <c r="O62" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="P62" s="8" t="n">
+        <v>45793.6944444444</v>
+      </c>
     </row>
     <row r="63" customHeight="1" ht="20">
       <c r="A63" s="5" t="n">
-        <v>561</v>
+        <v>722</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>1523</v>
+        <v>1684</v>
       </c>
       <c r="C63" s="6" t="n">
-        <v>45655</v>
+        <v>46020</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>45660</v>
+        <v>46027</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>1</v>
+        <v>1390</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1</v>
+        <v>1390</v>
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
@@ -2637,39 +2637,39 @@
       <c r="K63" s="5"/>
       <c r="L63" s="7"/>
       <c r="M63" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N63" s="8" t="n">
-        <v>45646</v>
+        <v>45908</v>
       </c>
       <c r="O63" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P63" s="8" t="n">
-        <v>45793.6944444444</v>
+        <v>46030.6407060185</v>
       </c>
     </row>
     <row r="64" customHeight="1" ht="20">
       <c r="A64" s="5" t="n">
-        <v>722</v>
+        <v>741</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>1684</v>
+        <v>1703</v>
       </c>
       <c r="C64" s="6" t="n">
-        <v>46020</v>
+        <v>45995</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>46027</v>
+        <v>45999</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>1390</v>
+        <v>690</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>1390</v>
+        <v>690</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
@@ -2680,36 +2680,36 @@
         <v>19</v>
       </c>
       <c r="N64" s="8" t="n">
-        <v>45908</v>
+        <v>45951</v>
       </c>
       <c r="O64" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P64" s="8" t="n">
-        <v>46030.6407060185</v>
+        <v>46030.640462963</v>
       </c>
     </row>
     <row r="65" customHeight="1" ht="20">
       <c r="A65" s="5" t="n">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>1703</v>
+        <v>1723</v>
       </c>
       <c r="C65" s="6" t="n">
-        <v>45995</v>
+        <v>46144</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>45999</v>
+        <v>46149</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>690</v>
+        <v>790</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>690</v>
+        <v>790</v>
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
@@ -2720,36 +2720,32 @@
         <v>19</v>
       </c>
       <c r="N65" s="8" t="n">
-        <v>45951</v>
-      </c>
-      <c r="O65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P65" s="8" t="n">
-        <v>46030.640462963</v>
-      </c>
+        <v>45963.3395717593</v>
+      </c>
+      <c r="O65" s="7"/>
+      <c r="P65" s="8"/>
     </row>
     <row r="66" customHeight="1" ht="20">
       <c r="A66" s="5" t="n">
-        <v>761</v>
+        <v>1</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>1723</v>
+        <v>24</v>
       </c>
       <c r="C66" s="6" t="n">
-        <v>46144</v>
+        <v>44324</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>46149</v>
+        <v>44325</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>790</v>
+        <v>230</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>790</v>
+        <v>130</v>
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
@@ -2757,26 +2753,26 @@
       <c r="K66" s="5"/>
       <c r="L66" s="7"/>
       <c r="M66" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N66" s="8" t="n">
-        <v>45963.3395717593</v>
+        <v>44420.5177546296</v>
       </c>
       <c r="O66" s="7"/>
       <c r="P66" s="8"/>
     </row>
     <row r="67" customHeight="1" ht="20">
       <c r="A67" s="5" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C67" s="6" t="n">
-        <v>44324</v>
+        <v>43995</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>44325</v>
+        <v>43996</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>18</v>
@@ -2796,7 +2792,7 @@
         <v>17</v>
       </c>
       <c r="N67" s="8" t="n">
-        <v>44420.5177546296</v>
+        <v>44420.5183796296</v>
       </c>
       <c r="O67" s="7"/>
       <c r="P67" s="8"/>
@@ -2806,13 +2802,13 @@
         <v>22</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C68" s="6" t="n">
-        <v>43995</v>
+        <v>44121</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>43996</v>
+        <v>44122</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>18</v>
@@ -2832,32 +2828,32 @@
         <v>17</v>
       </c>
       <c r="N68" s="8" t="n">
-        <v>44420.5183796296</v>
+        <v>44420.5187268519</v>
       </c>
       <c r="O68" s="7"/>
       <c r="P68" s="8"/>
     </row>
     <row r="69" customHeight="1" ht="20">
       <c r="A69" s="5" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C69" s="6" t="n">
-        <v>44121</v>
+        <v>44149</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>44122</v>
+        <v>44149</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
@@ -2868,26 +2864,26 @@
         <v>17</v>
       </c>
       <c r="N69" s="8" t="n">
-        <v>44420.5187268519</v>
+        <v>44446.5248032407</v>
       </c>
       <c r="O69" s="7"/>
       <c r="P69" s="8"/>
     </row>
     <row r="70" customHeight="1" ht="20">
       <c r="A70" s="5" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C70" s="6" t="n">
-        <v>44149</v>
+        <v>44492</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>44149</v>
+        <v>44492</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>130</v>
@@ -2904,32 +2900,36 @@
         <v>17</v>
       </c>
       <c r="N70" s="8" t="n">
-        <v>44446.5248032407</v>
-      </c>
-      <c r="O70" s="7"/>
-      <c r="P70" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O70" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P70" s="8" t="n">
+        <v>44785.5593287037</v>
+      </c>
     </row>
     <row r="71" customHeight="1" ht="20">
       <c r="A71" s="5" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C71" s="6" t="n">
-        <v>44492</v>
+        <v>44133</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>44492</v>
+        <v>44136</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>130</v>
+        <v>520</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>30</v>
+        <v>280</v>
       </c>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
@@ -2946,30 +2946,30 @@
         <v>17</v>
       </c>
       <c r="P71" s="8" t="n">
-        <v>44785.5593287037</v>
+        <v>44847.4125231481</v>
       </c>
     </row>
     <row r="72" customHeight="1" ht="20">
       <c r="A72" s="5" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>44133</v>
+        <v>43690</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>44136</v>
+        <v>43697</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>520</v>
+        <v>780</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>280</v>
+        <v>560</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
@@ -2980,36 +2980,32 @@
         <v>17</v>
       </c>
       <c r="N72" s="8" t="n">
-        <v>44446</v>
-      </c>
-      <c r="O72" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P72" s="8" t="n">
-        <v>44847.4125231481</v>
-      </c>
+        <v>44446.5365856481</v>
+      </c>
+      <c r="O72" s="7"/>
+      <c r="P72" s="8"/>
     </row>
     <row r="73" customHeight="1" ht="20">
       <c r="A73" s="5" t="n">
         <v>27</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C73" s="6" t="n">
-        <v>43690</v>
+        <v>44380</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>43697</v>
+        <v>44386</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>780</v>
+        <v>820</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
@@ -3020,32 +3016,32 @@
         <v>17</v>
       </c>
       <c r="N73" s="8" t="n">
-        <v>44446.5365856481</v>
+        <v>44446.5373958333</v>
       </c>
       <c r="O73" s="7"/>
       <c r="P73" s="8"/>
     </row>
     <row r="74" customHeight="1" ht="20">
       <c r="A74" s="5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C74" s="6" t="n">
-        <v>44380</v>
+        <v>43932</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>44386</v>
+        <v>43938</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>820</v>
+        <v>890</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
@@ -3056,7 +3052,7 @@
         <v>17</v>
       </c>
       <c r="N74" s="8" t="n">
-        <v>44446.5373958333</v>
+        <v>44446.5383217593</v>
       </c>
       <c r="O74" s="7"/>
       <c r="P74" s="8"/>
@@ -3066,22 +3062,22 @@
         <v>25</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C75" s="6" t="n">
-        <v>43932</v>
+        <v>44380</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>43938</v>
+        <v>44386</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F75" s="5" t="n">
         <v>890</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
@@ -3092,32 +3088,32 @@
         <v>17</v>
       </c>
       <c r="N75" s="8" t="n">
-        <v>44446.5383217593</v>
+        <v>44446.5391898148</v>
       </c>
       <c r="O75" s="7"/>
       <c r="P75" s="8"/>
     </row>
     <row r="76" customHeight="1" ht="20">
       <c r="A76" s="5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="C76" s="6" t="n">
-        <v>44380</v>
+        <v>44611</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>44386</v>
+        <v>44612</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>890</v>
+        <v>245</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>590</v>
+        <v>140</v>
       </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
@@ -3128,32 +3124,36 @@
         <v>17</v>
       </c>
       <c r="N76" s="8" t="n">
-        <v>44446.5391898148</v>
-      </c>
-      <c r="O76" s="7"/>
-      <c r="P76" s="8"/>
+        <v>44603</v>
+      </c>
+      <c r="O76" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P76" s="8" t="n">
+        <v>44620.6170717593</v>
+      </c>
     </row>
     <row r="77" customHeight="1" ht="20">
       <c r="A77" s="5" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>182</v>
+        <v>302</v>
       </c>
       <c r="C77" s="6" t="n">
-        <v>44611</v>
+        <v>44786</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>44612</v>
+        <v>44797</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>245</v>
+        <v>1440</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>140</v>
+        <v>990</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
@@ -3164,36 +3164,32 @@
         <v>17</v>
       </c>
       <c r="N77" s="8" t="n">
-        <v>44603</v>
-      </c>
-      <c r="O77" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P77" s="8" t="n">
-        <v>44620.6170717593</v>
-      </c>
+        <v>44655.6645833333</v>
+      </c>
+      <c r="O77" s="7"/>
+      <c r="P77" s="8"/>
     </row>
     <row r="78" customHeight="1" ht="20">
       <c r="A78" s="5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>302</v>
+        <v>363</v>
       </c>
       <c r="C78" s="6" t="n">
-        <v>44786</v>
+        <v>44737</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>44797</v>
+        <v>44743</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>1440</v>
+        <v>890</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>990</v>
+        <v>590</v>
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
@@ -3204,34 +3200,40 @@
         <v>17</v>
       </c>
       <c r="N78" s="8" t="n">
-        <v>44655.6645833333</v>
-      </c>
-      <c r="O78" s="7"/>
-      <c r="P78" s="8"/>
+        <v>44679</v>
+      </c>
+      <c r="O78" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P78" s="8" t="n">
+        <v>44745.8054282407</v>
+      </c>
     </row>
     <row r="79" customHeight="1" ht="20">
       <c r="A79" s="5" t="n">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>363</v>
+        <v>462</v>
       </c>
       <c r="C79" s="6" t="n">
-        <v>44737</v>
+        <v>44898</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>44743</v>
+        <v>44907</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>890</v>
+        <v>1600</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>590</v>
-      </c>
-      <c r="H79" s="5"/>
+        <v>1350</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>1550</v>
+      </c>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
@@ -3240,40 +3242,38 @@
         <v>17</v>
       </c>
       <c r="N79" s="8" t="n">
-        <v>44679</v>
+        <v>44791</v>
       </c>
       <c r="O79" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P79" s="8" t="n">
-        <v>44745.8054282407</v>
+        <v>44915.6469675926</v>
       </c>
     </row>
     <row r="80" customHeight="1" ht="20">
       <c r="A80" s="5" t="n">
-        <v>141</v>
+        <v>201</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>462</v>
+        <v>522</v>
       </c>
       <c r="C80" s="6" t="n">
-        <v>44898</v>
+        <v>44856</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>44907</v>
+        <v>44857</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>1600</v>
+        <v>245</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1350</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>1550</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="H80" s="5"/>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
@@ -3282,36 +3282,36 @@
         <v>17</v>
       </c>
       <c r="N80" s="8" t="n">
-        <v>44791</v>
+        <v>44834</v>
       </c>
       <c r="O80" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P80" s="8" t="n">
-        <v>44915.6469675926</v>
+        <v>44837.3615972222</v>
       </c>
     </row>
     <row r="81" customHeight="1" ht="20">
       <c r="A81" s="5" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>522</v>
+        <v>742</v>
       </c>
       <c r="C81" s="6" t="n">
-        <v>44856</v>
+        <v>45010</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>44857</v>
+        <v>45011</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
@@ -3322,36 +3322,36 @@
         <v>17</v>
       </c>
       <c r="N81" s="8" t="n">
-        <v>44834</v>
+        <v>44994</v>
       </c>
       <c r="O81" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P81" s="8" t="n">
-        <v>44837.3615972222</v>
+        <v>45012.3928240741</v>
       </c>
     </row>
     <row r="82" customHeight="1" ht="20">
       <c r="A82" s="5" t="n">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>742</v>
+        <v>782</v>
       </c>
       <c r="C82" s="6" t="n">
-        <v>45010</v>
+        <v>45115</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>45011</v>
+        <v>45127</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>250</v>
+        <v>1490</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>150</v>
+        <v>995</v>
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
@@ -3362,36 +3362,32 @@
         <v>17</v>
       </c>
       <c r="N82" s="8" t="n">
-        <v>44994</v>
-      </c>
-      <c r="O82" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P82" s="8" t="n">
-        <v>45012.3928240741</v>
-      </c>
+        <v>45013.6681597222</v>
+      </c>
+      <c r="O82" s="7"/>
+      <c r="P82" s="8"/>
     </row>
     <row r="83" customHeight="1" ht="20">
       <c r="A83" s="5" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C83" s="6" t="n">
-        <v>45115</v>
+        <v>45101</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>45127</v>
+        <v>45108</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>1490</v>
+        <v>1100</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>995</v>
+        <v>710</v>
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
@@ -3402,32 +3398,32 @@
         <v>17</v>
       </c>
       <c r="N83" s="8" t="n">
-        <v>45013.6681597222</v>
+        <v>45013.6687037037</v>
       </c>
       <c r="O83" s="7"/>
       <c r="P83" s="8"/>
     </row>
     <row r="84" customHeight="1" ht="20">
       <c r="A84" s="5" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>783</v>
+        <v>942</v>
       </c>
       <c r="C84" s="6" t="n">
-        <v>45101</v>
+        <v>45107</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>45108</v>
+        <v>45109</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>1100</v>
+        <v>180</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>710</v>
+        <v>100</v>
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
@@ -3438,32 +3434,36 @@
         <v>17</v>
       </c>
       <c r="N84" s="8" t="n">
-        <v>45013.6687037037</v>
-      </c>
-      <c r="O84" s="7"/>
-      <c r="P84" s="8"/>
+        <v>45080</v>
+      </c>
+      <c r="O84" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P84" s="8" t="n">
+        <v>45111.2536921296</v>
+      </c>
     </row>
     <row r="85" customHeight="1" ht="20">
       <c r="A85" s="5" t="n">
-        <v>26</v>
+        <v>381</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>942</v>
+        <v>962</v>
       </c>
       <c r="C85" s="6" t="n">
-        <v>45107</v>
+        <v>45110</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>45109</v>
+        <v>45111</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
@@ -3474,13 +3474,13 @@
         <v>17</v>
       </c>
       <c r="N85" s="8" t="n">
-        <v>45080</v>
+        <v>45082</v>
       </c>
       <c r="O85" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P85" s="8" t="n">
-        <v>45111.2536921296</v>
+        <v>45111.2538310185</v>
       </c>
     </row>
     <row r="86" customHeight="1" ht="20">
@@ -3488,22 +3488,22 @@
         <v>381</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>962</v>
+        <v>1082</v>
       </c>
       <c r="C86" s="6" t="n">
-        <v>45110</v>
+        <v>45177</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>45111</v>
+        <v>45179</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
@@ -3514,36 +3514,36 @@
         <v>17</v>
       </c>
       <c r="N86" s="8" t="n">
-        <v>45082</v>
+        <v>45173</v>
       </c>
       <c r="O86" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P86" s="8" t="n">
-        <v>45111.2538310185</v>
+        <v>45173.6145601852</v>
       </c>
     </row>
     <row r="87" customHeight="1" ht="20">
       <c r="A87" s="5" t="n">
-        <v>381</v>
+        <v>301</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>1082</v>
+        <v>1122</v>
       </c>
       <c r="C87" s="6" t="n">
-        <v>45177</v>
+        <v>45268</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>45179</v>
+        <v>45270</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>500</v>
+        <v>145</v>
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
@@ -3554,36 +3554,36 @@
         <v>17</v>
       </c>
       <c r="N87" s="8" t="n">
-        <v>45173</v>
+        <v>45205</v>
       </c>
       <c r="O87" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P87" s="8" t="n">
-        <v>45173.6145601852</v>
+        <v>45267.4084143519</v>
       </c>
     </row>
     <row r="88" customHeight="1" ht="20">
       <c r="A88" s="5" t="n">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>1122</v>
+        <v>1162</v>
       </c>
       <c r="C88" s="6" t="n">
-        <v>45268</v>
+        <v>45318</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>45270</v>
+        <v>45319</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>370</v>
+        <v>250</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
@@ -3594,36 +3594,36 @@
         <v>17</v>
       </c>
       <c r="N88" s="8" t="n">
-        <v>45205</v>
+        <v>45274</v>
       </c>
       <c r="O88" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P88" s="8" t="n">
-        <v>45267.4084143519</v>
+        <v>45320.4609837963</v>
       </c>
     </row>
     <row r="89" customHeight="1" ht="20">
       <c r="A89" s="5" t="n">
-        <v>81</v>
+        <v>441</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>1162</v>
+        <v>1182</v>
       </c>
       <c r="C89" s="6" t="n">
-        <v>45318</v>
+        <v>45290</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>45319</v>
+        <v>45295</v>
       </c>
       <c r="E89" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>250</v>
+        <v>860</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>150</v>
+        <v>660</v>
       </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
@@ -3634,36 +3634,36 @@
         <v>17</v>
       </c>
       <c r="N89" s="8" t="n">
-        <v>45274</v>
+        <v>45277</v>
       </c>
       <c r="O89" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P89" s="8" t="n">
-        <v>45320.4609837963</v>
+        <v>45285.4578009259</v>
       </c>
     </row>
     <row r="90" customHeight="1" ht="20">
       <c r="A90" s="5" t="n">
-        <v>441</v>
+        <v>261</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>1182</v>
+        <v>1202</v>
       </c>
       <c r="C90" s="6" t="n">
-        <v>45290</v>
+        <v>45366</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>45295</v>
+        <v>45368</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>860</v>
+        <v>385</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>660</v>
+        <v>240</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
@@ -3674,36 +3674,36 @@
         <v>17</v>
       </c>
       <c r="N90" s="8" t="n">
-        <v>45277</v>
+        <v>45280</v>
       </c>
       <c r="O90" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P90" s="8" t="n">
-        <v>45285.4578009259</v>
+        <v>45419.522962963</v>
       </c>
     </row>
     <row r="91" customHeight="1" ht="20">
       <c r="A91" s="5" t="n">
-        <v>261</v>
+        <v>181</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>1202</v>
+        <v>1262</v>
       </c>
       <c r="C91" s="6" t="n">
-        <v>45366</v>
+        <v>45339</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>45368</v>
+        <v>45340</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>385</v>
+        <v>250</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
@@ -3714,36 +3714,36 @@
         <v>17</v>
       </c>
       <c r="N91" s="8" t="n">
-        <v>45280</v>
+        <v>45303</v>
       </c>
       <c r="O91" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P91" s="8" t="n">
-        <v>45419.522962963</v>
+        <v>45343.4145486111</v>
       </c>
     </row>
     <row r="92" customHeight="1" ht="20">
       <c r="A92" s="5" t="n">
-        <v>181</v>
+        <v>27</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>1262</v>
+        <v>1342</v>
       </c>
       <c r="C92" s="6" t="n">
-        <v>45339</v>
+        <v>45444</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>45340</v>
+        <v>45451</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>250</v>
+        <v>940</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>150</v>
+        <v>590</v>
       </c>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
@@ -3754,36 +3754,32 @@
         <v>17</v>
       </c>
       <c r="N92" s="8" t="n">
-        <v>45303</v>
-      </c>
-      <c r="O92" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P92" s="8" t="n">
-        <v>45343.4145486111</v>
-      </c>
+        <v>45313.4136458333</v>
+      </c>
+      <c r="O92" s="7"/>
+      <c r="P92" s="8"/>
     </row>
     <row r="93" customHeight="1" ht="20">
       <c r="A93" s="5" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>1342</v>
+        <v>1403</v>
       </c>
       <c r="C93" s="6" t="n">
-        <v>45444</v>
+        <v>45451</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>45451</v>
+        <v>45459</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>940</v>
+        <v>990</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>590</v>
+        <v>690</v>
       </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
@@ -3794,32 +3790,32 @@
         <v>17</v>
       </c>
       <c r="N93" s="8" t="n">
-        <v>45313.4136458333</v>
+        <v>45348.3647453704</v>
       </c>
       <c r="O93" s="7"/>
       <c r="P93" s="8"/>
     </row>
     <row r="94" customHeight="1" ht="20">
       <c r="A94" s="5" t="n">
-        <v>41</v>
+        <v>321</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>1403</v>
+        <v>1444</v>
       </c>
       <c r="C94" s="6" t="n">
-        <v>45451</v>
+        <v>45464</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>45459</v>
+        <v>45478</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>990</v>
+        <v>1650</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>690</v>
+        <v>1100</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
@@ -3830,32 +3826,32 @@
         <v>17</v>
       </c>
       <c r="N94" s="8" t="n">
-        <v>45348.3647453704</v>
+        <v>45405.5582175926</v>
       </c>
       <c r="O94" s="7"/>
       <c r="P94" s="8"/>
     </row>
     <row r="95" customHeight="1" ht="20">
       <c r="A95" s="5" t="n">
-        <v>321</v>
+        <v>622</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>1444</v>
+        <v>1583</v>
       </c>
       <c r="C95" s="6" t="n">
-        <v>45464</v>
+        <v>45767</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>45478</v>
+        <v>45772</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>1650</v>
+        <v>790</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>1100</v>
+        <v>790</v>
       </c>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
@@ -3863,35 +3859,39 @@
       <c r="K95" s="5"/>
       <c r="L95" s="7"/>
       <c r="M95" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N95" s="8" t="n">
-        <v>45405.5582175926</v>
-      </c>
-      <c r="O95" s="7"/>
-      <c r="P95" s="8"/>
+        <v>45700</v>
+      </c>
+      <c r="O95" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="P95" s="8" t="n">
+        <v>45793.6939930556</v>
+      </c>
     </row>
     <row r="96" customHeight="1" ht="20">
       <c r="A96" s="5" t="n">
-        <v>622</v>
+        <v>861</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>1583</v>
+        <v>1823</v>
       </c>
       <c r="C96" s="6" t="n">
-        <v>45767</v>
+        <v>46122</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>45772</v>
+        <v>46132</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>790</v>
+        <v>2290</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>790</v>
+        <v>2290</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
@@ -3902,36 +3902,32 @@
         <v>19</v>
       </c>
       <c r="N96" s="8" t="n">
-        <v>45700</v>
-      </c>
-      <c r="O96" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P96" s="8" t="n">
-        <v>45793.6939930556</v>
-      </c>
+        <v>46031.3055439815</v>
+      </c>
+      <c r="O96" s="7"/>
+      <c r="P96" s="8"/>
     </row>
     <row r="97" customHeight="1" ht="20">
       <c r="A97" s="5" t="n">
-        <v>861</v>
+        <v>681</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>1823</v>
+        <v>1647</v>
       </c>
       <c r="C97" s="6" t="n">
-        <v>46122</v>
+        <v>46138</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>46132</v>
+        <v>46144</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>2290</v>
+        <v>1160</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>2290</v>
+        <v>1160</v>
       </c>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
@@ -3942,32 +3938,36 @@
         <v>19</v>
       </c>
       <c r="N97" s="8" t="n">
-        <v>46031.3055439815</v>
-      </c>
-      <c r="O97" s="7"/>
-      <c r="P97" s="8"/>
+        <v>45793</v>
+      </c>
+      <c r="O97" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="P97" s="8" t="n">
+        <v>45958.4886226852</v>
+      </c>
     </row>
     <row r="98" customHeight="1" ht="20">
       <c r="A98" s="5" t="n">
-        <v>681</v>
+        <v>762</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>1647</v>
+        <v>1724</v>
       </c>
       <c r="C98" s="6" t="n">
-        <v>46138</v>
+        <v>46021</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>46144</v>
+        <v>46026</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>1160</v>
+        <v>990</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>1160</v>
+        <v>990</v>
       </c>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
@@ -3978,27 +3978,27 @@
         <v>19</v>
       </c>
       <c r="N98" s="8" t="n">
-        <v>45793</v>
+        <v>45963</v>
       </c>
       <c r="O98" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P98" s="8" t="n">
-        <v>45958.4886226852</v>
+        <v>46030.6411574074</v>
       </c>
     </row>
     <row r="99" customHeight="1" ht="20">
       <c r="A99" s="5" t="n">
-        <v>762</v>
+        <v>621</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>1724</v>
+        <v>1683</v>
       </c>
       <c r="C99" s="6" t="n">
-        <v>46021</v>
+        <v>45950</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>46026</v>
+        <v>45955</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>18</v>
@@ -4018,36 +4018,36 @@
         <v>19</v>
       </c>
       <c r="N99" s="8" t="n">
-        <v>45963</v>
+        <v>45908</v>
       </c>
       <c r="O99" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P99" s="8" t="n">
-        <v>46030.6411574074</v>
+        <v>45951.6467939815</v>
       </c>
     </row>
     <row r="100" customHeight="1" ht="20">
       <c r="A100" s="5" t="n">
-        <v>621</v>
+        <v>781</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>1683</v>
+        <v>1743</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>45950</v>
+        <v>46020</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>45955</v>
+        <v>46025</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>990</v>
+        <v>1</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>990</v>
+        <v>1</v>
       </c>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
@@ -4058,36 +4058,36 @@
         <v>19</v>
       </c>
       <c r="N100" s="8" t="n">
-        <v>45908</v>
+        <v>45964</v>
       </c>
       <c r="O100" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P100" s="8" t="n">
-        <v>45951.6467939815</v>
+        <v>46030.6409490741</v>
       </c>
     </row>
     <row r="101" customHeight="1" ht="20">
       <c r="A101" s="5" t="n">
-        <v>781</v>
+        <v>801</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>1743</v>
+        <v>1763</v>
       </c>
       <c r="C101" s="6" t="n">
-        <v>46020</v>
+        <v>46137</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>46025</v>
+        <v>46143</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
@@ -4098,36 +4098,32 @@
         <v>19</v>
       </c>
       <c r="N101" s="8" t="n">
-        <v>45964</v>
-      </c>
-      <c r="O101" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P101" s="8" t="n">
-        <v>46030.6409490741</v>
-      </c>
+        <v>45981.7479166667</v>
+      </c>
+      <c r="O101" s="7"/>
+      <c r="P101" s="8"/>
     </row>
     <row r="102" customHeight="1" ht="20">
       <c r="A102" s="5" t="n">
-        <v>801</v>
+        <v>1</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>1763</v>
+        <v>1</v>
       </c>
       <c r="C102" s="6" t="n">
-        <v>46137</v>
+        <v>43505</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>46143</v>
+        <v>43506</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
@@ -4135,29 +4131,33 @@
       <c r="K102" s="5"/>
       <c r="L102" s="7"/>
       <c r="M102" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N102" s="8" t="n">
-        <v>45981.7479166667</v>
-      </c>
-      <c r="O102" s="7"/>
-      <c r="P102" s="8"/>
+        <v>44420</v>
+      </c>
+      <c r="O102" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P102" s="8" t="n">
+        <v>44853.7957060185</v>
+      </c>
     </row>
     <row r="103" customHeight="1" ht="20">
       <c r="A103" s="5" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C103" s="6" t="n">
-        <v>43505</v>
+        <v>44345</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>43506</v>
+        <v>44346</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F103" s="5" t="n">
         <v>230</v>
@@ -4174,30 +4174,26 @@
         <v>17</v>
       </c>
       <c r="N103" s="8" t="n">
-        <v>44420</v>
-      </c>
-      <c r="O103" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P103" s="8" t="n">
-        <v>44853.7957060185</v>
-      </c>
+        <v>44445.5079513889</v>
+      </c>
+      <c r="O103" s="7"/>
+      <c r="P103" s="8"/>
     </row>
     <row r="104" customHeight="1" ht="20">
       <c r="A104" s="5" t="n">
         <v>54</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C104" s="6" t="n">
-        <v>44345</v>
+        <v>44464</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>44346</v>
+        <v>44465</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F104" s="5" t="n">
         <v>230</v>
@@ -4214,26 +4210,30 @@
         <v>17</v>
       </c>
       <c r="N104" s="8" t="n">
-        <v>44445.5079513889</v>
-      </c>
-      <c r="O104" s="7"/>
-      <c r="P104" s="8"/>
+        <v>44445</v>
+      </c>
+      <c r="O104" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P104" s="8" t="n">
+        <v>44764.5626388889</v>
+      </c>
     </row>
     <row r="105" customHeight="1" ht="20">
       <c r="A105" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C105" s="6" t="n">
-        <v>44464</v>
+        <v>44474</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>44465</v>
+        <v>44475</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F105" s="5" t="n">
         <v>230</v>
@@ -4250,30 +4250,30 @@
         <v>17</v>
       </c>
       <c r="N105" s="8" t="n">
-        <v>44445</v>
+        <v>44446.2805902778</v>
       </c>
       <c r="O105" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P105" s="8" t="n">
-        <v>44764.5626388889</v>
+        <v>44586.645775463</v>
       </c>
     </row>
     <row r="106" customHeight="1" ht="20">
       <c r="A106" s="5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C106" s="6" t="n">
-        <v>44474</v>
+        <v>43603</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>44475</v>
+        <v>43604</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F106" s="5" t="n">
         <v>230</v>
@@ -4290,36 +4290,36 @@
         <v>17</v>
       </c>
       <c r="N106" s="8" t="n">
-        <v>44446.2805902778</v>
+        <v>44446</v>
       </c>
       <c r="O106" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P106" s="8" t="n">
-        <v>44586.645775463</v>
+        <v>44764.6144791667</v>
       </c>
     </row>
     <row r="107" customHeight="1" ht="20">
       <c r="A107" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C107" s="6" t="n">
-        <v>43603</v>
+        <v>43506</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>43604</v>
+        <v>43506</v>
       </c>
       <c r="E107" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
@@ -4336,7 +4336,7 @@
         <v>17</v>
       </c>
       <c r="P107" s="8" t="n">
-        <v>44764.6144791667</v>
+        <v>44767.5292824074</v>
       </c>
     </row>
     <row r="108" customHeight="1" ht="20">
@@ -4344,13 +4344,13 @@
         <v>52</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C108" s="6" t="n">
-        <v>43506</v>
+        <v>43877</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>43506</v>
+        <v>43877</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>18</v>
@@ -4376,30 +4376,30 @@
         <v>17</v>
       </c>
       <c r="P108" s="8" t="n">
-        <v>44767.5292824074</v>
+        <v>44767.5397337963</v>
       </c>
     </row>
     <row r="109" customHeight="1" ht="20">
       <c r="A109" s="5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C109" s="6" t="n">
-        <v>43877</v>
+        <v>44170</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>43877</v>
+        <v>44173</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>130</v>
+        <v>495</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>30</v>
+        <v>310</v>
       </c>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
@@ -4410,36 +4410,32 @@
         <v>17</v>
       </c>
       <c r="N109" s="8" t="n">
-        <v>44446</v>
-      </c>
-      <c r="O109" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P109" s="8" t="n">
-        <v>44767.5397337963</v>
-      </c>
+        <v>44446.5258333333</v>
+      </c>
+      <c r="O109" s="7"/>
+      <c r="P109" s="8"/>
     </row>
     <row r="110" customHeight="1" ht="20">
       <c r="A110" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B110" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="B110" s="5" t="n">
-        <v>50</v>
-      </c>
       <c r="C110" s="6" t="n">
-        <v>44170</v>
+        <v>44331</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>44173</v>
+        <v>44332</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>495</v>
+        <v>230</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>310</v>
+        <v>130</v>
       </c>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
@@ -4450,32 +4446,36 @@
         <v>17</v>
       </c>
       <c r="N110" s="8" t="n">
-        <v>44446.5258333333</v>
-      </c>
-      <c r="O110" s="7"/>
-      <c r="P110" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P110" s="8" t="n">
+        <v>44785.5036921296</v>
+      </c>
     </row>
     <row r="111" customHeight="1" ht="20">
       <c r="A111" s="5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C111" s="6" t="n">
-        <v>44331</v>
+        <v>43554</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>44332</v>
+        <v>43554</v>
       </c>
       <c r="E111" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
@@ -4492,30 +4492,30 @@
         <v>17</v>
       </c>
       <c r="P111" s="8" t="n">
-        <v>44785.5036921296</v>
+        <v>44785.5278240741</v>
       </c>
     </row>
     <row r="112" customHeight="1" ht="20">
       <c r="A112" s="5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C112" s="6" t="n">
-        <v>43554</v>
+        <v>43764</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>43554</v>
+        <v>43765</v>
       </c>
       <c r="E112" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F112" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="G112" s="5" t="n">
         <v>130</v>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
@@ -4532,7 +4532,7 @@
         <v>17</v>
       </c>
       <c r="P112" s="8" t="n">
-        <v>44785.5278240741</v>
+        <v>44785.5824074074</v>
       </c>
     </row>
     <row r="113" customHeight="1" ht="20">
@@ -4540,13 +4540,13 @@
         <v>48</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C113" s="6" t="n">
-        <v>43764</v>
+        <v>43862</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>43765</v>
+        <v>43863</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>18</v>
@@ -4572,7 +4572,7 @@
         <v>17</v>
       </c>
       <c r="P113" s="8" t="n">
-        <v>44785.5824074074</v>
+        <v>44785.5965856481</v>
       </c>
     </row>
     <row r="114" customHeight="1" ht="20">
@@ -4580,13 +4580,13 @@
         <v>48</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C114" s="6" t="n">
-        <v>43862</v>
+        <v>44009</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>43863</v>
+        <v>44010</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>18</v>
@@ -4612,7 +4612,7 @@
         <v>17</v>
       </c>
       <c r="P114" s="8" t="n">
-        <v>44785.5965856481</v>
+        <v>44785.6159259259</v>
       </c>
     </row>
     <row r="115" customHeight="1" ht="20">
@@ -4620,13 +4620,13 @@
         <v>48</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C115" s="6" t="n">
-        <v>44009</v>
+        <v>44100</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>44010</v>
+        <v>44101</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>18</v>
@@ -4652,21 +4652,21 @@
         <v>17</v>
       </c>
       <c r="P115" s="8" t="n">
-        <v>44785.6159259259</v>
+        <v>44792.5683217593</v>
       </c>
     </row>
     <row r="116" customHeight="1" ht="20">
       <c r="A116" s="5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C116" s="6" t="n">
-        <v>44100</v>
+        <v>44338</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>44101</v>
+        <v>44339</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>18</v>
@@ -4692,21 +4692,21 @@
         <v>17</v>
       </c>
       <c r="P116" s="8" t="n">
-        <v>44792.5683217593</v>
+        <v>44792.5857291667</v>
       </c>
     </row>
     <row r="117" customHeight="1" ht="20">
       <c r="A117" s="5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C117" s="6" t="n">
-        <v>44338</v>
+        <v>44107</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>44339</v>
+        <v>44108</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>18</v>
@@ -4732,7 +4732,7 @@
         <v>17</v>
       </c>
       <c r="P117" s="8" t="n">
-        <v>44792.5857291667</v>
+        <v>44819.4365393519</v>
       </c>
     </row>
     <row r="118" customHeight="1" ht="20">
@@ -4740,13 +4740,13 @@
         <v>46</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C118" s="6" t="n">
-        <v>44107</v>
+        <v>44401</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>44108</v>
+        <v>44402</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>18</v>
@@ -4772,30 +4772,30 @@
         <v>17</v>
       </c>
       <c r="P118" s="8" t="n">
-        <v>44819.4365393519</v>
+        <v>44819.4539351852</v>
       </c>
     </row>
     <row r="119" customHeight="1" ht="20">
       <c r="A119" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C119" s="6" t="n">
-        <v>44401</v>
+        <v>43769</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>44402</v>
+        <v>43772</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>230</v>
+        <v>495</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>130</v>
+        <v>245</v>
       </c>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
@@ -4812,21 +4812,21 @@
         <v>17</v>
       </c>
       <c r="P119" s="8" t="n">
-        <v>44819.4539351852</v>
+        <v>44819.5838773148</v>
       </c>
     </row>
     <row r="120" customHeight="1" ht="20">
       <c r="A120" s="5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C120" s="6" t="n">
-        <v>43769</v>
+        <v>44498</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>43772</v>
+        <v>44501</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>18</v>
@@ -4835,7 +4835,7 @@
         <v>495</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>245</v>
+        <v>310</v>
       </c>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
@@ -4852,30 +4852,30 @@
         <v>17</v>
       </c>
       <c r="P120" s="8" t="n">
-        <v>44819.5838773148</v>
+        <v>44837.6617939815</v>
       </c>
     </row>
     <row r="121" customHeight="1" ht="20">
       <c r="A121" s="5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C121" s="6" t="n">
-        <v>44498</v>
+        <v>43981</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>44501</v>
+        <v>43989</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>495</v>
+        <v>1050</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>310</v>
+        <v>580</v>
       </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
@@ -4886,36 +4886,32 @@
         <v>17</v>
       </c>
       <c r="N121" s="8" t="n">
-        <v>44446</v>
-      </c>
-      <c r="O121" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P121" s="8" t="n">
-        <v>44837.6617939815</v>
-      </c>
+        <v>44446.5351157407</v>
+      </c>
+      <c r="O121" s="7"/>
+      <c r="P121" s="8"/>
     </row>
     <row r="122" customHeight="1" ht="20">
       <c r="A122" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>43981</v>
+        <v>44450</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>43989</v>
+        <v>44457</v>
       </c>
       <c r="E122" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>1050</v>
+        <v>970</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>580</v>
+        <v>690</v>
       </c>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
@@ -4926,32 +4922,32 @@
         <v>17</v>
       </c>
       <c r="N122" s="8" t="n">
-        <v>44446.5351157407</v>
+        <v>44446.5361226852</v>
       </c>
       <c r="O122" s="7"/>
       <c r="P122" s="8"/>
     </row>
     <row r="123" customHeight="1" ht="20">
       <c r="A123" s="5" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C123" s="6" t="n">
-        <v>44450</v>
+        <v>44023</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>44457</v>
+        <v>44029</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>970</v>
+        <v>790</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>690</v>
+        <v>570</v>
       </c>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
@@ -4962,32 +4958,32 @@
         <v>17</v>
       </c>
       <c r="N123" s="8" t="n">
-        <v>44446.5361226852</v>
+        <v>44446.5370138889</v>
       </c>
       <c r="O123" s="7"/>
       <c r="P123" s="8"/>
     </row>
     <row r="124" customHeight="1" ht="20">
       <c r="A124" s="5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C124" s="6" t="n">
-        <v>44023</v>
+        <v>43575</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>44029</v>
+        <v>43581</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>790</v>
+        <v>860</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
@@ -4998,7 +4994,7 @@
         <v>17</v>
       </c>
       <c r="N124" s="8" t="n">
-        <v>44446.5370138889</v>
+        <v>44446.5379398148</v>
       </c>
       <c r="O124" s="7"/>
       <c r="P124" s="8"/>
@@ -5008,22 +5004,22 @@
         <v>25</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C125" s="6" t="n">
-        <v>43575</v>
+        <v>44284</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>43581</v>
+        <v>44290</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>550</v>
+        <v>590</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
@@ -5034,7 +5030,7 @@
         <v>17</v>
       </c>
       <c r="N125" s="8" t="n">
-        <v>44446.5379398148</v>
+        <v>44446.5387268519</v>
       </c>
       <c r="O125" s="7"/>
       <c r="P125" s="8"/>
@@ -5044,22 +5040,22 @@
         <v>25</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C126" s="6" t="n">
-        <v>44284</v>
+        <v>44665</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>44290</v>
+        <v>44671</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>890</v>
+        <v>1150</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>590</v>
+        <v>770</v>
       </c>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
@@ -5070,32 +5066,36 @@
         <v>17</v>
       </c>
       <c r="N126" s="8" t="n">
-        <v>44446.5387268519</v>
-      </c>
-      <c r="O126" s="7"/>
-      <c r="P126" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O126" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P126" s="8" t="n">
+        <v>44676.391724537</v>
+      </c>
     </row>
     <row r="127" customHeight="1" ht="20">
       <c r="A127" s="5" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="C127" s="6" t="n">
-        <v>44665</v>
+        <v>44653</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>44671</v>
+        <v>44653</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>1150</v>
+        <v>130</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>770</v>
+        <v>30</v>
       </c>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
@@ -5106,36 +5106,32 @@
         <v>17</v>
       </c>
       <c r="N127" s="8" t="n">
-        <v>44446</v>
-      </c>
-      <c r="O127" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P127" s="8" t="n">
-        <v>44676.391724537</v>
-      </c>
+        <v>44646.3677199074</v>
+      </c>
+      <c r="O127" s="7"/>
+      <c r="P127" s="8"/>
     </row>
     <row r="128" customHeight="1" ht="20">
       <c r="A128" s="5" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>263</v>
+        <v>84</v>
       </c>
       <c r="C128" s="6" t="n">
-        <v>44653</v>
+        <v>44359</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>44653</v>
+        <v>44360</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F128" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="G128" s="5" t="n">
         <v>130</v>
-      </c>
-      <c r="G128" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
@@ -5146,101 +5142,105 @@
         <v>17</v>
       </c>
       <c r="N128" s="8" t="n">
-        <v>44646.3677199074</v>
+        <v>44446.542337963</v>
       </c>
       <c r="O128" s="7"/>
       <c r="P128" s="8"/>
     </row>
     <row r="129" customHeight="1" ht="20">
       <c r="A129" s="5" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C129" s="6" t="n">
-        <v>44359</v>
+        <v>44450</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>44360</v>
+        <v>44453</v>
       </c>
       <c r="E129" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>230</v>
+        <v>830</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
       <c r="K129" s="5"/>
-      <c r="L129" s="7"/>
+      <c r="L129" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="M129" s="7" t="s">
         <v>17</v>
       </c>
       <c r="N129" s="8" t="n">
-        <v>44446.542337963</v>
-      </c>
-      <c r="O129" s="7"/>
-      <c r="P129" s="8"/>
+        <v>44447</v>
+      </c>
+      <c r="O129" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P129" s="8" t="n">
+        <v>44837.6220949074</v>
+      </c>
     </row>
     <row r="130" customHeight="1" ht="20">
       <c r="A130" s="5" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>85</v>
+        <v>342</v>
       </c>
       <c r="C130" s="6" t="n">
-        <v>44450</v>
+        <v>44723</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>44453</v>
+        <v>44724</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>830</v>
+        <v>245</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
       <c r="K130" s="5"/>
-      <c r="L130" s="7" t="s">
-        <v>21</v>
-      </c>
+      <c r="L130" s="7"/>
       <c r="M130" s="7" t="s">
         <v>17</v>
       </c>
       <c r="N130" s="8" t="n">
-        <v>44447</v>
+        <v>44665</v>
       </c>
       <c r="O130" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P130" s="8" t="n">
-        <v>44837.6220949074</v>
+        <v>44731.4374652778</v>
       </c>
     </row>
     <row r="131" customHeight="1" ht="20">
       <c r="A131" s="5" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>342</v>
+        <v>422</v>
       </c>
       <c r="C131" s="6" t="n">
-        <v>44723</v>
+        <v>44828</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>44724</v>
+        <v>44829</v>
       </c>
       <c r="E131" s="7" t="s">
         <v>18</v>
@@ -5260,27 +5260,27 @@
         <v>17</v>
       </c>
       <c r="N131" s="8" t="n">
-        <v>44665</v>
+        <v>44748</v>
       </c>
       <c r="O131" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P131" s="8" t="n">
-        <v>44731.4374652778</v>
+        <v>44830.3892361111</v>
       </c>
     </row>
     <row r="132" customHeight="1" ht="20">
       <c r="A132" s="5" t="n">
-        <v>48</v>
+        <v>181</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>422</v>
+        <v>502</v>
       </c>
       <c r="C132" s="6" t="n">
-        <v>44828</v>
+        <v>44849</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>44829</v>
+        <v>44850</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>18</v>
@@ -5300,36 +5300,36 @@
         <v>17</v>
       </c>
       <c r="N132" s="8" t="n">
-        <v>44748</v>
+        <v>44810</v>
       </c>
       <c r="O132" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P132" s="8" t="n">
-        <v>44830.3892361111</v>
+        <v>44847.397962963</v>
       </c>
     </row>
     <row r="133" customHeight="1" ht="20">
       <c r="A133" s="5" t="n">
-        <v>181</v>
+        <v>48</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>502</v>
+        <v>682</v>
       </c>
       <c r="C133" s="6" t="n">
-        <v>44849</v>
+        <v>44989</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>44850</v>
+        <v>44990</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
@@ -5340,27 +5340,27 @@
         <v>17</v>
       </c>
       <c r="N133" s="8" t="n">
-        <v>44810</v>
+        <v>44970</v>
       </c>
       <c r="O133" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P133" s="8" t="n">
-        <v>44847.397962963</v>
+        <v>44988.7055555556</v>
       </c>
     </row>
     <row r="134" customHeight="1" ht="20">
       <c r="A134" s="5" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>682</v>
+        <v>702</v>
       </c>
       <c r="C134" s="6" t="n">
-        <v>44989</v>
+        <v>44996</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>44990</v>
+        <v>44997</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>18</v>
@@ -5380,36 +5380,36 @@
         <v>17</v>
       </c>
       <c r="N134" s="8" t="n">
-        <v>44970</v>
+        <v>44986</v>
       </c>
       <c r="O134" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P134" s="8" t="n">
-        <v>44988.7055555556</v>
+        <v>44998.346400463</v>
       </c>
     </row>
     <row r="135" customHeight="1" ht="20">
       <c r="A135" s="5" t="n">
-        <v>81</v>
+        <v>281</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>702</v>
+        <v>822</v>
       </c>
       <c r="C135" s="6" t="n">
-        <v>44996</v>
+        <v>45227</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>44997</v>
+        <v>45230</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>250</v>
+        <v>540</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>150</v>
+        <v>345</v>
       </c>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
@@ -5420,36 +5420,36 @@
         <v>17</v>
       </c>
       <c r="N135" s="8" t="n">
-        <v>44986</v>
+        <v>45032</v>
       </c>
       <c r="O135" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P135" s="8" t="n">
-        <v>44998.346400463</v>
+        <v>45231.536724537</v>
       </c>
     </row>
     <row r="136" customHeight="1" ht="20">
       <c r="A136" s="5" t="n">
-        <v>281</v>
+        <v>361</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>822</v>
+        <v>902</v>
       </c>
       <c r="C136" s="6" t="n">
-        <v>45227</v>
+        <v>45074</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>45230</v>
+        <v>45078</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>540</v>
+        <v>695</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>345</v>
+        <v>495</v>
       </c>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
@@ -5460,36 +5460,36 @@
         <v>17</v>
       </c>
       <c r="N136" s="8" t="n">
-        <v>45032</v>
+        <v>45069</v>
       </c>
       <c r="O136" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P136" s="8" t="n">
-        <v>45231.536724537</v>
+        <v>45071.3412962963</v>
       </c>
     </row>
     <row r="137" customHeight="1" ht="20">
       <c r="A137" s="5" t="n">
-        <v>361</v>
+        <v>401</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>902</v>
+        <v>982</v>
       </c>
       <c r="C137" s="6" t="n">
-        <v>45074</v>
+        <v>45129</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>45078</v>
+        <v>45132</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>695</v>
+        <v>670</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>495</v>
+        <v>380</v>
       </c>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
@@ -5500,36 +5500,32 @@
         <v>17</v>
       </c>
       <c r="N137" s="8" t="n">
-        <v>45069</v>
-      </c>
-      <c r="O137" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P137" s="8" t="n">
-        <v>45071.3412962963</v>
-      </c>
+        <v>45111.2535763889</v>
+      </c>
+      <c r="O137" s="7"/>
+      <c r="P137" s="8"/>
     </row>
     <row r="138" customHeight="1" ht="20">
       <c r="A138" s="5" t="n">
-        <v>401</v>
+        <v>41</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>982</v>
+        <v>1062</v>
       </c>
       <c r="C138" s="6" t="n">
-        <v>45129</v>
+        <v>45206</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>45132</v>
+        <v>45214</v>
       </c>
       <c r="E138" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>670</v>
+        <v>1100</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>380</v>
+        <v>710</v>
       </c>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
@@ -5540,32 +5536,32 @@
         <v>17</v>
       </c>
       <c r="N138" s="8" t="n">
-        <v>45111.2535763889</v>
+        <v>45171.606875</v>
       </c>
       <c r="O138" s="7"/>
       <c r="P138" s="8"/>
     </row>
     <row r="139" customHeight="1" ht="20">
       <c r="A139" s="5" t="n">
-        <v>41</v>
+        <v>461</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>1062</v>
+        <v>1302</v>
       </c>
       <c r="C139" s="6" t="n">
-        <v>45206</v>
+        <v>45346</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>45214</v>
+        <v>45347</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>1100</v>
+        <v>250</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>710</v>
+        <v>150</v>
       </c>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
@@ -5576,32 +5572,36 @@
         <v>17</v>
       </c>
       <c r="N139" s="8" t="n">
-        <v>45171.606875</v>
-      </c>
-      <c r="O139" s="7"/>
-      <c r="P139" s="8"/>
+        <v>45308</v>
+      </c>
+      <c r="O139" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P139" s="8" t="n">
+        <v>45345.4013194444</v>
+      </c>
     </row>
     <row r="140" customHeight="1" ht="20">
       <c r="A140" s="5" t="n">
-        <v>461</v>
+        <v>541</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>1302</v>
+        <v>1503</v>
       </c>
       <c r="C140" s="6" t="n">
-        <v>45346</v>
+        <v>45594</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>45347</v>
+        <v>45598</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>250</v>
+        <v>690</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>150</v>
+        <v>690</v>
       </c>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
@@ -5609,39 +5609,39 @@
       <c r="K140" s="5"/>
       <c r="L140" s="7"/>
       <c r="M140" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N140" s="8" t="n">
-        <v>45308</v>
+        <v>45582</v>
       </c>
       <c r="O140" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P140" s="8" t="n">
-        <v>45345.4013194444</v>
+        <v>45793.6943287037</v>
       </c>
     </row>
     <row r="141" customHeight="1" ht="20">
       <c r="A141" s="5" t="n">
-        <v>541</v>
+        <v>821</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>1503</v>
+        <v>1783</v>
       </c>
       <c r="C141" s="6" t="n">
-        <v>45594</v>
+        <v>45996</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>45598</v>
+        <v>45998</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>690</v>
+        <v>490</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>690</v>
+        <v>490</v>
       </c>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
@@ -5652,36 +5652,32 @@
         <v>19</v>
       </c>
       <c r="N141" s="8" t="n">
-        <v>45582</v>
-      </c>
-      <c r="O141" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P141" s="8" t="n">
-        <v>45793.6943287037</v>
-      </c>
+        <v>45983.3458449074</v>
+      </c>
+      <c r="O141" s="7"/>
+      <c r="P141" s="8"/>
     </row>
     <row r="142" customHeight="1" ht="20">
       <c r="A142" s="5" t="n">
-        <v>821</v>
+        <v>541</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>1783</v>
+        <v>1664</v>
       </c>
       <c r="C142" s="6" t="n">
-        <v>45996</v>
+        <v>45915</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>45998</v>
+        <v>45919</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
@@ -5692,48 +5688,12 @@
         <v>19</v>
       </c>
       <c r="N142" s="8" t="n">
-        <v>45983.3458449074</v>
-      </c>
-      <c r="O142" s="7"/>
-      <c r="P142" s="8"/>
-    </row>
-    <row r="143" customHeight="1" ht="20">
-      <c r="A143" s="5" t="n">
-        <v>541</v>
-      </c>
-      <c r="B143" s="5" t="n">
-        <v>1664</v>
-      </c>
-      <c r="C143" s="6" t="n">
-        <v>45915</v>
-      </c>
-      <c r="D143" s="6" t="n">
-        <v>45919</v>
-      </c>
-      <c r="E143" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F143" s="5" t="n">
-        <v>690</v>
-      </c>
-      <c r="G143" s="5" t="n">
-        <v>690</v>
-      </c>
-      <c r="H143" s="5"/>
-      <c r="I143" s="5"/>
-      <c r="J143" s="5"/>
-      <c r="K143" s="5"/>
-      <c r="L143" s="7"/>
-      <c r="M143" s="7" t="s">
+        <v>45811</v>
+      </c>
+      <c r="O142" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="N143" s="8" t="n">
-        <v>45811</v>
-      </c>
-      <c r="O143" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P143" s="8" t="n">
+      <c r="P142" s="8" t="n">
         <v>45951.6466550926</v>
       </c>
     </row>

--- a/inp_Excel/ana_date_viaggi.xlsx
+++ b/inp_Excel/ana_date_viaggi.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="22">
   <si>
     <t>VIAGGIO_ID_FK</t>
   </si>
@@ -178,8 +178,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:P142" totalsRowShown="0" headerRowCount="1">
-  <autoFilter ref="A1:P142"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" displayName="foglio1" ref="A1:P144" totalsRowShown="0" headerRowCount="1">
+  <autoFilter ref="A1:P144"/>
   <tableColumns count="16">
     <tableColumn id="1" name="VIAGGIO_ID_FK"/>
     <tableColumn id="2" name="DATA_VIAGGIO_ID"/>
@@ -1271,10 +1271,10 @@
         <v>1784</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>46045</v>
+        <v>46066</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>46047</v>
+        <v>46068</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>16</v>
@@ -1294,10 +1294,14 @@
         <v>19</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>45983.3522106481</v>
-      </c>
-      <c r="O28" s="7"/>
-      <c r="P28" s="8"/>
+        <v>45983</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>46053.8093518519</v>
+      </c>
     </row>
     <row r="29" customHeight="1" ht="20">
       <c r="A29" s="5" t="n">
@@ -1997,13 +2001,13 @@
         <v>1584</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>45774</v>
+        <v>46160</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>45780</v>
+        <v>46165</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F47" s="5" t="n">
         <v>1060</v>
@@ -2026,7 +2030,7 @@
         <v>19</v>
       </c>
       <c r="P47" s="8" t="n">
-        <v>45793.6937847222</v>
+        <v>46053.8084606481</v>
       </c>
     </row>
     <row r="48" customHeight="1" ht="20">
@@ -2727,25 +2731,25 @@
     </row>
     <row r="66" customHeight="1" ht="20">
       <c r="A66" s="5" t="n">
-        <v>1</v>
+        <v>901</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>24</v>
+        <v>1863</v>
       </c>
       <c r="C66" s="6" t="n">
-        <v>44324</v>
+        <v>46106</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>44325</v>
+        <v>46109</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>230</v>
+        <v>590</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>130</v>
+        <v>590</v>
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
@@ -2753,26 +2757,26 @@
       <c r="K66" s="5"/>
       <c r="L66" s="7"/>
       <c r="M66" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N66" s="8" t="n">
-        <v>44420.5177546296</v>
+        <v>46053.8152199074</v>
       </c>
       <c r="O66" s="7"/>
       <c r="P66" s="8"/>
     </row>
     <row r="67" customHeight="1" ht="20">
       <c r="A67" s="5" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C67" s="6" t="n">
-        <v>43995</v>
+        <v>44324</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>43996</v>
+        <v>44325</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>18</v>
@@ -2792,7 +2796,7 @@
         <v>17</v>
       </c>
       <c r="N67" s="8" t="n">
-        <v>44420.5183796296</v>
+        <v>44420.5177546296</v>
       </c>
       <c r="O67" s="7"/>
       <c r="P67" s="8"/>
@@ -2802,13 +2806,13 @@
         <v>22</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C68" s="6" t="n">
-        <v>44121</v>
+        <v>43995</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>44122</v>
+        <v>43996</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>18</v>
@@ -2828,32 +2832,32 @@
         <v>17</v>
       </c>
       <c r="N68" s="8" t="n">
-        <v>44420.5187268519</v>
+        <v>44420.5183796296</v>
       </c>
       <c r="O68" s="7"/>
       <c r="P68" s="8"/>
     </row>
     <row r="69" customHeight="1" ht="20">
       <c r="A69" s="5" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C69" s="6" t="n">
-        <v>44149</v>
+        <v>44121</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>44149</v>
+        <v>44122</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F69" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="G69" s="5" t="n">
         <v>130</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
@@ -2864,26 +2868,26 @@
         <v>17</v>
       </c>
       <c r="N69" s="8" t="n">
-        <v>44446.5248032407</v>
+        <v>44420.5187268519</v>
       </c>
       <c r="O69" s="7"/>
       <c r="P69" s="8"/>
     </row>
     <row r="70" customHeight="1" ht="20">
       <c r="A70" s="5" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C70" s="6" t="n">
-        <v>44492</v>
+        <v>44149</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>44492</v>
+        <v>44149</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>130</v>
@@ -2900,36 +2904,32 @@
         <v>17</v>
       </c>
       <c r="N70" s="8" t="n">
-        <v>44446</v>
-      </c>
-      <c r="O70" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P70" s="8" t="n">
-        <v>44785.5593287037</v>
-      </c>
+        <v>44446.5248032407</v>
+      </c>
+      <c r="O70" s="7"/>
+      <c r="P70" s="8"/>
     </row>
     <row r="71" customHeight="1" ht="20">
       <c r="A71" s="5" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C71" s="6" t="n">
-        <v>44133</v>
+        <v>44492</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>44136</v>
+        <v>44492</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>520</v>
+        <v>130</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
@@ -2946,30 +2946,30 @@
         <v>17</v>
       </c>
       <c r="P71" s="8" t="n">
-        <v>44847.4125231481</v>
+        <v>44785.5593287037</v>
       </c>
     </row>
     <row r="72" customHeight="1" ht="20">
       <c r="A72" s="5" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>43690</v>
+        <v>44133</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>43697</v>
+        <v>44136</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>780</v>
+        <v>520</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>560</v>
+        <v>280</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
@@ -2980,32 +2980,36 @@
         <v>17</v>
       </c>
       <c r="N72" s="8" t="n">
-        <v>44446.5365856481</v>
-      </c>
-      <c r="O72" s="7"/>
-      <c r="P72" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P72" s="8" t="n">
+        <v>44847.4125231481</v>
+      </c>
     </row>
     <row r="73" customHeight="1" ht="20">
       <c r="A73" s="5" t="n">
         <v>27</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C73" s="6" t="n">
-        <v>44380</v>
+        <v>43690</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>44386</v>
+        <v>43697</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>820</v>
+        <v>780</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
@@ -3016,32 +3020,32 @@
         <v>17</v>
       </c>
       <c r="N73" s="8" t="n">
-        <v>44446.5373958333</v>
+        <v>44446.5365856481</v>
       </c>
       <c r="O73" s="7"/>
       <c r="P73" s="8"/>
     </row>
     <row r="74" customHeight="1" ht="20">
       <c r="A74" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C74" s="6" t="n">
-        <v>43932</v>
+        <v>44380</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>43938</v>
+        <v>44386</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>890</v>
+        <v>820</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
@@ -3052,7 +3056,7 @@
         <v>17</v>
       </c>
       <c r="N74" s="8" t="n">
-        <v>44446.5383217593</v>
+        <v>44446.5373958333</v>
       </c>
       <c r="O74" s="7"/>
       <c r="P74" s="8"/>
@@ -3062,22 +3066,22 @@
         <v>25</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C75" s="6" t="n">
-        <v>44380</v>
+        <v>43932</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>44386</v>
+        <v>43938</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F75" s="5" t="n">
         <v>890</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
@@ -3088,32 +3092,32 @@
         <v>17</v>
       </c>
       <c r="N75" s="8" t="n">
-        <v>44446.5391898148</v>
+        <v>44446.5383217593</v>
       </c>
       <c r="O75" s="7"/>
       <c r="P75" s="8"/>
     </row>
     <row r="76" customHeight="1" ht="20">
       <c r="A76" s="5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="C76" s="6" t="n">
-        <v>44611</v>
+        <v>44380</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>44612</v>
+        <v>44386</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>245</v>
+        <v>890</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>140</v>
+        <v>590</v>
       </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
@@ -3124,36 +3128,32 @@
         <v>17</v>
       </c>
       <c r="N76" s="8" t="n">
-        <v>44603</v>
-      </c>
-      <c r="O76" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P76" s="8" t="n">
-        <v>44620.6170717593</v>
-      </c>
+        <v>44446.5391898148</v>
+      </c>
+      <c r="O76" s="7"/>
+      <c r="P76" s="8"/>
     </row>
     <row r="77" customHeight="1" ht="20">
       <c r="A77" s="5" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>302</v>
+        <v>182</v>
       </c>
       <c r="C77" s="6" t="n">
-        <v>44786</v>
+        <v>44611</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>44797</v>
+        <v>44612</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>1440</v>
+        <v>245</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>990</v>
+        <v>140</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
@@ -3164,32 +3164,36 @@
         <v>17</v>
       </c>
       <c r="N77" s="8" t="n">
-        <v>44655.6645833333</v>
-      </c>
-      <c r="O77" s="7"/>
-      <c r="P77" s="8"/>
+        <v>44603</v>
+      </c>
+      <c r="O77" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P77" s="8" t="n">
+        <v>44620.6170717593</v>
+      </c>
     </row>
     <row r="78" customHeight="1" ht="20">
       <c r="A78" s="5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>363</v>
+        <v>302</v>
       </c>
       <c r="C78" s="6" t="n">
-        <v>44737</v>
+        <v>44786</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>44743</v>
+        <v>44797</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>890</v>
+        <v>1440</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>590</v>
+        <v>990</v>
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
@@ -3200,40 +3204,34 @@
         <v>17</v>
       </c>
       <c r="N78" s="8" t="n">
-        <v>44679</v>
-      </c>
-      <c r="O78" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P78" s="8" t="n">
-        <v>44745.8054282407</v>
-      </c>
+        <v>44655.6645833333</v>
+      </c>
+      <c r="O78" s="7"/>
+      <c r="P78" s="8"/>
     </row>
     <row r="79" customHeight="1" ht="20">
       <c r="A79" s="5" t="n">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>462</v>
+        <v>363</v>
       </c>
       <c r="C79" s="6" t="n">
-        <v>44898</v>
+        <v>44737</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>44907</v>
+        <v>44743</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>1600</v>
+        <v>890</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1350</v>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>1550</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="H79" s="5"/>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
@@ -3242,38 +3240,40 @@
         <v>17</v>
       </c>
       <c r="N79" s="8" t="n">
-        <v>44791</v>
+        <v>44679</v>
       </c>
       <c r="O79" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P79" s="8" t="n">
-        <v>44915.6469675926</v>
+        <v>44745.8054282407</v>
       </c>
     </row>
     <row r="80" customHeight="1" ht="20">
       <c r="A80" s="5" t="n">
-        <v>201</v>
+        <v>141</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>522</v>
+        <v>462</v>
       </c>
       <c r="C80" s="6" t="n">
-        <v>44856</v>
+        <v>44898</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>44857</v>
+        <v>44907</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>245</v>
+        <v>1600</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="H80" s="5"/>
+        <v>1350</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>1550</v>
+      </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
@@ -3282,36 +3282,36 @@
         <v>17</v>
       </c>
       <c r="N80" s="8" t="n">
-        <v>44834</v>
+        <v>44791</v>
       </c>
       <c r="O80" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P80" s="8" t="n">
-        <v>44837.3615972222</v>
+        <v>44915.6469675926</v>
       </c>
     </row>
     <row r="81" customHeight="1" ht="20">
       <c r="A81" s="5" t="n">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>742</v>
+        <v>522</v>
       </c>
       <c r="C81" s="6" t="n">
-        <v>45010</v>
+        <v>44856</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>45011</v>
+        <v>44857</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
@@ -3322,36 +3322,36 @@
         <v>17</v>
       </c>
       <c r="N81" s="8" t="n">
-        <v>44994</v>
+        <v>44834</v>
       </c>
       <c r="O81" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P81" s="8" t="n">
-        <v>45012.3928240741</v>
+        <v>44837.3615972222</v>
       </c>
     </row>
     <row r="82" customHeight="1" ht="20">
       <c r="A82" s="5" t="n">
-        <v>23</v>
+        <v>101</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>782</v>
+        <v>742</v>
       </c>
       <c r="C82" s="6" t="n">
-        <v>45115</v>
+        <v>45010</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>45127</v>
+        <v>45011</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>1490</v>
+        <v>250</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>995</v>
+        <v>150</v>
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
@@ -3362,32 +3362,36 @@
         <v>17</v>
       </c>
       <c r="N82" s="8" t="n">
-        <v>45013.6681597222</v>
-      </c>
-      <c r="O82" s="7"/>
-      <c r="P82" s="8"/>
+        <v>44994</v>
+      </c>
+      <c r="O82" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P82" s="8" t="n">
+        <v>45012.3928240741</v>
+      </c>
     </row>
     <row r="83" customHeight="1" ht="20">
       <c r="A83" s="5" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C83" s="6" t="n">
-        <v>45101</v>
+        <v>45115</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>45108</v>
+        <v>45127</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>1100</v>
+        <v>1490</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>710</v>
+        <v>995</v>
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
@@ -3398,32 +3402,32 @@
         <v>17</v>
       </c>
       <c r="N83" s="8" t="n">
-        <v>45013.6687037037</v>
+        <v>45013.6681597222</v>
       </c>
       <c r="O83" s="7"/>
       <c r="P83" s="8"/>
     </row>
     <row r="84" customHeight="1" ht="20">
       <c r="A84" s="5" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>942</v>
+        <v>783</v>
       </c>
       <c r="C84" s="6" t="n">
-        <v>45107</v>
+        <v>45101</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>45109</v>
+        <v>45108</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>180</v>
+        <v>1100</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>100</v>
+        <v>710</v>
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
@@ -3434,36 +3438,32 @@
         <v>17</v>
       </c>
       <c r="N84" s="8" t="n">
-        <v>45080</v>
-      </c>
-      <c r="O84" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P84" s="8" t="n">
-        <v>45111.2536921296</v>
-      </c>
+        <v>45013.6687037037</v>
+      </c>
+      <c r="O84" s="7"/>
+      <c r="P84" s="8"/>
     </row>
     <row r="85" customHeight="1" ht="20">
       <c r="A85" s="5" t="n">
-        <v>381</v>
+        <v>26</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>962</v>
+        <v>942</v>
       </c>
       <c r="C85" s="6" t="n">
-        <v>45110</v>
+        <v>45107</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>45111</v>
+        <v>45109</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
@@ -3474,13 +3474,13 @@
         <v>17</v>
       </c>
       <c r="N85" s="8" t="n">
-        <v>45082</v>
+        <v>45080</v>
       </c>
       <c r="O85" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P85" s="8" t="n">
-        <v>45111.2538310185</v>
+        <v>45111.2536921296</v>
       </c>
     </row>
     <row r="86" customHeight="1" ht="20">
@@ -3488,22 +3488,22 @@
         <v>381</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>1082</v>
+        <v>962</v>
       </c>
       <c r="C86" s="6" t="n">
-        <v>45177</v>
+        <v>45110</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>45179</v>
+        <v>45111</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
@@ -3514,36 +3514,36 @@
         <v>17</v>
       </c>
       <c r="N86" s="8" t="n">
-        <v>45173</v>
+        <v>45082</v>
       </c>
       <c r="O86" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P86" s="8" t="n">
-        <v>45173.6145601852</v>
+        <v>45111.2538310185</v>
       </c>
     </row>
     <row r="87" customHeight="1" ht="20">
       <c r="A87" s="5" t="n">
-        <v>301</v>
+        <v>381</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>1122</v>
+        <v>1082</v>
       </c>
       <c r="C87" s="6" t="n">
-        <v>45268</v>
+        <v>45177</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>45270</v>
+        <v>45179</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>145</v>
+        <v>500</v>
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
@@ -3554,36 +3554,36 @@
         <v>17</v>
       </c>
       <c r="N87" s="8" t="n">
-        <v>45205</v>
+        <v>45173</v>
       </c>
       <c r="O87" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P87" s="8" t="n">
-        <v>45267.4084143519</v>
+        <v>45173.6145601852</v>
       </c>
     </row>
     <row r="88" customHeight="1" ht="20">
       <c r="A88" s="5" t="n">
-        <v>81</v>
+        <v>301</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>1162</v>
+        <v>1122</v>
       </c>
       <c r="C88" s="6" t="n">
-        <v>45318</v>
+        <v>45268</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>45319</v>
+        <v>45270</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
@@ -3594,36 +3594,36 @@
         <v>17</v>
       </c>
       <c r="N88" s="8" t="n">
-        <v>45274</v>
+        <v>45205</v>
       </c>
       <c r="O88" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P88" s="8" t="n">
-        <v>45320.4609837963</v>
+        <v>45267.4084143519</v>
       </c>
     </row>
     <row r="89" customHeight="1" ht="20">
       <c r="A89" s="5" t="n">
-        <v>441</v>
+        <v>81</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>1182</v>
+        <v>1162</v>
       </c>
       <c r="C89" s="6" t="n">
-        <v>45290</v>
+        <v>45318</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>45295</v>
+        <v>45319</v>
       </c>
       <c r="E89" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>860</v>
+        <v>250</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>660</v>
+        <v>150</v>
       </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
@@ -3634,36 +3634,36 @@
         <v>17</v>
       </c>
       <c r="N89" s="8" t="n">
-        <v>45277</v>
+        <v>45274</v>
       </c>
       <c r="O89" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P89" s="8" t="n">
-        <v>45285.4578009259</v>
+        <v>45320.4609837963</v>
       </c>
     </row>
     <row r="90" customHeight="1" ht="20">
       <c r="A90" s="5" t="n">
-        <v>261</v>
+        <v>441</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>1202</v>
+        <v>1182</v>
       </c>
       <c r="C90" s="6" t="n">
-        <v>45366</v>
+        <v>45290</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>45368</v>
+        <v>45295</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>385</v>
+        <v>860</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>240</v>
+        <v>660</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
@@ -3674,36 +3674,36 @@
         <v>17</v>
       </c>
       <c r="N90" s="8" t="n">
-        <v>45280</v>
+        <v>45277</v>
       </c>
       <c r="O90" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P90" s="8" t="n">
-        <v>45419.522962963</v>
+        <v>45285.4578009259</v>
       </c>
     </row>
     <row r="91" customHeight="1" ht="20">
       <c r="A91" s="5" t="n">
-        <v>181</v>
+        <v>261</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>1262</v>
+        <v>1202</v>
       </c>
       <c r="C91" s="6" t="n">
-        <v>45339</v>
+        <v>45366</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>45340</v>
+        <v>45368</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>250</v>
+        <v>385</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
@@ -3714,36 +3714,36 @@
         <v>17</v>
       </c>
       <c r="N91" s="8" t="n">
-        <v>45303</v>
+        <v>45280</v>
       </c>
       <c r="O91" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P91" s="8" t="n">
-        <v>45343.4145486111</v>
+        <v>45419.522962963</v>
       </c>
     </row>
     <row r="92" customHeight="1" ht="20">
       <c r="A92" s="5" t="n">
-        <v>27</v>
+        <v>181</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>1342</v>
+        <v>1262</v>
       </c>
       <c r="C92" s="6" t="n">
-        <v>45444</v>
+        <v>45339</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>45451</v>
+        <v>45340</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>940</v>
+        <v>250</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>590</v>
+        <v>150</v>
       </c>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
@@ -3754,32 +3754,36 @@
         <v>17</v>
       </c>
       <c r="N92" s="8" t="n">
-        <v>45313.4136458333</v>
-      </c>
-      <c r="O92" s="7"/>
-      <c r="P92" s="8"/>
+        <v>45303</v>
+      </c>
+      <c r="O92" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P92" s="8" t="n">
+        <v>45343.4145486111</v>
+      </c>
     </row>
     <row r="93" customHeight="1" ht="20">
       <c r="A93" s="5" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>1403</v>
+        <v>1342</v>
       </c>
       <c r="C93" s="6" t="n">
+        <v>45444</v>
+      </c>
+      <c r="D93" s="6" t="n">
         <v>45451</v>
-      </c>
-      <c r="D93" s="6" t="n">
-        <v>45459</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>990</v>
+        <v>940</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>690</v>
+        <v>590</v>
       </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
@@ -3790,32 +3794,32 @@
         <v>17</v>
       </c>
       <c r="N93" s="8" t="n">
-        <v>45348.3647453704</v>
+        <v>45313.4136458333</v>
       </c>
       <c r="O93" s="7"/>
       <c r="P93" s="8"/>
     </row>
     <row r="94" customHeight="1" ht="20">
       <c r="A94" s="5" t="n">
-        <v>321</v>
+        <v>41</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>1444</v>
+        <v>1403</v>
       </c>
       <c r="C94" s="6" t="n">
-        <v>45464</v>
+        <v>45451</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>45478</v>
+        <v>45459</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>1650</v>
+        <v>990</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>1100</v>
+        <v>690</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
@@ -3826,32 +3830,32 @@
         <v>17</v>
       </c>
       <c r="N94" s="8" t="n">
-        <v>45405.5582175926</v>
+        <v>45348.3647453704</v>
       </c>
       <c r="O94" s="7"/>
       <c r="P94" s="8"/>
     </row>
     <row r="95" customHeight="1" ht="20">
       <c r="A95" s="5" t="n">
-        <v>622</v>
+        <v>321</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>1583</v>
+        <v>1444</v>
       </c>
       <c r="C95" s="6" t="n">
-        <v>45767</v>
+        <v>45464</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>45772</v>
+        <v>45478</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>790</v>
+        <v>1650</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>790</v>
+        <v>1100</v>
       </c>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
@@ -3859,39 +3863,35 @@
       <c r="K95" s="5"/>
       <c r="L95" s="7"/>
       <c r="M95" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N95" s="8" t="n">
-        <v>45700</v>
-      </c>
-      <c r="O95" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P95" s="8" t="n">
-        <v>45793.6939930556</v>
-      </c>
+        <v>45405.5582175926</v>
+      </c>
+      <c r="O95" s="7"/>
+      <c r="P95" s="8"/>
     </row>
     <row r="96" customHeight="1" ht="20">
       <c r="A96" s="5" t="n">
-        <v>861</v>
+        <v>622</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>1823</v>
+        <v>1583</v>
       </c>
       <c r="C96" s="6" t="n">
-        <v>46122</v>
+        <v>46114</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>2290</v>
+        <v>760</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>2290</v>
+        <v>770</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
@@ -3902,32 +3902,36 @@
         <v>19</v>
       </c>
       <c r="N96" s="8" t="n">
-        <v>46031.3055439815</v>
-      </c>
-      <c r="O96" s="7"/>
-      <c r="P96" s="8"/>
+        <v>45700</v>
+      </c>
+      <c r="O96" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="P96" s="8" t="n">
+        <v>46047.6481018519</v>
+      </c>
     </row>
     <row r="97" customHeight="1" ht="20">
       <c r="A97" s="5" t="n">
-        <v>681</v>
+        <v>861</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>1647</v>
+        <v>1823</v>
       </c>
       <c r="C97" s="6" t="n">
-        <v>46138</v>
+        <v>46122</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>46144</v>
+        <v>46132</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>1160</v>
+        <v>2290</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>1160</v>
+        <v>2290</v>
       </c>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
@@ -3938,36 +3942,32 @@
         <v>19</v>
       </c>
       <c r="N97" s="8" t="n">
-        <v>45793</v>
-      </c>
-      <c r="O97" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P97" s="8" t="n">
-        <v>45958.4886226852</v>
-      </c>
+        <v>46031.3055439815</v>
+      </c>
+      <c r="O97" s="7"/>
+      <c r="P97" s="8"/>
     </row>
     <row r="98" customHeight="1" ht="20">
       <c r="A98" s="5" t="n">
-        <v>762</v>
+        <v>681</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>1724</v>
+        <v>1647</v>
       </c>
       <c r="C98" s="6" t="n">
-        <v>46021</v>
+        <v>46138</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>46026</v>
+        <v>46144</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>990</v>
+        <v>1160</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>990</v>
+        <v>1160</v>
       </c>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
@@ -3978,27 +3978,27 @@
         <v>19</v>
       </c>
       <c r="N98" s="8" t="n">
-        <v>45963</v>
+        <v>45793</v>
       </c>
       <c r="O98" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P98" s="8" t="n">
-        <v>46030.6411574074</v>
+        <v>45958.4886226852</v>
       </c>
     </row>
     <row r="99" customHeight="1" ht="20">
       <c r="A99" s="5" t="n">
-        <v>621</v>
+        <v>762</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>1683</v>
+        <v>1724</v>
       </c>
       <c r="C99" s="6" t="n">
-        <v>45950</v>
+        <v>46021</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>45955</v>
+        <v>46026</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>18</v>
@@ -4018,36 +4018,36 @@
         <v>19</v>
       </c>
       <c r="N99" s="8" t="n">
-        <v>45908</v>
+        <v>45963</v>
       </c>
       <c r="O99" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P99" s="8" t="n">
-        <v>45951.6467939815</v>
+        <v>46030.6411574074</v>
       </c>
     </row>
     <row r="100" customHeight="1" ht="20">
       <c r="A100" s="5" t="n">
-        <v>781</v>
+        <v>621</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>1743</v>
+        <v>1683</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>46020</v>
+        <v>45950</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>46025</v>
+        <v>45955</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>1</v>
+        <v>990</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>1</v>
+        <v>990</v>
       </c>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
@@ -4058,36 +4058,36 @@
         <v>19</v>
       </c>
       <c r="N100" s="8" t="n">
-        <v>45964</v>
+        <v>45908</v>
       </c>
       <c r="O100" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P100" s="8" t="n">
-        <v>46030.6409490741</v>
+        <v>45951.6467939815</v>
       </c>
     </row>
     <row r="101" customHeight="1" ht="20">
       <c r="A101" s="5" t="n">
-        <v>801</v>
+        <v>781</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>1763</v>
+        <v>1743</v>
       </c>
       <c r="C101" s="6" t="n">
-        <v>46137</v>
+        <v>46020</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>46143</v>
+        <v>46025</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
@@ -4098,32 +4098,36 @@
         <v>19</v>
       </c>
       <c r="N101" s="8" t="n">
-        <v>45981.7479166667</v>
-      </c>
-      <c r="O101" s="7"/>
-      <c r="P101" s="8"/>
+        <v>45964</v>
+      </c>
+      <c r="O101" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P101" s="8" t="n">
+        <v>46030.6409490741</v>
+      </c>
     </row>
     <row r="102" customHeight="1" ht="20">
       <c r="A102" s="5" t="n">
-        <v>1</v>
+        <v>801</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>1</v>
+        <v>1763</v>
       </c>
       <c r="C102" s="6" t="n">
-        <v>43505</v>
+        <v>46137</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>43506</v>
+        <v>46143</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
@@ -4131,39 +4135,35 @@
       <c r="K102" s="5"/>
       <c r="L102" s="7"/>
       <c r="M102" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N102" s="8" t="n">
-        <v>44420</v>
-      </c>
-      <c r="O102" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P102" s="8" t="n">
-        <v>44853.7957060185</v>
-      </c>
+        <v>45981.7479166667</v>
+      </c>
+      <c r="O102" s="7"/>
+      <c r="P102" s="8"/>
     </row>
     <row r="103" customHeight="1" ht="20">
       <c r="A103" s="5" t="n">
-        <v>54</v>
+        <v>881</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>42</v>
+        <v>1843</v>
       </c>
       <c r="C103" s="6" t="n">
-        <v>44345</v>
+        <v>46104</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>44346</v>
+        <v>46108</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>230</v>
+        <v>660</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>130</v>
+        <v>660</v>
       </c>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
@@ -4171,26 +4171,26 @@
       <c r="K103" s="5"/>
       <c r="L103" s="7"/>
       <c r="M103" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N103" s="8" t="n">
-        <v>44445.5079513889</v>
+        <v>46049.8521064815</v>
       </c>
       <c r="O103" s="7"/>
       <c r="P103" s="8"/>
     </row>
     <row r="104" customHeight="1" ht="20">
       <c r="A104" s="5" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="C104" s="6" t="n">
-        <v>44464</v>
+        <v>43505</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>44465</v>
+        <v>43506</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>18</v>
@@ -4210,27 +4210,27 @@
         <v>17</v>
       </c>
       <c r="N104" s="8" t="n">
-        <v>44445</v>
+        <v>44420</v>
       </c>
       <c r="O104" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P104" s="8" t="n">
-        <v>44764.5626388889</v>
+        <v>44853.7957060185</v>
       </c>
     </row>
     <row r="105" customHeight="1" ht="20">
       <c r="A105" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C105" s="6" t="n">
-        <v>44474</v>
+        <v>44345</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>44475</v>
+        <v>44346</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>16</v>
@@ -4250,27 +4250,23 @@
         <v>17</v>
       </c>
       <c r="N105" s="8" t="n">
-        <v>44446.2805902778</v>
-      </c>
-      <c r="O105" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P105" s="8" t="n">
-        <v>44586.645775463</v>
-      </c>
+        <v>44445.5079513889</v>
+      </c>
+      <c r="O105" s="7"/>
+      <c r="P105" s="8"/>
     </row>
     <row r="106" customHeight="1" ht="20">
       <c r="A106" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C106" s="6" t="n">
-        <v>43603</v>
+        <v>44464</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>43604</v>
+        <v>44465</v>
       </c>
       <c r="E106" s="7" t="s">
         <v>18</v>
@@ -4290,36 +4286,36 @@
         <v>17</v>
       </c>
       <c r="N106" s="8" t="n">
-        <v>44446</v>
+        <v>44445</v>
       </c>
       <c r="O106" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P106" s="8" t="n">
-        <v>44764.6144791667</v>
+        <v>44764.5626388889</v>
       </c>
     </row>
     <row r="107" customHeight="1" ht="20">
       <c r="A107" s="5" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C107" s="6" t="n">
-        <v>43506</v>
+        <v>44474</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>43506</v>
+        <v>44475</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F107" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="G107" s="5" t="n">
         <v>130</v>
-      </c>
-      <c r="G107" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
@@ -4330,36 +4326,36 @@
         <v>17</v>
       </c>
       <c r="N107" s="8" t="n">
-        <v>44446</v>
+        <v>44446.2805902778</v>
       </c>
       <c r="O107" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P107" s="8" t="n">
-        <v>44767.5292824074</v>
+        <v>44586.645775463</v>
       </c>
     </row>
     <row r="108" customHeight="1" ht="20">
       <c r="A108" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C108" s="6" t="n">
-        <v>43877</v>
+        <v>43603</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>43877</v>
+        <v>43604</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F108" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="G108" s="5" t="n">
         <v>130</v>
-      </c>
-      <c r="G108" s="5" t="n">
-        <v>30</v>
       </c>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
@@ -4376,30 +4372,30 @@
         <v>17</v>
       </c>
       <c r="P108" s="8" t="n">
-        <v>44767.5397337963</v>
+        <v>44764.6144791667</v>
       </c>
     </row>
     <row r="109" customHeight="1" ht="20">
       <c r="A109" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C109" s="6" t="n">
-        <v>44170</v>
+        <v>43506</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>44173</v>
+        <v>43506</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>495</v>
+        <v>130</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>310</v>
+        <v>30</v>
       </c>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
@@ -4410,32 +4406,36 @@
         <v>17</v>
       </c>
       <c r="N109" s="8" t="n">
-        <v>44446.5258333333</v>
-      </c>
-      <c r="O109" s="7"/>
-      <c r="P109" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O109" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P109" s="8" t="n">
+        <v>44767.5292824074</v>
+      </c>
     </row>
     <row r="110" customHeight="1" ht="20">
       <c r="A110" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C110" s="6" t="n">
-        <v>44331</v>
+        <v>43877</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>44332</v>
+        <v>43877</v>
       </c>
       <c r="E110" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
@@ -4452,30 +4452,30 @@
         <v>17</v>
       </c>
       <c r="P110" s="8" t="n">
-        <v>44785.5036921296</v>
+        <v>44767.5397337963</v>
       </c>
     </row>
     <row r="111" customHeight="1" ht="20">
       <c r="A111" s="5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C111" s="6" t="n">
-        <v>43554</v>
+        <v>44170</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>43554</v>
+        <v>44173</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>130</v>
+        <v>495</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>30</v>
+        <v>310</v>
       </c>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
@@ -4486,27 +4486,23 @@
         <v>17</v>
       </c>
       <c r="N111" s="8" t="n">
-        <v>44446</v>
-      </c>
-      <c r="O111" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P111" s="8" t="n">
-        <v>44785.5278240741</v>
-      </c>
+        <v>44446.5258333333</v>
+      </c>
+      <c r="O111" s="7"/>
+      <c r="P111" s="8"/>
     </row>
     <row r="112" customHeight="1" ht="20">
       <c r="A112" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C112" s="6" t="n">
-        <v>43764</v>
+        <v>44331</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>43765</v>
+        <v>44332</v>
       </c>
       <c r="E112" s="7" t="s">
         <v>18</v>
@@ -4532,30 +4528,30 @@
         <v>17</v>
       </c>
       <c r="P112" s="8" t="n">
-        <v>44785.5824074074</v>
+        <v>44785.5036921296</v>
       </c>
     </row>
     <row r="113" customHeight="1" ht="20">
       <c r="A113" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C113" s="6" t="n">
-        <v>43862</v>
+        <v>43554</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>43863</v>
+        <v>43554</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
@@ -4572,7 +4568,7 @@
         <v>17</v>
       </c>
       <c r="P113" s="8" t="n">
-        <v>44785.5965856481</v>
+        <v>44785.5278240741</v>
       </c>
     </row>
     <row r="114" customHeight="1" ht="20">
@@ -4580,13 +4576,13 @@
         <v>48</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C114" s="6" t="n">
-        <v>44009</v>
+        <v>43764</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>44010</v>
+        <v>43765</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>18</v>
@@ -4612,7 +4608,7 @@
         <v>17</v>
       </c>
       <c r="P114" s="8" t="n">
-        <v>44785.6159259259</v>
+        <v>44785.5824074074</v>
       </c>
     </row>
     <row r="115" customHeight="1" ht="20">
@@ -4620,13 +4616,13 @@
         <v>48</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C115" s="6" t="n">
-        <v>44100</v>
+        <v>43862</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>44101</v>
+        <v>43863</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>18</v>
@@ -4652,21 +4648,21 @@
         <v>17</v>
       </c>
       <c r="P115" s="8" t="n">
-        <v>44792.5683217593</v>
+        <v>44785.5965856481</v>
       </c>
     </row>
     <row r="116" customHeight="1" ht="20">
       <c r="A116" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C116" s="6" t="n">
-        <v>44338</v>
+        <v>44009</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>44339</v>
+        <v>44010</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>18</v>
@@ -4692,21 +4688,21 @@
         <v>17</v>
       </c>
       <c r="P116" s="8" t="n">
-        <v>44792.5857291667</v>
+        <v>44785.6159259259</v>
       </c>
     </row>
     <row r="117" customHeight="1" ht="20">
       <c r="A117" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C117" s="6" t="n">
-        <v>44107</v>
+        <v>44100</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>44108</v>
+        <v>44101</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>18</v>
@@ -4732,21 +4728,21 @@
         <v>17</v>
       </c>
       <c r="P117" s="8" t="n">
-        <v>44819.4365393519</v>
+        <v>44792.5683217593</v>
       </c>
     </row>
     <row r="118" customHeight="1" ht="20">
       <c r="A118" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C118" s="6" t="n">
-        <v>44401</v>
+        <v>44338</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>44402</v>
+        <v>44339</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>18</v>
@@ -4772,30 +4768,30 @@
         <v>17</v>
       </c>
       <c r="P118" s="8" t="n">
-        <v>44819.4539351852</v>
+        <v>44792.5857291667</v>
       </c>
     </row>
     <row r="119" customHeight="1" ht="20">
       <c r="A119" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C119" s="6" t="n">
-        <v>43769</v>
+        <v>44107</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>43772</v>
+        <v>44108</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>495</v>
+        <v>230</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>245</v>
+        <v>130</v>
       </c>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
@@ -4812,30 +4808,30 @@
         <v>17</v>
       </c>
       <c r="P119" s="8" t="n">
-        <v>44819.5838773148</v>
+        <v>44819.4365393519</v>
       </c>
     </row>
     <row r="120" customHeight="1" ht="20">
       <c r="A120" s="5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C120" s="6" t="n">
-        <v>44498</v>
+        <v>44401</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>44501</v>
+        <v>44402</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>495</v>
+        <v>230</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>310</v>
+        <v>130</v>
       </c>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
@@ -4852,30 +4848,30 @@
         <v>17</v>
       </c>
       <c r="P120" s="8" t="n">
-        <v>44837.6617939815</v>
+        <v>44819.4539351852</v>
       </c>
     </row>
     <row r="121" customHeight="1" ht="20">
       <c r="A121" s="5" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C121" s="6" t="n">
-        <v>43981</v>
+        <v>43769</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>43989</v>
+        <v>43772</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>1050</v>
+        <v>495</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>580</v>
+        <v>245</v>
       </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
@@ -4886,32 +4882,36 @@
         <v>17</v>
       </c>
       <c r="N121" s="8" t="n">
-        <v>44446.5351157407</v>
-      </c>
-      <c r="O121" s="7"/>
-      <c r="P121" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O121" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P121" s="8" t="n">
+        <v>44819.5838773148</v>
+      </c>
     </row>
     <row r="122" customHeight="1" ht="20">
       <c r="A122" s="5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>44450</v>
+        <v>44498</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>44457</v>
+        <v>44501</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>970</v>
+        <v>495</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>690</v>
+        <v>310</v>
       </c>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
@@ -4922,32 +4922,36 @@
         <v>17</v>
       </c>
       <c r="N122" s="8" t="n">
-        <v>44446.5361226852</v>
-      </c>
-      <c r="O122" s="7"/>
-      <c r="P122" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O122" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P122" s="8" t="n">
+        <v>44837.6617939815</v>
+      </c>
     </row>
     <row r="123" customHeight="1" ht="20">
       <c r="A123" s="5" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C123" s="6" t="n">
-        <v>44023</v>
+        <v>43981</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>44029</v>
+        <v>43989</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>790</v>
+        <v>1050</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
@@ -4958,32 +4962,32 @@
         <v>17</v>
       </c>
       <c r="N123" s="8" t="n">
-        <v>44446.5370138889</v>
+        <v>44446.5351157407</v>
       </c>
       <c r="O123" s="7"/>
       <c r="P123" s="8"/>
     </row>
     <row r="124" customHeight="1" ht="20">
       <c r="A124" s="5" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C124" s="6" t="n">
-        <v>43575</v>
+        <v>44450</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>43581</v>
+        <v>44457</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>860</v>
+        <v>970</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>550</v>
+        <v>690</v>
       </c>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
@@ -4994,32 +4998,32 @@
         <v>17</v>
       </c>
       <c r="N124" s="8" t="n">
-        <v>44446.5379398148</v>
+        <v>44446.5361226852</v>
       </c>
       <c r="O124" s="7"/>
       <c r="P124" s="8"/>
     </row>
     <row r="125" customHeight="1" ht="20">
       <c r="A125" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C125" s="6" t="n">
-        <v>44284</v>
+        <v>44023</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>44290</v>
+        <v>44029</v>
       </c>
       <c r="E125" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>890</v>
+        <v>790</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
@@ -5030,7 +5034,7 @@
         <v>17</v>
       </c>
       <c r="N125" s="8" t="n">
-        <v>44446.5387268519</v>
+        <v>44446.5370138889</v>
       </c>
       <c r="O125" s="7"/>
       <c r="P125" s="8"/>
@@ -5040,22 +5044,22 @@
         <v>25</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C126" s="6" t="n">
-        <v>44665</v>
+        <v>43575</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>44671</v>
+        <v>43581</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>1150</v>
+        <v>860</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>770</v>
+        <v>550</v>
       </c>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
@@ -5066,36 +5070,32 @@
         <v>17</v>
       </c>
       <c r="N126" s="8" t="n">
-        <v>44446</v>
-      </c>
-      <c r="O126" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P126" s="8" t="n">
-        <v>44676.391724537</v>
-      </c>
+        <v>44446.5379398148</v>
+      </c>
+      <c r="O126" s="7"/>
+      <c r="P126" s="8"/>
     </row>
     <row r="127" customHeight="1" ht="20">
       <c r="A127" s="5" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>263</v>
+        <v>77</v>
       </c>
       <c r="C127" s="6" t="n">
-        <v>44653</v>
+        <v>44284</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>44653</v>
+        <v>44290</v>
       </c>
       <c r="E127" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>130</v>
+        <v>890</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>30</v>
+        <v>590</v>
       </c>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
@@ -5106,32 +5106,32 @@
         <v>17</v>
       </c>
       <c r="N127" s="8" t="n">
-        <v>44646.3677199074</v>
+        <v>44446.5387268519</v>
       </c>
       <c r="O127" s="7"/>
       <c r="P127" s="8"/>
     </row>
     <row r="128" customHeight="1" ht="20">
       <c r="A128" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C128" s="6" t="n">
-        <v>44359</v>
+        <v>44665</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>44360</v>
+        <v>44671</v>
       </c>
       <c r="E128" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>230</v>
+        <v>1150</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>130</v>
+        <v>770</v>
       </c>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
@@ -5142,74 +5142,72 @@
         <v>17</v>
       </c>
       <c r="N128" s="8" t="n">
-        <v>44446.542337963</v>
-      </c>
-      <c r="O128" s="7"/>
-      <c r="P128" s="8"/>
+        <v>44446</v>
+      </c>
+      <c r="O128" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P128" s="8" t="n">
+        <v>44676.391724537</v>
+      </c>
     </row>
     <row r="129" customHeight="1" ht="20">
       <c r="A129" s="5" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>85</v>
+        <v>263</v>
       </c>
       <c r="C129" s="6" t="n">
-        <v>44450</v>
+        <v>44653</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>44453</v>
+        <v>44653</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>830</v>
+        <v>130</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
       <c r="K129" s="5"/>
-      <c r="L129" s="7" t="s">
-        <v>21</v>
-      </c>
+      <c r="L129" s="7"/>
       <c r="M129" s="7" t="s">
         <v>17</v>
       </c>
       <c r="N129" s="8" t="n">
-        <v>44447</v>
-      </c>
-      <c r="O129" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P129" s="8" t="n">
-        <v>44837.6220949074</v>
-      </c>
+        <v>44646.3677199074</v>
+      </c>
+      <c r="O129" s="7"/>
+      <c r="P129" s="8"/>
     </row>
     <row r="130" customHeight="1" ht="20">
       <c r="A130" s="5" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>342</v>
+        <v>84</v>
       </c>
       <c r="C130" s="6" t="n">
-        <v>44723</v>
+        <v>44359</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>44724</v>
+        <v>44360</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
@@ -5220,67 +5218,65 @@
         <v>17</v>
       </c>
       <c r="N130" s="8" t="n">
-        <v>44665</v>
-      </c>
-      <c r="O130" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P130" s="8" t="n">
-        <v>44731.4374652778</v>
-      </c>
+        <v>44446.542337963</v>
+      </c>
+      <c r="O130" s="7"/>
+      <c r="P130" s="8"/>
     </row>
     <row r="131" customHeight="1" ht="20">
       <c r="A131" s="5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>422</v>
+        <v>85</v>
       </c>
       <c r="C131" s="6" t="n">
-        <v>44828</v>
+        <v>44450</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>44829</v>
+        <v>44453</v>
       </c>
       <c r="E131" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>245</v>
+        <v>830</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
       <c r="K131" s="5"/>
-      <c r="L131" s="7"/>
+      <c r="L131" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="M131" s="7" t="s">
         <v>17</v>
       </c>
       <c r="N131" s="8" t="n">
-        <v>44748</v>
+        <v>44447</v>
       </c>
       <c r="O131" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P131" s="8" t="n">
-        <v>44830.3892361111</v>
+        <v>44837.6220949074</v>
       </c>
     </row>
     <row r="132" customHeight="1" ht="20">
       <c r="A132" s="5" t="n">
-        <v>181</v>
+        <v>54</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>502</v>
+        <v>342</v>
       </c>
       <c r="C132" s="6" t="n">
-        <v>44849</v>
+        <v>44723</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>44850</v>
+        <v>44724</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>18</v>
@@ -5300,13 +5296,13 @@
         <v>17</v>
       </c>
       <c r="N132" s="8" t="n">
-        <v>44810</v>
+        <v>44665</v>
       </c>
       <c r="O132" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P132" s="8" t="n">
-        <v>44847.397962963</v>
+        <v>44731.4374652778</v>
       </c>
     </row>
     <row r="133" customHeight="1" ht="20">
@@ -5314,22 +5310,22 @@
         <v>48</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>682</v>
+        <v>422</v>
       </c>
       <c r="C133" s="6" t="n">
-        <v>44989</v>
+        <v>44828</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>44990</v>
+        <v>44829</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
@@ -5340,36 +5336,36 @@
         <v>17</v>
       </c>
       <c r="N133" s="8" t="n">
-        <v>44970</v>
+        <v>44748</v>
       </c>
       <c r="O133" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P133" s="8" t="n">
-        <v>44988.7055555556</v>
+        <v>44830.3892361111</v>
       </c>
     </row>
     <row r="134" customHeight="1" ht="20">
       <c r="A134" s="5" t="n">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>702</v>
+        <v>502</v>
       </c>
       <c r="C134" s="6" t="n">
-        <v>44996</v>
+        <v>44849</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>44997</v>
+        <v>44850</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
@@ -5380,36 +5376,36 @@
         <v>17</v>
       </c>
       <c r="N134" s="8" t="n">
-        <v>44986</v>
+        <v>44810</v>
       </c>
       <c r="O134" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P134" s="8" t="n">
-        <v>44998.346400463</v>
+        <v>44847.397962963</v>
       </c>
     </row>
     <row r="135" customHeight="1" ht="20">
       <c r="A135" s="5" t="n">
-        <v>281</v>
+        <v>48</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>822</v>
+        <v>682</v>
       </c>
       <c r="C135" s="6" t="n">
-        <v>45227</v>
+        <v>44989</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>45230</v>
+        <v>44990</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>540</v>
+        <v>250</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>345</v>
+        <v>150</v>
       </c>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
@@ -5420,36 +5416,36 @@
         <v>17</v>
       </c>
       <c r="N135" s="8" t="n">
-        <v>45032</v>
+        <v>44970</v>
       </c>
       <c r="O135" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P135" s="8" t="n">
-        <v>45231.536724537</v>
+        <v>44988.7055555556</v>
       </c>
     </row>
     <row r="136" customHeight="1" ht="20">
       <c r="A136" s="5" t="n">
-        <v>361</v>
+        <v>81</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>902</v>
+        <v>702</v>
       </c>
       <c r="C136" s="6" t="n">
-        <v>45074</v>
+        <v>44996</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>45078</v>
+        <v>44997</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>695</v>
+        <v>250</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>495</v>
+        <v>150</v>
       </c>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
@@ -5460,36 +5456,36 @@
         <v>17</v>
       </c>
       <c r="N136" s="8" t="n">
-        <v>45069</v>
+        <v>44986</v>
       </c>
       <c r="O136" s="7" t="s">
         <v>17</v>
       </c>
       <c r="P136" s="8" t="n">
-        <v>45071.3412962963</v>
+        <v>44998.346400463</v>
       </c>
     </row>
     <row r="137" customHeight="1" ht="20">
       <c r="A137" s="5" t="n">
-        <v>401</v>
+        <v>281</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>982</v>
+        <v>822</v>
       </c>
       <c r="C137" s="6" t="n">
-        <v>45129</v>
+        <v>45227</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>45132</v>
+        <v>45230</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>670</v>
+        <v>540</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>380</v>
+        <v>345</v>
       </c>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
@@ -5500,32 +5496,36 @@
         <v>17</v>
       </c>
       <c r="N137" s="8" t="n">
-        <v>45111.2535763889</v>
-      </c>
-      <c r="O137" s="7"/>
-      <c r="P137" s="8"/>
+        <v>45032</v>
+      </c>
+      <c r="O137" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P137" s="8" t="n">
+        <v>45231.536724537</v>
+      </c>
     </row>
     <row r="138" customHeight="1" ht="20">
       <c r="A138" s="5" t="n">
-        <v>41</v>
+        <v>361</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>1062</v>
+        <v>902</v>
       </c>
       <c r="C138" s="6" t="n">
-        <v>45206</v>
+        <v>45074</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>45214</v>
+        <v>45078</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>1100</v>
+        <v>695</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>710</v>
+        <v>495</v>
       </c>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
@@ -5536,32 +5536,36 @@
         <v>17</v>
       </c>
       <c r="N138" s="8" t="n">
-        <v>45171.606875</v>
-      </c>
-      <c r="O138" s="7"/>
-      <c r="P138" s="8"/>
+        <v>45069</v>
+      </c>
+      <c r="O138" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P138" s="8" t="n">
+        <v>45071.3412962963</v>
+      </c>
     </row>
     <row r="139" customHeight="1" ht="20">
       <c r="A139" s="5" t="n">
-        <v>461</v>
+        <v>401</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>1302</v>
+        <v>982</v>
       </c>
       <c r="C139" s="6" t="n">
-        <v>45346</v>
+        <v>45129</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>45347</v>
+        <v>45132</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>250</v>
+        <v>670</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>150</v>
+        <v>380</v>
       </c>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
@@ -5572,36 +5576,32 @@
         <v>17</v>
       </c>
       <c r="N139" s="8" t="n">
-        <v>45308</v>
-      </c>
-      <c r="O139" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P139" s="8" t="n">
-        <v>45345.4013194444</v>
-      </c>
+        <v>45111.2535763889</v>
+      </c>
+      <c r="O139" s="7"/>
+      <c r="P139" s="8"/>
     </row>
     <row r="140" customHeight="1" ht="20">
       <c r="A140" s="5" t="n">
-        <v>541</v>
+        <v>41</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>1503</v>
+        <v>1062</v>
       </c>
       <c r="C140" s="6" t="n">
-        <v>45594</v>
+        <v>45206</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>45598</v>
+        <v>45214</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>690</v>
+        <v>1100</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>690</v>
+        <v>710</v>
       </c>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
@@ -5609,39 +5609,35 @@
       <c r="K140" s="5"/>
       <c r="L140" s="7"/>
       <c r="M140" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N140" s="8" t="n">
-        <v>45582</v>
-      </c>
-      <c r="O140" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P140" s="8" t="n">
-        <v>45793.6943287037</v>
-      </c>
+        <v>45171.606875</v>
+      </c>
+      <c r="O140" s="7"/>
+      <c r="P140" s="8"/>
     </row>
     <row r="141" customHeight="1" ht="20">
       <c r="A141" s="5" t="n">
-        <v>821</v>
+        <v>461</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>1783</v>
+        <v>1302</v>
       </c>
       <c r="C141" s="6" t="n">
-        <v>45996</v>
+        <v>45346</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>45998</v>
+        <v>45347</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>490</v>
+        <v>250</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>490</v>
+        <v>150</v>
       </c>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
@@ -5649,26 +5645,30 @@
       <c r="K141" s="5"/>
       <c r="L141" s="7"/>
       <c r="M141" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N141" s="8" t="n">
-        <v>45983.3458449074</v>
-      </c>
-      <c r="O141" s="7"/>
-      <c r="P141" s="8"/>
+        <v>45308</v>
+      </c>
+      <c r="O141" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P141" s="8" t="n">
+        <v>45345.4013194444</v>
+      </c>
     </row>
     <row r="142" customHeight="1" ht="20">
       <c r="A142" s="5" t="n">
         <v>541</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>1664</v>
+        <v>1503</v>
       </c>
       <c r="C142" s="6" t="n">
-        <v>45915</v>
+        <v>45594</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>45919</v>
+        <v>45598</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>18</v>
@@ -5688,12 +5688,88 @@
         <v>19</v>
       </c>
       <c r="N142" s="8" t="n">
-        <v>45811</v>
+        <v>45582</v>
       </c>
       <c r="O142" s="7" t="s">
         <v>19</v>
       </c>
       <c r="P142" s="8" t="n">
+        <v>45793.6943287037</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" ht="20">
+      <c r="A143" s="5" t="n">
+        <v>821</v>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>1783</v>
+      </c>
+      <c r="C143" s="6" t="n">
+        <v>45996</v>
+      </c>
+      <c r="D143" s="6" t="n">
+        <v>45998</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>490</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>490</v>
+      </c>
+      <c r="H143" s="5"/>
+      <c r="I143" s="5"/>
+      <c r="J143" s="5"/>
+      <c r="K143" s="5"/>
+      <c r="L143" s="7"/>
+      <c r="M143" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="N143" s="8" t="n">
+        <v>45983.3458449074</v>
+      </c>
+      <c r="O143" s="7"/>
+      <c r="P143" s="8"/>
+    </row>
+    <row r="144" customHeight="1" ht="20">
+      <c r="A144" s="5" t="n">
+        <v>541</v>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>1664</v>
+      </c>
+      <c r="C144" s="6" t="n">
+        <v>45915</v>
+      </c>
+      <c r="D144" s="6" t="n">
+        <v>45919</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>690</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>690</v>
+      </c>
+      <c r="H144" s="5"/>
+      <c r="I144" s="5"/>
+      <c r="J144" s="5"/>
+      <c r="K144" s="5"/>
+      <c r="L144" s="7"/>
+      <c r="M144" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="N144" s="8" t="n">
+        <v>45811</v>
+      </c>
+      <c r="O144" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="P144" s="8" t="n">
         <v>45951.6466550926</v>
       </c>
     </row>
